--- a/UA.xlsx
+++ b/UA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7939A7E-0025-4250-84D1-A9FE67563641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7C3E96-253D-4064-A797-4F952D0EE36B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{B45FBDD8-2A38-46CA-919C-F08CA889F169}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
   <si>
     <t>Under Armor</t>
   </si>
@@ -219,7 +219,10 @@
     <t>Apperal</t>
   </si>
   <si>
-    <t>FQ326</t>
+    <t>FY26</t>
+  </si>
+  <si>
+    <t>FQ426</t>
   </si>
 </sst>
 </file>
@@ -677,7 +680,7 @@
         <v>4</v>
       </c>
       <c r="I2" s="2">
-        <v>7.47</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -685,11 +688,10 @@
         <v>5</v>
       </c>
       <c r="I3" s="3">
-        <f>188.834386+34.45+202.605615</f>
-        <v>425.89000099999998</v>
+        <v>425.983</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -701,7 +703,7 @@
       </c>
       <c r="I4" s="3">
         <f>+I2*I3</f>
-        <v>3181.39830747</v>
+        <v>2117.1355100000001</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -712,10 +714,10 @@
         <v>7</v>
       </c>
       <c r="I5" s="3">
-        <v>464.64800000000002</v>
+        <v>309.16800000000001</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -723,11 +725,11 @@
         <v>8</v>
       </c>
       <c r="I6" s="3">
-        <f>599.682+390.049</f>
-        <v>989.73099999999999</v>
+        <f>599.835+590.609</f>
+        <v>1190.444</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -736,7 +738,7 @@
       </c>
       <c r="I7" s="3">
         <f>+I4-I5+I6</f>
-        <v>3706.4813074699996</v>
+        <v>2998.4115099999999</v>
       </c>
     </row>
   </sheetData>
@@ -817,6 +819,9 @@
       <c r="U2" s="4" t="s">
         <v>46</v>
       </c>
+      <c r="V2" s="12" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="3" spans="1:91" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -867,7 +872,9 @@
       <c r="U3" s="6">
         <v>3105.6239999999998</v>
       </c>
-      <c r="V3" s="6"/>
+      <c r="V3" s="6">
+        <v>2859.42</v>
+      </c>
       <c r="W3" s="6"/>
       <c r="X3" s="6"/>
       <c r="Y3" s="6"/>
@@ -970,7 +977,9 @@
       <c r="U4" s="6">
         <v>1086.578</v>
       </c>
-      <c r="V4" s="6"/>
+      <c r="V4" s="6">
+        <v>1180.51</v>
+      </c>
       <c r="W4" s="6"/>
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
@@ -1073,7 +1082,9 @@
       <c r="U5" s="6">
         <v>755.43700000000001</v>
       </c>
-      <c r="V5" s="6"/>
+      <c r="V5" s="6">
+        <v>719.13400000000001</v>
+      </c>
       <c r="W5" s="6"/>
       <c r="X5" s="6"/>
       <c r="Y5" s="6"/>
@@ -1176,7 +1187,9 @@
       <c r="U6" s="6">
         <v>215.42700000000002</v>
       </c>
-      <c r="V6" s="6"/>
+      <c r="V6" s="6">
+        <v>234.191</v>
+      </c>
       <c r="W6" s="6"/>
       <c r="X6" s="6"/>
       <c r="Y6" s="6"/>
@@ -1279,7 +1292,9 @@
       <c r="U7" s="6">
         <v>3451.4139999999998</v>
       </c>
-      <c r="V7" s="6"/>
+      <c r="V7" s="6">
+        <v>3395.0529999999999</v>
+      </c>
       <c r="W7" s="6"/>
       <c r="X7" s="6"/>
       <c r="Y7" s="6"/>
@@ -1382,7 +1397,9 @@
       <c r="U8" s="6">
         <v>1206.202</v>
       </c>
-      <c r="V8" s="6"/>
+      <c r="V8" s="6">
+        <v>1076.383</v>
+      </c>
       <c r="W8" s="6"/>
       <c r="X8" s="6"/>
       <c r="Y8" s="6"/>
@@ -1485,7 +1502,9 @@
       <c r="U9" s="6">
         <v>410.86</v>
       </c>
-      <c r="V9" s="6"/>
+      <c r="V9" s="6">
+        <v>414.46600000000001</v>
+      </c>
       <c r="W9" s="6"/>
       <c r="X9" s="6"/>
       <c r="Y9" s="6"/>
@@ -1588,7 +1607,9 @@
       <c r="U10" s="6">
         <v>2978.8690000000001</v>
       </c>
-      <c r="V10" s="6"/>
+      <c r="V10" s="6">
+        <v>2831.7869999999998</v>
+      </c>
       <c r="W10" s="6"/>
       <c r="X10" s="6"/>
       <c r="Y10" s="6"/>
@@ -1691,7 +1712,9 @@
       <c r="U11" s="6">
         <v>2089.607</v>
       </c>
-      <c r="V11" s="6"/>
+      <c r="V11" s="6">
+        <v>2054.1149999999998</v>
+      </c>
       <c r="W11" s="6"/>
       <c r="X11" s="6"/>
       <c r="Y11" s="6"/>
@@ -1794,7 +1817,9 @@
       <c r="U12" s="6">
         <v>97.580999999999989</v>
       </c>
-      <c r="V12" s="6"/>
+      <c r="V12" s="6">
+        <v>107.35299999999999</v>
+      </c>
       <c r="W12" s="6"/>
       <c r="X12" s="6"/>
       <c r="Y12" s="6"/>
@@ -1897,7 +1922,9 @@
       <c r="U13" s="6">
         <v>1.244</v>
       </c>
-      <c r="V13" s="6"/>
+      <c r="V13" s="6">
+        <v>-26.885000000000002</v>
+      </c>
       <c r="W13" s="6"/>
       <c r="X13" s="6"/>
       <c r="Y13" s="6"/>
@@ -2000,7 +2027,9 @@
       <c r="U14" s="7">
         <v>5164.3099999999995</v>
       </c>
-      <c r="V14" s="7"/>
+      <c r="V14" s="7">
+        <v>4966.37</v>
+      </c>
       <c r="W14" s="7"/>
       <c r="X14" s="6"/>
       <c r="Y14" s="6"/>
@@ -2120,7 +2149,9 @@
       <c r="U15" s="6">
         <v>2689.5659999999998</v>
       </c>
-      <c r="V15" s="6"/>
+      <c r="V15" s="6">
+        <v>2707.5120000000002</v>
+      </c>
       <c r="W15" s="6"/>
       <c r="X15" s="6"/>
       <c r="Y15" s="6"/>
@@ -2256,7 +2287,10 @@
         <f>+U14-U15</f>
         <v>2474.7439999999997</v>
       </c>
-      <c r="V16" s="6"/>
+      <c r="V16" s="6">
+        <f>+V14-V15</f>
+        <v>2258.8579999999997</v>
+      </c>
       <c r="W16" s="6"/>
       <c r="X16" s="6"/>
       <c r="Y16" s="6"/>
@@ -2376,7 +2410,9 @@
       <c r="U17" s="6">
         <v>2601.991</v>
       </c>
-      <c r="V17" s="6"/>
+      <c r="V17" s="6">
+        <v>2294.2510000000002</v>
+      </c>
       <c r="W17" s="6"/>
       <c r="X17" s="6"/>
       <c r="Y17" s="6"/>
@@ -2496,7 +2532,9 @@
       <c r="U18" s="6">
         <v>57.968999999999994</v>
       </c>
-      <c r="V18" s="6"/>
+      <c r="V18" s="6">
+        <v>127.71899999999999</v>
+      </c>
       <c r="W18" s="6"/>
       <c r="X18" s="6"/>
       <c r="Y18" s="6"/>
@@ -2625,14 +2663,17 @@
       <c r="R19" s="6"/>
       <c r="S19" s="6"/>
       <c r="T19" s="6">
-        <f t="shared" ref="T19:U19" si="4">+T16-T17-T18</f>
+        <f t="shared" ref="T19:V19" si="4">+T16-T17-T18</f>
         <v>229.75099999999975</v>
       </c>
       <c r="U19" s="6">
         <f t="shared" si="4"/>
         <v>-185.21600000000029</v>
       </c>
-      <c r="V19" s="6"/>
+      <c r="V19" s="6">
+        <f t="shared" si="4"/>
+        <v>-163.11200000000048</v>
+      </c>
       <c r="W19" s="6"/>
       <c r="X19" s="6"/>
       <c r="Y19" s="6"/>
@@ -2752,7 +2793,9 @@
       <c r="U20" s="6">
         <v>-6.1150000000000002</v>
       </c>
-      <c r="V20" s="6"/>
+      <c r="V20" s="6">
+        <v>-30.288</v>
+      </c>
       <c r="W20" s="6"/>
       <c r="X20" s="6"/>
       <c r="Y20" s="6"/>
@@ -2872,7 +2915,9 @@
       <c r="U21" s="6">
         <v>-13.431000000000001</v>
       </c>
-      <c r="V21" s="6"/>
+      <c r="V21" s="6">
+        <v>-7.2759999999999998</v>
+      </c>
       <c r="W21" s="6"/>
       <c r="X21" s="6"/>
       <c r="Y21" s="6"/>
@@ -3001,14 +3046,17 @@
       <c r="R22" s="6"/>
       <c r="S22" s="6"/>
       <c r="T22" s="6">
-        <f t="shared" ref="T22:U22" si="7">+T19+SUM(T20:T21)</f>
+        <f t="shared" ref="T22:V22" si="7">+T19+SUM(T20:T21)</f>
         <v>262.03799999999978</v>
       </c>
       <c r="U22" s="6">
         <f t="shared" si="7"/>
         <v>-204.76200000000028</v>
       </c>
-      <c r="V22" s="6"/>
+      <c r="V22" s="6">
+        <f t="shared" si="7"/>
+        <v>-200.67600000000047</v>
+      </c>
       <c r="W22" s="6"/>
       <c r="X22" s="6"/>
       <c r="Y22" s="6"/>
@@ -3128,7 +3176,9 @@
       <c r="U23" s="6">
         <v>-2.8900000000000006</v>
       </c>
-      <c r="V23" s="6"/>
+      <c r="V23" s="6">
+        <v>294.75200000000001</v>
+      </c>
       <c r="W23" s="6"/>
       <c r="X23" s="6"/>
       <c r="Y23" s="6"/>
@@ -3248,7 +3298,9 @@
       <c r="U24" s="6">
         <v>0.60499999999999998</v>
       </c>
-      <c r="V24" s="6"/>
+      <c r="V24" s="6">
+        <v>-0.215</v>
+      </c>
       <c r="W24" s="6"/>
       <c r="X24" s="6"/>
       <c r="Y24" s="6"/>
@@ -3377,14 +3429,17 @@
       <c r="R25" s="6"/>
       <c r="S25" s="6"/>
       <c r="T25" s="6">
-        <f t="shared" ref="T25:U25" si="10">+T22-T23+T24</f>
+        <f t="shared" ref="T25:V25" si="10">+T22-T23+T24</f>
         <v>232.00599999999977</v>
       </c>
       <c r="U25" s="6">
         <f t="shared" si="10"/>
         <v>-201.26700000000031</v>
       </c>
-      <c r="V25" s="6"/>
+      <c r="V25" s="6">
+        <f t="shared" si="10"/>
+        <v>-495.64300000000043</v>
+      </c>
       <c r="W25" s="6"/>
       <c r="X25" s="6"/>
       <c r="Y25" s="6"/>
@@ -3611,7 +3666,10 @@
         <f>+U25/U28</f>
         <v>-0.46563876193351661</v>
       </c>
-      <c r="V27" s="8"/>
+      <c r="V27" s="8">
+        <f>+V25/V28</f>
+        <v>-1.1619129109769688</v>
+      </c>
       <c r="W27" s="8"/>
       <c r="X27" s="8"/>
       <c r="Y27" s="8"/>
@@ -3733,7 +3791,9 @@
         <f>+AVERAGE(G28:J28)</f>
         <v>432.23849999999999</v>
       </c>
-      <c r="V28" s="3"/>
+      <c r="V28" s="3">
+        <v>426.57499999999999</v>
+      </c>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>

--- a/UA.xlsx
+++ b/UA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7C3E96-253D-4064-A797-4F952D0EE36B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD604C5-A11D-4AD9-93C2-732E36F0C384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{B45FBDD8-2A38-46CA-919C-F08CA889F169}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{B45FBDD8-2A38-46CA-919C-F08CA889F169}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="66">
   <si>
     <t>Under Armor</t>
   </si>
@@ -222,7 +222,19 @@
     <t>FY26</t>
   </si>
   <si>
-    <t>FQ426</t>
+    <t>FQ127</t>
+  </si>
+  <si>
+    <t>Q127</t>
+  </si>
+  <si>
+    <t>Q227</t>
+  </si>
+  <si>
+    <t>Q327</t>
+  </si>
+  <si>
+    <t>Q427</t>
   </si>
 </sst>
 </file>
@@ -234,13 +246,19 @@
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -303,24 +321,27 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -680,7 +701,7 @@
         <v>4</v>
       </c>
       <c r="I2" s="2">
-        <v>4.97</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -688,9 +709,10 @@
         <v>5</v>
       </c>
       <c r="I3" s="3">
-        <v>425.983</v>
-      </c>
-      <c r="J3" s="12" t="s">
+        <f>108.839506+34.45+206.256034</f>
+        <v>349.54554000000002</v>
+      </c>
+      <c r="J3" s="13" t="s">
         <v>61</v>
       </c>
     </row>
@@ -703,7 +725,7 @@
       </c>
       <c r="I4" s="3">
         <f>+I2*I3</f>
-        <v>2117.1355100000001</v>
+        <v>1932.9868362000002</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -714,9 +736,9 @@
         <v>7</v>
       </c>
       <c r="I5" s="3">
-        <v>309.16800000000001</v>
-      </c>
-      <c r="J5" s="12" t="s">
+        <v>395.98099999999999</v>
+      </c>
+      <c r="J5" s="13" t="s">
         <v>61</v>
       </c>
     </row>
@@ -725,10 +747,9 @@
         <v>8</v>
       </c>
       <c r="I6" s="3">
-        <f>599.835+590.609</f>
-        <v>1190.444</v>
-      </c>
-      <c r="J6" s="12" t="s">
+        <v>591.15800000000002</v>
+      </c>
+      <c r="J6" s="13" t="s">
         <v>61</v>
       </c>
     </row>
@@ -738,7 +759,7 @@
       </c>
       <c r="I7" s="3">
         <f>+I4-I5+I6</f>
-        <v>2998.4115099999999</v>
+        <v>2128.1638362000003</v>
       </c>
     </row>
   </sheetData>
@@ -751,7 +772,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEC15970-3F02-49AA-AB56-DE3EED2AD09B}">
-  <dimension ref="A1:CM348"/>
+  <dimension ref="A1:CQ348"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -759,12 +780,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:91" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:91" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:95" x14ac:dyDescent="0.2">
       <c r="C2" s="4" t="s">
         <v>12</v>
       </c>
@@ -801,29 +822,41 @@
       <c r="N2" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="O2" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="P2" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q2" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="R2" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="T2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="Y2" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="V2" s="12" t="s">
+      <c r="Z2" s="12" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:91" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:95" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>37</v>
       </c>
@@ -860,25 +893,30 @@
       <c r="M3" s="6">
         <v>756.726</v>
       </c>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
+      <c r="N3" s="6">
+        <f>+Z3-SUM(K3:M3)</f>
+        <v>640.87300000000005</v>
+      </c>
+      <c r="O3" s="6">
+        <v>609.77700000000004</v>
+      </c>
       <c r="P3" s="6"/>
       <c r="Q3" s="6"/>
       <c r="R3" s="6"/>
       <c r="S3" s="6"/>
-      <c r="T3" s="6">
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6">
         <v>3505.1669999999999</v>
       </c>
-      <c r="U3" s="6">
+      <c r="Y3" s="6">
         <v>3105.6239999999998</v>
       </c>
-      <c r="V3" s="6">
+      <c r="Z3" s="6">
         <v>2859.42</v>
       </c>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="6"/>
       <c r="AA3" s="6"/>
       <c r="AB3" s="6"/>
       <c r="AC3" s="6"/>
@@ -927,8 +965,12 @@
       <c r="BT3" s="6"/>
       <c r="BU3" s="6"/>
       <c r="BV3" s="6"/>
-    </row>
-    <row r="4" spans="1:91" x14ac:dyDescent="0.2">
+      <c r="BW3" s="6"/>
+      <c r="BX3" s="6"/>
+      <c r="BY3" s="6"/>
+      <c r="BZ3" s="6"/>
+    </row>
+    <row r="4" spans="1:95" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>38</v>
       </c>
@@ -965,25 +1007,30 @@
       <c r="M4" s="6">
         <v>315.75099999999998</v>
       </c>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
+      <c r="N4" s="6">
+        <f t="shared" ref="N4:N24" si="0">+Z4-SUM(K4:M4)</f>
+        <v>298.47300000000007</v>
+      </c>
+      <c r="O4" s="6">
+        <v>278.68</v>
+      </c>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
       <c r="S4" s="6"/>
-      <c r="T4" s="6">
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6">
         <v>1081.915</v>
       </c>
-      <c r="U4" s="6">
+      <c r="Y4" s="6">
         <v>1086.578</v>
       </c>
-      <c r="V4" s="6">
+      <c r="Z4" s="6">
         <v>1180.51</v>
       </c>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="6"/>
       <c r="AA4" s="6"/>
       <c r="AB4" s="6"/>
       <c r="AC4" s="6"/>
@@ -1032,8 +1079,12 @@
       <c r="BT4" s="6"/>
       <c r="BU4" s="6"/>
       <c r="BV4" s="6"/>
-    </row>
-    <row r="5" spans="1:91" x14ac:dyDescent="0.2">
+      <c r="BW4" s="6"/>
+      <c r="BX4" s="6"/>
+      <c r="BY4" s="6"/>
+      <c r="BZ4" s="6"/>
+    </row>
+    <row r="5" spans="1:95" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>39</v>
       </c>
@@ -1070,25 +1121,30 @@
       <c r="M5" s="6">
         <v>190.88499999999999</v>
       </c>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
+      <c r="N5" s="6">
+        <f t="shared" si="0"/>
+        <v>185.68799999999999</v>
+      </c>
+      <c r="O5" s="6">
+        <v>152.58600000000001</v>
+      </c>
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
       <c r="S5" s="6"/>
-      <c r="T5" s="6">
+      <c r="T5" s="6"/>
+      <c r="U5" s="6"/>
+      <c r="V5" s="6"/>
+      <c r="W5" s="6"/>
+      <c r="X5" s="6">
         <v>873.01900000000001</v>
       </c>
-      <c r="U5" s="6">
+      <c r="Y5" s="6">
         <v>755.43700000000001</v>
       </c>
-      <c r="V5" s="6">
+      <c r="Z5" s="6">
         <v>719.13400000000001</v>
       </c>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="6"/>
       <c r="AA5" s="6"/>
       <c r="AB5" s="6"/>
       <c r="AC5" s="6"/>
@@ -1137,8 +1193,12 @@
       <c r="BT5" s="6"/>
       <c r="BU5" s="6"/>
       <c r="BV5" s="6"/>
-    </row>
-    <row r="6" spans="1:91" x14ac:dyDescent="0.2">
+      <c r="BW5" s="6"/>
+      <c r="BX5" s="6"/>
+      <c r="BY5" s="6"/>
+      <c r="BZ5" s="6"/>
+    </row>
+    <row r="6" spans="1:95" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>40</v>
       </c>
@@ -1175,25 +1235,30 @@
       <c r="M6" s="6">
         <v>70.602999999999994</v>
       </c>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
+      <c r="N6" s="6">
+        <f t="shared" si="0"/>
+        <v>55.198999999999984</v>
+      </c>
+      <c r="O6" s="6">
+        <v>58.753999999999998</v>
+      </c>
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
       <c r="S6" s="6"/>
-      <c r="T6" s="6">
+      <c r="T6" s="6"/>
+      <c r="U6" s="6"/>
+      <c r="V6" s="6"/>
+      <c r="W6" s="6"/>
+      <c r="X6" s="6">
         <v>229.48099999999999</v>
       </c>
-      <c r="U6" s="6">
+      <c r="Y6" s="6">
         <v>215.42700000000002</v>
       </c>
-      <c r="V6" s="6">
+      <c r="Z6" s="6">
         <v>234.191</v>
       </c>
-      <c r="W6" s="6"/>
-      <c r="X6" s="6"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
       <c r="AA6" s="6"/>
       <c r="AB6" s="6"/>
       <c r="AC6" s="6"/>
@@ -1242,8 +1307,12 @@
       <c r="BT6" s="6"/>
       <c r="BU6" s="6"/>
       <c r="BV6" s="6"/>
-    </row>
-    <row r="7" spans="1:91" x14ac:dyDescent="0.2">
+      <c r="BW6" s="6"/>
+      <c r="BX6" s="6"/>
+      <c r="BY6" s="6"/>
+      <c r="BZ6" s="6"/>
+    </row>
+    <row r="7" spans="1:95" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>59</v>
       </c>
@@ -1280,25 +1349,30 @@
       <c r="M7" s="6">
         <v>934.01499999999999</v>
       </c>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
+      <c r="N7" s="6">
+        <f t="shared" si="0"/>
+        <v>777.96300000000019</v>
+      </c>
+      <c r="O7" s="6">
+        <v>734.03499999999997</v>
+      </c>
       <c r="P7" s="6"/>
       <c r="Q7" s="6"/>
       <c r="R7" s="6"/>
       <c r="S7" s="6"/>
-      <c r="T7" s="6">
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6">
         <v>3789.0159999999996</v>
       </c>
-      <c r="U7" s="6">
+      <c r="Y7" s="6">
         <v>3451.4139999999998</v>
       </c>
-      <c r="V7" s="6">
+      <c r="Z7" s="6">
         <v>3395.0529999999999</v>
       </c>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="6"/>
       <c r="AA7" s="6"/>
       <c r="AB7" s="6"/>
       <c r="AC7" s="6"/>
@@ -1347,8 +1421,12 @@
       <c r="BT7" s="6"/>
       <c r="BU7" s="6"/>
       <c r="BV7" s="6"/>
-    </row>
-    <row r="8" spans="1:91" x14ac:dyDescent="0.2">
+      <c r="BW7" s="6"/>
+      <c r="BX7" s="6"/>
+      <c r="BY7" s="6"/>
+      <c r="BZ7" s="6"/>
+    </row>
+    <row r="8" spans="1:95" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>32</v>
       </c>
@@ -1385,25 +1463,30 @@
       <c r="M8" s="6">
         <v>265.13499999999999</v>
       </c>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
+      <c r="N8" s="6">
+        <f t="shared" si="0"/>
+        <v>281.76700000000005</v>
+      </c>
+      <c r="O8" s="6">
+        <v>245.262</v>
+      </c>
       <c r="P8" s="6"/>
       <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
       <c r="S8" s="6"/>
-      <c r="T8" s="6">
+      <c r="T8" s="6"/>
+      <c r="U8" s="6"/>
+      <c r="V8" s="6"/>
+      <c r="W8" s="6"/>
+      <c r="X8" s="6">
         <v>1383.6100000000001</v>
       </c>
-      <c r="U8" s="6">
+      <c r="Y8" s="6">
         <v>1206.202</v>
       </c>
-      <c r="V8" s="6">
+      <c r="Z8" s="6">
         <v>1076.383</v>
       </c>
-      <c r="W8" s="6"/>
-      <c r="X8" s="6"/>
-      <c r="Y8" s="6"/>
-      <c r="Z8" s="6"/>
       <c r="AA8" s="6"/>
       <c r="AB8" s="6"/>
       <c r="AC8" s="6"/>
@@ -1452,8 +1535,12 @@
       <c r="BT8" s="6"/>
       <c r="BU8" s="6"/>
       <c r="BV8" s="6"/>
-    </row>
-    <row r="9" spans="1:91" x14ac:dyDescent="0.2">
+      <c r="BW8" s="6"/>
+      <c r="BX8" s="6"/>
+      <c r="BY8" s="6"/>
+      <c r="BZ8" s="6"/>
+    </row>
+    <row r="9" spans="1:95" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>53</v>
       </c>
@@ -1490,25 +1577,30 @@
       <c r="M9" s="6">
         <v>107.66</v>
       </c>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
+      <c r="N9" s="6">
+        <f t="shared" si="0"/>
+        <v>93.65100000000001</v>
+      </c>
+      <c r="O9" s="6">
+        <v>95.694000000000003</v>
+      </c>
       <c r="P9" s="6"/>
       <c r="Q9" s="6"/>
       <c r="R9" s="6"/>
       <c r="S9" s="6"/>
-      <c r="T9" s="6">
+      <c r="T9" s="6"/>
+      <c r="U9" s="6"/>
+      <c r="V9" s="6"/>
+      <c r="W9" s="6"/>
+      <c r="X9" s="6">
         <v>405.71500000000003</v>
       </c>
-      <c r="U9" s="6">
+      <c r="Y9" s="6">
         <v>410.86</v>
       </c>
-      <c r="V9" s="6">
+      <c r="Z9" s="6">
         <v>414.46600000000001</v>
       </c>
-      <c r="W9" s="6"/>
-      <c r="X9" s="6"/>
-      <c r="Y9" s="6"/>
-      <c r="Z9" s="6"/>
       <c r="AA9" s="6"/>
       <c r="AB9" s="6"/>
       <c r="AC9" s="6"/>
@@ -1557,8 +1649,12 @@
       <c r="BT9" s="6"/>
       <c r="BU9" s="6"/>
       <c r="BV9" s="6"/>
-    </row>
-    <row r="10" spans="1:91" x14ac:dyDescent="0.2">
+      <c r="BW9" s="6"/>
+      <c r="BX9" s="6"/>
+      <c r="BY9" s="6"/>
+      <c r="BZ9" s="6"/>
+    </row>
+    <row r="10" spans="1:95" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>35</v>
       </c>
@@ -1595,25 +1691,30 @@
       <c r="M10" s="6">
         <v>659.96500000000003</v>
       </c>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
+      <c r="N10" s="6">
+        <f t="shared" si="0"/>
+        <v>747.72199999999975</v>
+      </c>
+      <c r="O10" s="6">
+        <v>638.46799999999996</v>
+      </c>
       <c r="P10" s="6"/>
       <c r="Q10" s="6"/>
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
-      <c r="T10" s="6">
+      <c r="T10" s="6"/>
+      <c r="U10" s="6"/>
+      <c r="V10" s="6"/>
+      <c r="W10" s="6"/>
+      <c r="X10" s="6">
         <v>3243.1869999999999</v>
       </c>
-      <c r="U10" s="6">
+      <c r="Y10" s="6">
         <v>2978.8690000000001</v>
       </c>
-      <c r="V10" s="6">
+      <c r="Z10" s="6">
         <v>2831.7869999999998</v>
       </c>
-      <c r="W10" s="6"/>
-      <c r="X10" s="6"/>
-      <c r="Y10" s="6"/>
-      <c r="Z10" s="6"/>
       <c r="AA10" s="6"/>
       <c r="AB10" s="6"/>
       <c r="AC10" s="6"/>
@@ -1662,8 +1763,12 @@
       <c r="BT10" s="6"/>
       <c r="BU10" s="6"/>
       <c r="BV10" s="6"/>
-    </row>
-    <row r="11" spans="1:91" x14ac:dyDescent="0.2">
+      <c r="BW10" s="6"/>
+      <c r="BX10" s="6"/>
+      <c r="BY10" s="6"/>
+      <c r="BZ10" s="6"/>
+    </row>
+    <row r="11" spans="1:95" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>33</v>
       </c>
@@ -1700,25 +1805,30 @@
       <c r="M11" s="6">
         <v>646.84500000000003</v>
       </c>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
+      <c r="N11" s="6">
+        <f t="shared" si="0"/>
+        <v>405.55899999999974</v>
+      </c>
+      <c r="O11" s="6">
+        <v>436.52300000000002</v>
+      </c>
       <c r="P11" s="6"/>
       <c r="Q11" s="6"/>
       <c r="R11" s="6"/>
       <c r="S11" s="6"/>
-      <c r="T11" s="6">
+      <c r="T11" s="6"/>
+      <c r="U11" s="6"/>
+      <c r="V11" s="6"/>
+      <c r="W11" s="6"/>
+      <c r="X11" s="6">
         <v>2335.154</v>
       </c>
-      <c r="U11" s="6">
+      <c r="Y11" s="6">
         <v>2089.607</v>
       </c>
-      <c r="V11" s="6">
+      <c r="Z11" s="6">
         <v>2054.1149999999998</v>
       </c>
-      <c r="W11" s="6"/>
-      <c r="X11" s="6"/>
-      <c r="Y11" s="6"/>
-      <c r="Z11" s="6"/>
       <c r="AA11" s="6"/>
       <c r="AB11" s="6"/>
       <c r="AC11" s="6"/>
@@ -1767,8 +1877,12 @@
       <c r="BT11" s="6"/>
       <c r="BU11" s="6"/>
       <c r="BV11" s="6"/>
-    </row>
-    <row r="12" spans="1:91" x14ac:dyDescent="0.2">
+      <c r="BW11" s="6"/>
+      <c r="BX11" s="6"/>
+      <c r="BY11" s="6"/>
+      <c r="BZ11" s="6"/>
+    </row>
+    <row r="12" spans="1:95" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>34</v>
       </c>
@@ -1805,25 +1919,30 @@
       <c r="M12" s="6">
         <v>27.155000000000001</v>
       </c>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
+      <c r="N12" s="6">
+        <f t="shared" si="0"/>
+        <v>26.85199999999999</v>
+      </c>
+      <c r="O12" s="6">
+        <v>24.806000000000001</v>
+      </c>
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
       <c r="R12" s="6"/>
       <c r="S12" s="6"/>
-      <c r="T12" s="6">
+      <c r="T12" s="6"/>
+      <c r="U12" s="6"/>
+      <c r="V12" s="6"/>
+      <c r="W12" s="6"/>
+      <c r="X12" s="6">
         <v>111.24100000000001</v>
       </c>
-      <c r="U12" s="6">
+      <c r="Y12" s="6">
         <v>97.580999999999989</v>
       </c>
-      <c r="V12" s="6">
+      <c r="Z12" s="6">
         <v>107.35299999999999</v>
       </c>
-      <c r="W12" s="6"/>
-      <c r="X12" s="6"/>
-      <c r="Y12" s="6"/>
-      <c r="Z12" s="6"/>
       <c r="AA12" s="6"/>
       <c r="AB12" s="6"/>
       <c r="AC12" s="6"/>
@@ -1872,8 +1991,12 @@
       <c r="BT12" s="6"/>
       <c r="BU12" s="6"/>
       <c r="BV12" s="6"/>
-    </row>
-    <row r="13" spans="1:91" x14ac:dyDescent="0.2">
+      <c r="BW12" s="6"/>
+      <c r="BX12" s="6"/>
+      <c r="BY12" s="6"/>
+      <c r="BZ12" s="6"/>
+    </row>
+    <row r="13" spans="1:95" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>36</v>
       </c>
@@ -1910,25 +2033,30 @@
       <c r="M13" s="6">
         <v>-6.2039999999999997</v>
       </c>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
+      <c r="N13" s="6">
+        <f t="shared" si="0"/>
+        <v>-9.0720000000000027</v>
+      </c>
+      <c r="O13" s="6">
+        <v>-1.87</v>
+      </c>
       <c r="P13" s="6"/>
       <c r="Q13" s="6"/>
       <c r="R13" s="6"/>
       <c r="S13" s="6"/>
-      <c r="T13" s="6">
+      <c r="T13" s="6"/>
+      <c r="U13" s="6"/>
+      <c r="V13" s="6"/>
+      <c r="W13" s="6"/>
+      <c r="X13" s="6">
         <v>12.296999999999999</v>
       </c>
-      <c r="U13" s="6">
+      <c r="Y13" s="6">
         <v>1.244</v>
       </c>
-      <c r="V13" s="6">
+      <c r="Z13" s="6">
         <v>-26.885000000000002</v>
       </c>
-      <c r="W13" s="6"/>
-      <c r="X13" s="6"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="6"/>
       <c r="AA13" s="6"/>
       <c r="AB13" s="6"/>
       <c r="AC13" s="6"/>
@@ -1977,8 +2105,12 @@
       <c r="BT13" s="6"/>
       <c r="BU13" s="6"/>
       <c r="BV13" s="6"/>
-    </row>
-    <row r="14" spans="1:91" x14ac:dyDescent="0.2">
+      <c r="BW13" s="6"/>
+      <c r="BX13" s="6"/>
+      <c r="BY13" s="6"/>
+      <c r="BZ13" s="6"/>
+    </row>
+    <row r="14" spans="1:95" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
         <v>19</v>
       </c>
@@ -2015,26 +2147,31 @@
       <c r="M14" s="7">
         <v>1327.761</v>
       </c>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
+      <c r="N14" s="7">
+        <f t="shared" si="0"/>
+        <v>1171.1609999999996</v>
+      </c>
+      <c r="O14" s="7">
+        <v>1097.9269999999999</v>
+      </c>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
       <c r="R14" s="7"/>
       <c r="S14" s="7"/>
-      <c r="T14" s="7">
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
+      <c r="X14" s="7">
         <v>5701.8789999999999</v>
       </c>
-      <c r="U14" s="7">
+      <c r="Y14" s="7">
         <v>5164.3099999999995</v>
       </c>
-      <c r="V14" s="7">
+      <c r="Z14" s="7">
         <v>4966.37</v>
       </c>
-      <c r="W14" s="7"/>
-      <c r="X14" s="6"/>
-      <c r="Y14" s="6"/>
-      <c r="Z14" s="6"/>
-      <c r="AA14" s="6"/>
+      <c r="AA14" s="7"/>
       <c r="AB14" s="6"/>
       <c r="AC14" s="6"/>
       <c r="AD14" s="6"/>
@@ -2082,10 +2219,10 @@
       <c r="BT14" s="6"/>
       <c r="BU14" s="6"/>
       <c r="BV14" s="6"/>
-      <c r="BW14" s="3"/>
-      <c r="BX14" s="3"/>
-      <c r="BY14" s="3"/>
-      <c r="BZ14" s="3"/>
+      <c r="BW14" s="6"/>
+      <c r="BX14" s="6"/>
+      <c r="BY14" s="6"/>
+      <c r="BZ14" s="6"/>
       <c r="CA14" s="3"/>
       <c r="CB14" s="3"/>
       <c r="CC14" s="3"/>
@@ -2099,8 +2236,12 @@
       <c r="CK14" s="3"/>
       <c r="CL14" s="3"/>
       <c r="CM14" s="3"/>
-    </row>
-    <row r="15" spans="1:91" x14ac:dyDescent="0.2">
+      <c r="CN14" s="3"/>
+      <c r="CO14" s="3"/>
+      <c r="CP14" s="3"/>
+      <c r="CQ14" s="3"/>
+    </row>
+    <row r="15" spans="1:95" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>20</v>
       </c>
@@ -2137,25 +2278,30 @@
       <c r="M15" s="6">
         <v>738.02099999999996</v>
       </c>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
+      <c r="N15" s="6">
+        <f t="shared" si="0"/>
+        <v>679.12300000000027</v>
+      </c>
+      <c r="O15" s="6">
+        <v>504.09500000000003</v>
+      </c>
       <c r="P15" s="6"/>
       <c r="Q15" s="6"/>
       <c r="R15" s="6"/>
       <c r="S15" s="6"/>
-      <c r="T15" s="6">
+      <c r="T15" s="6"/>
+      <c r="U15" s="6"/>
+      <c r="V15" s="6"/>
+      <c r="W15" s="6"/>
+      <c r="X15" s="6">
         <v>3071.6260000000002</v>
       </c>
-      <c r="U15" s="6">
+      <c r="Y15" s="6">
         <v>2689.5659999999998</v>
       </c>
-      <c r="V15" s="6">
+      <c r="Z15" s="6">
         <v>2707.5120000000002</v>
       </c>
-      <c r="W15" s="6"/>
-      <c r="X15" s="6"/>
-      <c r="Y15" s="6"/>
-      <c r="Z15" s="6"/>
       <c r="AA15" s="6"/>
       <c r="AB15" s="6"/>
       <c r="AC15" s="6"/>
@@ -2204,10 +2350,10 @@
       <c r="BT15" s="6"/>
       <c r="BU15" s="6"/>
       <c r="BV15" s="6"/>
-      <c r="BW15" s="3"/>
-      <c r="BX15" s="3"/>
-      <c r="BY15" s="3"/>
-      <c r="BZ15" s="3"/>
+      <c r="BW15" s="6"/>
+      <c r="BX15" s="6"/>
+      <c r="BY15" s="6"/>
+      <c r="BZ15" s="6"/>
       <c r="CA15" s="3"/>
       <c r="CB15" s="3"/>
       <c r="CC15" s="3"/>
@@ -2221,29 +2367,33 @@
       <c r="CK15" s="3"/>
       <c r="CL15" s="3"/>
       <c r="CM15" s="3"/>
-    </row>
-    <row r="16" spans="1:91" x14ac:dyDescent="0.2">
+      <c r="CN15" s="3"/>
+      <c r="CO15" s="3"/>
+      <c r="CP15" s="3"/>
+      <c r="CQ15" s="3"/>
+    </row>
+    <row r="16" spans="1:95" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="6">
-        <f t="shared" ref="C16:G16" si="0">+C14-C15</f>
+        <f t="shared" ref="C16:G16" si="1">+C14-C15</f>
         <v>611.49499999999989</v>
       </c>
       <c r="D16" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>748.52300000000002</v>
       </c>
       <c r="E16" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>670.6389999999999</v>
       </c>
       <c r="F16" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>599.59599999999989</v>
       </c>
       <c r="G16" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>562.67499999999995</v>
       </c>
       <c r="H16" s="6">
@@ -2251,50 +2401,53 @@
         <v>696.13199999999995</v>
       </c>
       <c r="I16" s="6">
-        <f t="shared" ref="I16:N16" si="1">+I14-I15</f>
+        <f t="shared" ref="I16:O16" si="2">+I14-I15</f>
         <v>665.15499999999997</v>
       </c>
       <c r="J16" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>550.78200000000004</v>
       </c>
       <c r="K16" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>546.49599999999998</v>
       </c>
       <c r="L16" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>630.58400000000006</v>
       </c>
       <c r="M16" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>589.74</v>
       </c>
       <c r="N16" s="6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O16" s="6"/>
+        <f t="shared" si="2"/>
+        <v>492.03799999999933</v>
+      </c>
+      <c r="O16" s="6">
+        <f t="shared" si="2"/>
+        <v>593.83199999999988</v>
+      </c>
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
       <c r="S16" s="6"/>
-      <c r="T16" s="6">
-        <f>+T14-T15</f>
+      <c r="T16" s="6"/>
+      <c r="U16" s="6"/>
+      <c r="V16" s="6"/>
+      <c r="W16" s="6"/>
+      <c r="X16" s="6">
+        <f>+X14-X15</f>
         <v>2630.2529999999997</v>
       </c>
-      <c r="U16" s="6">
-        <f>+U14-U15</f>
+      <c r="Y16" s="6">
+        <f>+Y14-Y15</f>
         <v>2474.7439999999997</v>
       </c>
-      <c r="V16" s="6">
-        <f>+V14-V15</f>
+      <c r="Z16" s="6">
+        <f>+Z14-Z15</f>
         <v>2258.8579999999997</v>
       </c>
-      <c r="W16" s="6"/>
-      <c r="X16" s="6"/>
-      <c r="Y16" s="6"/>
-      <c r="Z16" s="6"/>
       <c r="AA16" s="6"/>
       <c r="AB16" s="6"/>
       <c r="AC16" s="6"/>
@@ -2343,10 +2496,10 @@
       <c r="BT16" s="6"/>
       <c r="BU16" s="6"/>
       <c r="BV16" s="6"/>
-      <c r="BW16" s="3"/>
-      <c r="BX16" s="3"/>
-      <c r="BY16" s="3"/>
-      <c r="BZ16" s="3"/>
+      <c r="BW16" s="6"/>
+      <c r="BX16" s="6"/>
+      <c r="BY16" s="6"/>
+      <c r="BZ16" s="6"/>
       <c r="CA16" s="3"/>
       <c r="CB16" s="3"/>
       <c r="CC16" s="3"/>
@@ -2360,8 +2513,12 @@
       <c r="CK16" s="3"/>
       <c r="CL16" s="3"/>
       <c r="CM16" s="3"/>
-    </row>
-    <row r="17" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN16" s="3"/>
+      <c r="CO16" s="3"/>
+      <c r="CP16" s="3"/>
+      <c r="CQ16" s="3"/>
+    </row>
+    <row r="17" spans="2:95" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>22</v>
       </c>
@@ -2398,25 +2555,30 @@
       <c r="M17" s="6">
         <v>664.54</v>
       </c>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
+      <c r="N17" s="6">
+        <f t="shared" si="0"/>
+        <v>517.73400000000038</v>
+      </c>
+      <c r="O17" s="6">
+        <v>543.08500000000004</v>
+      </c>
       <c r="P17" s="6"/>
       <c r="Q17" s="6"/>
       <c r="R17" s="6"/>
       <c r="S17" s="6"/>
-      <c r="T17" s="6">
+      <c r="T17" s="6"/>
+      <c r="U17" s="6"/>
+      <c r="V17" s="6"/>
+      <c r="W17" s="6"/>
+      <c r="X17" s="6">
         <v>2400.502</v>
       </c>
-      <c r="U17" s="6">
+      <c r="Y17" s="6">
         <v>2601.991</v>
       </c>
-      <c r="V17" s="6">
+      <c r="Z17" s="6">
         <v>2294.2510000000002</v>
       </c>
-      <c r="W17" s="6"/>
-      <c r="X17" s="6"/>
-      <c r="Y17" s="6"/>
-      <c r="Z17" s="6"/>
       <c r="AA17" s="6"/>
       <c r="AB17" s="6"/>
       <c r="AC17" s="6"/>
@@ -2465,10 +2627,10 @@
       <c r="BT17" s="6"/>
       <c r="BU17" s="6"/>
       <c r="BV17" s="6"/>
-      <c r="BW17" s="3"/>
-      <c r="BX17" s="3"/>
-      <c r="BY17" s="3"/>
-      <c r="BZ17" s="3"/>
+      <c r="BW17" s="6"/>
+      <c r="BX17" s="6"/>
+      <c r="BY17" s="6"/>
+      <c r="BZ17" s="6"/>
       <c r="CA17" s="3"/>
       <c r="CB17" s="3"/>
       <c r="CC17" s="3"/>
@@ -2482,8 +2644,12 @@
       <c r="CK17" s="3"/>
       <c r="CL17" s="3"/>
       <c r="CM17" s="3"/>
-    </row>
-    <row r="18" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN17" s="3"/>
+      <c r="CO17" s="3"/>
+      <c r="CP17" s="3"/>
+      <c r="CQ17" s="3"/>
+    </row>
+    <row r="18" spans="2:95" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>23</v>
       </c>
@@ -2520,25 +2686,30 @@
       <c r="M18" s="6">
         <v>74.98</v>
       </c>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
+      <c r="N18" s="6">
+        <f t="shared" si="0"/>
+        <v>8.0049999999999955</v>
+      </c>
+      <c r="O18" s="6">
+        <v>4.008</v>
+      </c>
       <c r="P18" s="6"/>
       <c r="Q18" s="6"/>
       <c r="R18" s="6"/>
       <c r="S18" s="6"/>
-      <c r="T18" s="6">
+      <c r="T18" s="6"/>
+      <c r="U18" s="6"/>
+      <c r="V18" s="6"/>
+      <c r="W18" s="6"/>
+      <c r="X18" s="6">
         <v>0</v>
       </c>
-      <c r="U18" s="6">
+      <c r="Y18" s="6">
         <v>57.968999999999994</v>
       </c>
-      <c r="V18" s="6">
+      <c r="Z18" s="6">
         <v>127.71899999999999</v>
       </c>
-      <c r="W18" s="6"/>
-      <c r="X18" s="6"/>
-      <c r="Y18" s="6"/>
-      <c r="Z18" s="6"/>
       <c r="AA18" s="6"/>
       <c r="AB18" s="6"/>
       <c r="AC18" s="6"/>
@@ -2587,10 +2758,10 @@
       <c r="BT18" s="6"/>
       <c r="BU18" s="6"/>
       <c r="BV18" s="6"/>
-      <c r="BW18" s="3"/>
-      <c r="BX18" s="3"/>
-      <c r="BY18" s="3"/>
-      <c r="BZ18" s="3"/>
+      <c r="BW18" s="6"/>
+      <c r="BX18" s="6"/>
+      <c r="BY18" s="6"/>
+      <c r="BZ18" s="6"/>
       <c r="CA18" s="3"/>
       <c r="CB18" s="3"/>
       <c r="CC18" s="3"/>
@@ -2604,29 +2775,33 @@
       <c r="CK18" s="3"/>
       <c r="CL18" s="3"/>
       <c r="CM18" s="3"/>
-    </row>
-    <row r="19" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN18" s="3"/>
+      <c r="CO18" s="3"/>
+      <c r="CP18" s="3"/>
+      <c r="CQ18" s="3"/>
+    </row>
+    <row r="19" spans="2:95" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="6">
-        <f t="shared" ref="C19:G19" si="2">+C16-C17-C18</f>
+        <f t="shared" ref="C19:G19" si="3">+C16-C17-C18</f>
         <v>22.422999999999888</v>
       </c>
       <c r="D19" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>139.47300000000007</v>
       </c>
       <c r="E19" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>71.408999999999878</v>
       </c>
       <c r="F19" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-3.5540000000000873</v>
       </c>
       <c r="G19" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-299.72800000000007</v>
       </c>
       <c r="H19" s="6">
@@ -2634,50 +2809,53 @@
         <v>173.07999999999993</v>
       </c>
       <c r="I19" s="6">
-        <f t="shared" ref="I19:N19" si="3">+I16-I17-I18</f>
+        <f t="shared" ref="I19:O19" si="4">+I16-I17-I18</f>
         <v>13.508999999999951</v>
       </c>
       <c r="J19" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-72.076999999999998</v>
       </c>
       <c r="K19" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.3229999999999542</v>
       </c>
       <c r="L19" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>17.046000000000113</v>
       </c>
       <c r="M19" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-149.77999999999997</v>
       </c>
       <c r="N19" s="6">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O19" s="6"/>
+        <f t="shared" si="4"/>
+        <v>-33.701000000001045</v>
+      </c>
+      <c r="O19" s="6">
+        <f t="shared" si="4"/>
+        <v>46.738999999999841</v>
+      </c>
       <c r="P19" s="6"/>
       <c r="Q19" s="6"/>
       <c r="R19" s="6"/>
       <c r="S19" s="6"/>
-      <c r="T19" s="6">
-        <f t="shared" ref="T19:V19" si="4">+T16-T17-T18</f>
+      <c r="T19" s="6"/>
+      <c r="U19" s="6"/>
+      <c r="V19" s="6"/>
+      <c r="W19" s="6"/>
+      <c r="X19" s="6">
+        <f t="shared" ref="X19:Z19" si="5">+X16-X17-X18</f>
         <v>229.75099999999975</v>
       </c>
-      <c r="U19" s="6">
-        <f t="shared" si="4"/>
+      <c r="Y19" s="6">
+        <f t="shared" si="5"/>
         <v>-185.21600000000029</v>
       </c>
-      <c r="V19" s="6">
-        <f t="shared" si="4"/>
+      <c r="Z19" s="6">
+        <f t="shared" si="5"/>
         <v>-163.11200000000048</v>
       </c>
-      <c r="W19" s="6"/>
-      <c r="X19" s="6"/>
-      <c r="Y19" s="6"/>
-      <c r="Z19" s="6"/>
       <c r="AA19" s="6"/>
       <c r="AB19" s="6"/>
       <c r="AC19" s="6"/>
@@ -2726,10 +2904,10 @@
       <c r="BT19" s="6"/>
       <c r="BU19" s="6"/>
       <c r="BV19" s="6"/>
-      <c r="BW19" s="3"/>
-      <c r="BX19" s="3"/>
-      <c r="BY19" s="3"/>
-      <c r="BZ19" s="3"/>
+      <c r="BW19" s="6"/>
+      <c r="BX19" s="6"/>
+      <c r="BY19" s="6"/>
+      <c r="BZ19" s="6"/>
       <c r="CA19" s="3"/>
       <c r="CB19" s="3"/>
       <c r="CC19" s="3"/>
@@ -2743,8 +2921,12 @@
       <c r="CK19" s="3"/>
       <c r="CL19" s="3"/>
       <c r="CM19" s="3"/>
-    </row>
-    <row r="20" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN19" s="3"/>
+      <c r="CO19" s="3"/>
+      <c r="CP19" s="3"/>
+      <c r="CQ19" s="3"/>
+    </row>
+    <row r="20" spans="2:95" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>25</v>
       </c>
@@ -2781,25 +2963,30 @@
       <c r="M20" s="6">
         <v>-8.8919999999999995</v>
       </c>
-      <c r="N20" s="6"/>
-      <c r="O20" s="6"/>
+      <c r="N20" s="6">
+        <f t="shared" si="0"/>
+        <v>-8.7399999999999984</v>
+      </c>
+      <c r="O20" s="6">
+        <v>-10.645</v>
+      </c>
       <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
       <c r="R20" s="6"/>
       <c r="S20" s="6"/>
-      <c r="T20" s="6">
+      <c r="T20" s="6"/>
+      <c r="U20" s="6"/>
+      <c r="V20" s="6"/>
+      <c r="W20" s="6"/>
+      <c r="X20" s="6">
         <v>0.26800000000000024</v>
       </c>
-      <c r="U20" s="6">
+      <c r="Y20" s="6">
         <v>-6.1150000000000002</v>
       </c>
-      <c r="V20" s="6">
+      <c r="Z20" s="6">
         <v>-30.288</v>
       </c>
-      <c r="W20" s="6"/>
-      <c r="X20" s="6"/>
-      <c r="Y20" s="6"/>
-      <c r="Z20" s="6"/>
       <c r="AA20" s="6"/>
       <c r="AB20" s="6"/>
       <c r="AC20" s="6"/>
@@ -2848,10 +3035,10 @@
       <c r="BT20" s="6"/>
       <c r="BU20" s="6"/>
       <c r="BV20" s="6"/>
-      <c r="BW20" s="3"/>
-      <c r="BX20" s="3"/>
-      <c r="BY20" s="3"/>
-      <c r="BZ20" s="3"/>
+      <c r="BW20" s="6"/>
+      <c r="BX20" s="6"/>
+      <c r="BY20" s="6"/>
+      <c r="BZ20" s="6"/>
       <c r="CA20" s="3"/>
       <c r="CB20" s="3"/>
       <c r="CC20" s="3"/>
@@ -2865,8 +3052,12 @@
       <c r="CK20" s="3"/>
       <c r="CL20" s="3"/>
       <c r="CM20" s="3"/>
-    </row>
-    <row r="21" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN20" s="3"/>
+      <c r="CO20" s="3"/>
+      <c r="CP20" s="3"/>
+      <c r="CQ20" s="3"/>
+    </row>
+    <row r="21" spans="2:95" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>26</v>
       </c>
@@ -2903,25 +3094,30 @@
       <c r="M21" s="6">
         <v>-1.5840000000000001</v>
       </c>
-      <c r="N21" s="6"/>
-      <c r="O21" s="6"/>
+      <c r="N21" s="6">
+        <f t="shared" si="0"/>
+        <v>-5.4999999999999716E-2</v>
+      </c>
+      <c r="O21" s="6">
+        <v>-7.0129999999999999</v>
+      </c>
       <c r="P21" s="6"/>
       <c r="Q21" s="6"/>
       <c r="R21" s="6"/>
       <c r="S21" s="6"/>
-      <c r="T21" s="6">
+      <c r="T21" s="6"/>
+      <c r="U21" s="6"/>
+      <c r="V21" s="6"/>
+      <c r="W21" s="6"/>
+      <c r="X21" s="6">
         <v>32.019000000000005</v>
       </c>
-      <c r="U21" s="6">
+      <c r="Y21" s="6">
         <v>-13.431000000000001</v>
       </c>
-      <c r="V21" s="6">
+      <c r="Z21" s="6">
         <v>-7.2759999999999998</v>
       </c>
-      <c r="W21" s="6"/>
-      <c r="X21" s="6"/>
-      <c r="Y21" s="6"/>
-      <c r="Z21" s="6"/>
       <c r="AA21" s="6"/>
       <c r="AB21" s="6"/>
       <c r="AC21" s="6"/>
@@ -2970,10 +3166,10 @@
       <c r="BT21" s="6"/>
       <c r="BU21" s="6"/>
       <c r="BV21" s="6"/>
-      <c r="BW21" s="3"/>
-      <c r="BX21" s="3"/>
-      <c r="BY21" s="3"/>
-      <c r="BZ21" s="3"/>
+      <c r="BW21" s="6"/>
+      <c r="BX21" s="6"/>
+      <c r="BY21" s="6"/>
+      <c r="BZ21" s="6"/>
       <c r="CA21" s="3"/>
       <c r="CB21" s="3"/>
       <c r="CC21" s="3"/>
@@ -2987,29 +3183,33 @@
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
       <c r="CM21" s="3"/>
-    </row>
-    <row r="22" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN21" s="3"/>
+      <c r="CO21" s="3"/>
+      <c r="CP21" s="3"/>
+      <c r="CQ21" s="3"/>
+    </row>
+    <row r="22" spans="2:95" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C22" s="6">
-        <f t="shared" ref="C22:G22" si="5">+C19+SUM(C20:C21)</f>
+        <f t="shared" ref="C22:G22" si="6">+C19+SUM(C20:C21)</f>
         <v>14.736999999999888</v>
       </c>
       <c r="D22" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>132.96000000000006</v>
       </c>
       <c r="E22" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>119.12499999999989</v>
       </c>
       <c r="F22" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-4.7840000000000877</v>
       </c>
       <c r="G22" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-300.11400000000009</v>
       </c>
       <c r="H22" s="6">
@@ -3017,50 +3217,53 @@
         <v>167.91299999999993</v>
       </c>
       <c r="I22" s="6">
-        <f t="shared" ref="I22:N22" si="6">+I19+SUM(I20:I21)</f>
+        <f t="shared" ref="I22:O22" si="7">+I19+SUM(I20:I21)</f>
         <v>7.55499999999995</v>
       </c>
       <c r="J22" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-80.116</v>
       </c>
       <c r="K22" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-5.4230000000000462</v>
       </c>
       <c r="L22" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.4990000000001125</v>
       </c>
       <c r="M22" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>-160.25599999999997</v>
       </c>
       <c r="N22" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O22" s="6"/>
+        <f t="shared" si="7"/>
+        <v>-42.496000000001047</v>
+      </c>
+      <c r="O22" s="6">
+        <f t="shared" si="7"/>
+        <v>29.08099999999984</v>
+      </c>
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
       <c r="S22" s="6"/>
-      <c r="T22" s="6">
-        <f t="shared" ref="T22:V22" si="7">+T19+SUM(T20:T21)</f>
+      <c r="T22" s="6"/>
+      <c r="U22" s="6"/>
+      <c r="V22" s="6"/>
+      <c r="W22" s="6"/>
+      <c r="X22" s="6">
+        <f t="shared" ref="X22:Z22" si="8">+X19+SUM(X20:X21)</f>
         <v>262.03799999999978</v>
       </c>
-      <c r="U22" s="6">
-        <f t="shared" si="7"/>
+      <c r="Y22" s="6">
+        <f t="shared" si="8"/>
         <v>-204.76200000000028</v>
       </c>
-      <c r="V22" s="6">
-        <f t="shared" si="7"/>
+      <c r="Z22" s="6">
+        <f t="shared" si="8"/>
         <v>-200.67600000000047</v>
       </c>
-      <c r="W22" s="6"/>
-      <c r="X22" s="6"/>
-      <c r="Y22" s="6"/>
-      <c r="Z22" s="6"/>
       <c r="AA22" s="6"/>
       <c r="AB22" s="6"/>
       <c r="AC22" s="6"/>
@@ -3109,10 +3312,10 @@
       <c r="BT22" s="6"/>
       <c r="BU22" s="6"/>
       <c r="BV22" s="6"/>
-      <c r="BW22" s="3"/>
-      <c r="BX22" s="3"/>
-      <c r="BY22" s="3"/>
-      <c r="BZ22" s="3"/>
+      <c r="BW22" s="6"/>
+      <c r="BX22" s="6"/>
+      <c r="BY22" s="6"/>
+      <c r="BZ22" s="6"/>
       <c r="CA22" s="3"/>
       <c r="CB22" s="3"/>
       <c r="CC22" s="3"/>
@@ -3126,8 +3329,12 @@
       <c r="CK22" s="3"/>
       <c r="CL22" s="3"/>
       <c r="CM22" s="3"/>
-    </row>
-    <row r="23" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN22" s="3"/>
+      <c r="CO22" s="3"/>
+      <c r="CP22" s="3"/>
+      <c r="CQ22" s="3"/>
+    </row>
+    <row r="23" spans="2:95" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>28</v>
       </c>
@@ -3164,25 +3371,30 @@
       <c r="M23" s="6">
         <v>270.60399999999998</v>
       </c>
-      <c r="N23" s="6"/>
-      <c r="O23" s="6"/>
+      <c r="N23" s="6">
+        <f t="shared" si="0"/>
+        <v>0.86600000000004229</v>
+      </c>
+      <c r="O23" s="6">
+        <v>28.314</v>
+      </c>
       <c r="P23" s="6"/>
       <c r="Q23" s="6"/>
       <c r="R23" s="6"/>
       <c r="S23" s="6"/>
-      <c r="T23" s="6">
+      <c r="T23" s="6"/>
+      <c r="U23" s="6"/>
+      <c r="V23" s="6"/>
+      <c r="W23" s="6"/>
+      <c r="X23" s="6">
         <v>30.006000000000007</v>
       </c>
-      <c r="U23" s="6">
+      <c r="Y23" s="6">
         <v>-2.8900000000000006</v>
       </c>
-      <c r="V23" s="6">
+      <c r="Z23" s="6">
         <v>294.75200000000001</v>
       </c>
-      <c r="W23" s="6"/>
-      <c r="X23" s="6"/>
-      <c r="Y23" s="6"/>
-      <c r="Z23" s="6"/>
       <c r="AA23" s="6"/>
       <c r="AB23" s="6"/>
       <c r="AC23" s="6"/>
@@ -3231,10 +3443,10 @@
       <c r="BT23" s="6"/>
       <c r="BU23" s="6"/>
       <c r="BV23" s="6"/>
-      <c r="BW23" s="3"/>
-      <c r="BX23" s="3"/>
-      <c r="BY23" s="3"/>
-      <c r="BZ23" s="3"/>
+      <c r="BW23" s="6"/>
+      <c r="BX23" s="6"/>
+      <c r="BY23" s="6"/>
+      <c r="BZ23" s="6"/>
       <c r="CA23" s="3"/>
       <c r="CB23" s="3"/>
       <c r="CC23" s="3"/>
@@ -3248,8 +3460,12 @@
       <c r="CK23" s="3"/>
       <c r="CL23" s="3"/>
       <c r="CM23" s="3"/>
-    </row>
-    <row r="24" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN23" s="3"/>
+      <c r="CO23" s="3"/>
+      <c r="CP23" s="3"/>
+      <c r="CQ23" s="3"/>
+    </row>
+    <row r="24" spans="2:95" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>29</v>
       </c>
@@ -3286,25 +3502,30 @@
       <c r="M24" s="6">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="N24" s="6"/>
-      <c r="O24" s="6"/>
+      <c r="N24" s="6">
+        <f t="shared" si="0"/>
+        <v>-2.7999999999999997E-2</v>
+      </c>
+      <c r="O24" s="6">
+        <v>-0.222</v>
+      </c>
       <c r="P24" s="6"/>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="6"/>
-      <c r="T24" s="6">
+      <c r="T24" s="6"/>
+      <c r="U24" s="6"/>
+      <c r="V24" s="6"/>
+      <c r="W24" s="6"/>
+      <c r="X24" s="6">
         <v>-2.6000000000000016E-2</v>
       </c>
-      <c r="U24" s="6">
+      <c r="Y24" s="6">
         <v>0.60499999999999998</v>
       </c>
-      <c r="V24" s="6">
+      <c r="Z24" s="6">
         <v>-0.215</v>
       </c>
-      <c r="W24" s="6"/>
-      <c r="X24" s="6"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
       <c r="AA24" s="6"/>
       <c r="AB24" s="6"/>
       <c r="AC24" s="6"/>
@@ -3353,10 +3574,10 @@
       <c r="BT24" s="6"/>
       <c r="BU24" s="6"/>
       <c r="BV24" s="6"/>
-      <c r="BW24" s="3"/>
-      <c r="BX24" s="3"/>
-      <c r="BY24" s="3"/>
-      <c r="BZ24" s="3"/>
+      <c r="BW24" s="6"/>
+      <c r="BX24" s="6"/>
+      <c r="BY24" s="6"/>
+      <c r="BZ24" s="6"/>
       <c r="CA24" s="3"/>
       <c r="CB24" s="3"/>
       <c r="CC24" s="3"/>
@@ -3370,29 +3591,33 @@
       <c r="CK24" s="3"/>
       <c r="CL24" s="3"/>
       <c r="CM24" s="3"/>
-    </row>
-    <row r="25" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN24" s="3"/>
+      <c r="CO24" s="3"/>
+      <c r="CP24" s="3"/>
+      <c r="CQ24" s="3"/>
+    </row>
+    <row r="25" spans="2:95" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C25" s="6">
-        <f t="shared" ref="C25:G25" si="8">+C22-C23+C24</f>
+        <f t="shared" ref="C25:G25" si="9">+C22-C23+C24</f>
         <v>10.009999999999888</v>
       </c>
       <c r="D25" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>104.67500000000005</v>
       </c>
       <c r="E25" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>110.75299999999989</v>
       </c>
       <c r="F25" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>6.5679999999999126</v>
       </c>
       <c r="G25" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-305.4260000000001</v>
       </c>
       <c r="H25" s="6">
@@ -3400,50 +3625,53 @@
         <v>170.38199999999992</v>
       </c>
       <c r="I25" s="6">
-        <f t="shared" ref="I25:N25" si="9">+I22-I23+I24</f>
+        <f t="shared" ref="I25:O25" si="10">+I22-I23+I24</f>
         <v>1.23399999999995</v>
       </c>
       <c r="J25" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-67.457000000000008</v>
       </c>
       <c r="K25" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-2.6120000000000463</v>
       </c>
       <c r="L25" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-18.81399999999989</v>
       </c>
       <c r="M25" s="6">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>-430.82699999999994</v>
       </c>
       <c r="N25" s="6">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="O25" s="6"/>
+        <f t="shared" si="10"/>
+        <v>-43.390000000001088</v>
+      </c>
+      <c r="O25" s="6">
+        <f t="shared" si="10"/>
+        <v>0.54499999999983961</v>
+      </c>
       <c r="P25" s="6"/>
       <c r="Q25" s="6"/>
       <c r="R25" s="6"/>
       <c r="S25" s="6"/>
-      <c r="T25" s="6">
-        <f t="shared" ref="T25:V25" si="10">+T22-T23+T24</f>
+      <c r="T25" s="6"/>
+      <c r="U25" s="6"/>
+      <c r="V25" s="6"/>
+      <c r="W25" s="6"/>
+      <c r="X25" s="6">
+        <f t="shared" ref="X25:Z25" si="11">+X22-X23+X24</f>
         <v>232.00599999999977</v>
       </c>
-      <c r="U25" s="6">
-        <f t="shared" si="10"/>
+      <c r="Y25" s="6">
+        <f t="shared" si="11"/>
         <v>-201.26700000000031</v>
       </c>
-      <c r="V25" s="6">
-        <f t="shared" si="10"/>
+      <c r="Z25" s="6">
+        <f t="shared" si="11"/>
         <v>-495.64300000000043</v>
       </c>
-      <c r="W25" s="6"/>
-      <c r="X25" s="6"/>
-      <c r="Y25" s="6"/>
-      <c r="Z25" s="6"/>
       <c r="AA25" s="6"/>
       <c r="AB25" s="6"/>
       <c r="AC25" s="6"/>
@@ -3492,10 +3720,10 @@
       <c r="BT25" s="6"/>
       <c r="BU25" s="6"/>
       <c r="BV25" s="6"/>
-      <c r="BW25" s="3"/>
-      <c r="BX25" s="3"/>
-      <c r="BY25" s="3"/>
-      <c r="BZ25" s="3"/>
+      <c r="BW25" s="6"/>
+      <c r="BX25" s="6"/>
+      <c r="BY25" s="6"/>
+      <c r="BZ25" s="6"/>
       <c r="CA25" s="3"/>
       <c r="CB25" s="3"/>
       <c r="CC25" s="3"/>
@@ -3509,8 +3737,12 @@
       <c r="CK25" s="3"/>
       <c r="CL25" s="3"/>
       <c r="CM25" s="3"/>
-    </row>
-    <row r="26" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN25" s="3"/>
+      <c r="CO25" s="3"/>
+      <c r="CP25" s="3"/>
+      <c r="CQ25" s="3"/>
+    </row>
+    <row r="26" spans="2:95" x14ac:dyDescent="0.2">
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -3600,29 +3832,33 @@
       <c r="CK26" s="3"/>
       <c r="CL26" s="3"/>
       <c r="CM26" s="3"/>
-    </row>
-    <row r="27" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN26" s="3"/>
+      <c r="CO26" s="3"/>
+      <c r="CP26" s="3"/>
+      <c r="CQ26" s="3"/>
+    </row>
+    <row r="27" spans="2:95" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C27" s="8">
-        <f t="shared" ref="C27:G27" si="11">+C25/C28</f>
+        <f t="shared" ref="C27:G27" si="12">+C25/C28</f>
         <v>2.2500854178280242E-2</v>
       </c>
       <c r="D27" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.23600698945944437</v>
       </c>
       <c r="E27" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.25325738485390331</v>
       </c>
       <c r="F27" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.5078676345670649E-2</v>
       </c>
       <c r="G27" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.70101195107564296</v>
       </c>
       <c r="H27" s="8">
@@ -3630,55 +3866,58 @@
         <v>0.39419746659725818</v>
       </c>
       <c r="I27" s="8">
-        <f t="shared" ref="I27:N27" si="12">+I25/I28</f>
+        <f t="shared" ref="I27:O27" si="13">+I25/I28</f>
         <v>2.8581752149420721E-3</v>
       </c>
       <c r="J27" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-0.15713546956384003</v>
       </c>
       <c r="K27" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-6.1154346828497328E-3</v>
       </c>
       <c r="L27" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-4.3922026380296228E-2</v>
       </c>
       <c r="M27" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-1.0140804293330508</v>
       </c>
-      <c r="N27" s="8" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O27" s="8"/>
+      <c r="N27" s="8">
+        <f t="shared" si="13"/>
+        <v>-0.1021313655568527</v>
+      </c>
+      <c r="O27" s="8">
+        <f t="shared" si="13"/>
+        <v>1.2740521169131928E-3</v>
+      </c>
       <c r="P27" s="8"/>
       <c r="Q27" s="8"/>
       <c r="R27" s="8"/>
       <c r="S27" s="8"/>
-      <c r="T27" s="8">
-        <f t="shared" ref="T27" si="13">+T25/T28</f>
+      <c r="T27" s="8"/>
+      <c r="U27" s="8"/>
+      <c r="V27" s="8"/>
+      <c r="W27" s="8"/>
+      <c r="X27" s="8">
+        <f t="shared" ref="X27" si="14">+X25/X28</f>
         <v>0.52689927229597744</v>
       </c>
-      <c r="U27" s="8">
-        <f>+U25/U28</f>
+      <c r="Y27" s="8">
+        <f>+Y25/Y28</f>
         <v>-0.46563876193351661</v>
       </c>
-      <c r="V27" s="8">
-        <f>+V25/V28</f>
+      <c r="Z27" s="8">
+        <f>+Z25/Z28</f>
         <v>-1.1619129109769688</v>
       </c>
-      <c r="W27" s="8"/>
-      <c r="X27" s="8"/>
-      <c r="Y27" s="8"/>
-      <c r="Z27" s="8"/>
       <c r="AA27" s="8"/>
-      <c r="AB27" s="3"/>
-      <c r="AC27" s="3"/>
-      <c r="AD27" s="3"/>
-      <c r="AE27" s="3"/>
+      <c r="AB27" s="8"/>
+      <c r="AC27" s="8"/>
+      <c r="AD27" s="8"/>
+      <c r="AE27" s="8"/>
       <c r="AF27" s="3"/>
       <c r="AG27" s="3"/>
       <c r="AH27" s="3"/>
@@ -3739,8 +3978,12 @@
       <c r="CK27" s="3"/>
       <c r="CL27" s="3"/>
       <c r="CM27" s="3"/>
-    </row>
-    <row r="28" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN27" s="3"/>
+      <c r="CO27" s="3"/>
+      <c r="CP27" s="3"/>
+      <c r="CQ27" s="3"/>
+    </row>
+    <row r="28" spans="2:95" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>5</v>
       </c>
@@ -3777,27 +4020,31 @@
       <c r="M28" s="3">
         <v>424.84500000000003</v>
       </c>
-      <c r="N28" s="3"/>
-      <c r="O28" s="3"/>
+      <c r="N28" s="3">
+        <v>424.84500000000003</v>
+      </c>
+      <c r="O28" s="3">
+        <v>427.76900000000001</v>
+      </c>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
-      <c r="T28" s="3">
+      <c r="T28" s="3"/>
+      <c r="U28" s="3"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="3">
         <f>+AVERAGE(C28:F28)</f>
         <v>440.32325000000003</v>
       </c>
-      <c r="U28" s="3">
+      <c r="Y28" s="3">
         <f>+AVERAGE(G28:J28)</f>
         <v>432.23849999999999</v>
       </c>
-      <c r="V28" s="3">
+      <c r="Z28" s="3">
         <v>426.57499999999999</v>
       </c>
-      <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
-      <c r="Y28" s="3"/>
-      <c r="Z28" s="3"/>
       <c r="AA28" s="3"/>
       <c r="AB28" s="3"/>
       <c r="AC28" s="3"/>
@@ -3863,8 +4110,12 @@
       <c r="CK28" s="3"/>
       <c r="CL28" s="3"/>
       <c r="CM28" s="3"/>
-    </row>
-    <row r="29" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN28" s="3"/>
+      <c r="CO28" s="3"/>
+      <c r="CP28" s="3"/>
+      <c r="CQ28" s="3"/>
+    </row>
+    <row r="29" spans="2:95" x14ac:dyDescent="0.2">
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
@@ -3954,8 +4205,12 @@
       <c r="CK29" s="3"/>
       <c r="CL29" s="3"/>
       <c r="CM29" s="3"/>
-    </row>
-    <row r="30" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN29" s="3"/>
+      <c r="CO29" s="3"/>
+      <c r="CP29" s="3"/>
+      <c r="CQ29" s="3"/>
+    </row>
+    <row r="30" spans="2:95" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>51</v>
       </c>
@@ -3964,29 +4219,41 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="9">
-        <f t="shared" ref="G30:J32" si="14">+G7/C7-1</f>
+        <f t="shared" ref="G30:J32" si="15">+G7/C7-1</f>
         <v>-8.103316343545397E-2</v>
       </c>
       <c r="H30" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-0.11510919739424763</v>
       </c>
       <c r="I30" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-4.9758275914641659E-2</v>
       </c>
       <c r="J30" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-0.11053893157439421</v>
       </c>
       <c r="K30" s="9">
         <f>+K7/G7-1</f>
         <v>-1.4779781259237401E-2</v>
       </c>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
-      <c r="O30" s="3"/>
+      <c r="L30" s="9">
+        <f t="shared" ref="L30:O32" si="16">+L7/H7-1</f>
+        <v>-1.1301874601451933E-2</v>
+      </c>
+      <c r="M30" s="9">
+        <f t="shared" si="16"/>
+        <v>-3.3178823850909089E-2</v>
+      </c>
+      <c r="N30" s="9">
+        <f t="shared" si="16"/>
+        <v>-3.0793243170509355E-3</v>
+      </c>
+      <c r="O30" s="9">
+        <f t="shared" si="16"/>
+        <v>-1.6819092623548082E-2</v>
+      </c>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
@@ -4063,8 +4330,12 @@
       <c r="CK30" s="3"/>
       <c r="CL30" s="3"/>
       <c r="CM30" s="3"/>
-    </row>
-    <row r="31" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN30" s="3"/>
+      <c r="CO30" s="3"/>
+      <c r="CP30" s="3"/>
+      <c r="CQ30" s="3"/>
+    </row>
+    <row r="31" spans="2:95" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>52</v>
       </c>
@@ -4073,29 +4344,41 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-0.14650919789919437</v>
       </c>
       <c r="H31" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-0.10945837438283379</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-9.0006042296072453E-2</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-0.1654921862508808</v>
       </c>
       <c r="K31" s="9">
-        <f t="shared" ref="K31:K32" si="15">+K8/G8-1</f>
+        <f t="shared" ref="K31:K32" si="17">+K8/G8-1</f>
         <v>-0.14347802273920784</v>
       </c>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-      <c r="O31" s="3"/>
+      <c r="L31" s="9">
+        <f t="shared" si="16"/>
+        <v>-0.15709809438547129</v>
+      </c>
+      <c r="M31" s="9">
+        <f t="shared" si="16"/>
+        <v>-0.11976109532283352</v>
+      </c>
+      <c r="N31" s="9">
+        <f t="shared" si="16"/>
+        <v>-2.7674785786502287E-4</v>
+      </c>
+      <c r="O31" s="9">
+        <f t="shared" si="16"/>
+        <v>-7.7459517406104905E-2</v>
+      </c>
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
@@ -4172,8 +4455,12 @@
       <c r="CK31" s="3"/>
       <c r="CL31" s="3"/>
       <c r="CM31" s="3"/>
-    </row>
-    <row r="32" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN31" s="3"/>
+      <c r="CO31" s="3"/>
+      <c r="CP31" s="3"/>
+      <c r="CQ31" s="3"/>
+    </row>
+    <row r="32" spans="2:95" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
         <v>54</v>
       </c>
@@ -4182,29 +4469,41 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-5.4331609817906745E-2</v>
       </c>
       <c r="H32" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2.1486312130813756E-2</v>
       </c>
       <c r="I32" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>5.6664434025452071E-2</v>
       </c>
       <c r="J32" s="9">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2.339783022033326E-2</v>
       </c>
       <c r="K32" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>8.1398238694688985E-2</v>
       </c>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
-      <c r="O32" s="3"/>
+      <c r="L32" s="9">
+        <f t="shared" si="16"/>
+        <v>-2.8389513752244855E-2</v>
+      </c>
+      <c r="M32" s="9">
+        <f t="shared" si="16"/>
+        <v>-2.5101419878296172E-2</v>
+      </c>
+      <c r="N32" s="9">
+        <f t="shared" si="16"/>
+        <v>2.3485825446438513E-2</v>
+      </c>
+      <c r="O32" s="9">
+        <f t="shared" si="16"/>
+        <v>-4.380583145146788E-2</v>
+      </c>
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
       <c r="R32" s="3"/>
@@ -4281,8 +4580,12 @@
       <c r="CK32" s="3"/>
       <c r="CL32" s="3"/>
       <c r="CM32" s="3"/>
-    </row>
-    <row r="33" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN32" s="3"/>
+      <c r="CO32" s="3"/>
+      <c r="CP32" s="3"/>
+      <c r="CQ32" s="3"/>
+    </row>
+    <row r="33" spans="2:95" x14ac:dyDescent="0.2">
       <c r="B33" s="1" t="s">
         <v>55</v>
       </c>
@@ -4291,29 +4594,41 @@
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="11">
-        <f t="shared" ref="G33:J33" si="16">+G14/C14-1</f>
+        <f t="shared" ref="G33:J33" si="18">+G14/C14-1</f>
         <v>-0.10121757222097771</v>
       </c>
       <c r="H33" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-0.10701077569424144</v>
       </c>
       <c r="I33" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-5.7201574920779485E-2</v>
       </c>
       <c r="J33" s="11">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-0.11380749243542798</v>
       </c>
       <c r="K33" s="11">
         <f>+K14/G14-1</f>
         <v>-4.1901213603511067E-2</v>
       </c>
-      <c r="L33" s="10"/>
-      <c r="M33" s="10"/>
-      <c r="N33" s="10"/>
-      <c r="O33" s="10"/>
+      <c r="L33" s="11">
+        <f t="shared" ref="L33:O33" si="19">+L14/H14-1</f>
+        <v>-4.6920601019425523E-2</v>
+      </c>
+      <c r="M33" s="11">
+        <f t="shared" si="19"/>
+        <v>-5.2302612561106465E-2</v>
+      </c>
+      <c r="N33" s="11">
+        <f t="shared" si="19"/>
+        <v>-7.9808027051045949E-3</v>
+      </c>
+      <c r="O33" s="11">
+        <f t="shared" si="19"/>
+        <v>-3.1868459386915182E-2</v>
+      </c>
       <c r="P33" s="10"/>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -4323,10 +4638,10 @@
       <c r="V33" s="10"/>
       <c r="W33" s="10"/>
       <c r="X33" s="10"/>
-      <c r="Y33" s="3"/>
-      <c r="Z33" s="3"/>
-      <c r="AA33" s="3"/>
-      <c r="AB33" s="3"/>
+      <c r="Y33" s="10"/>
+      <c r="Z33" s="10"/>
+      <c r="AA33" s="10"/>
+      <c r="AB33" s="10"/>
       <c r="AC33" s="3"/>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3"/>
@@ -4390,35 +4705,99 @@
       <c r="CK33" s="3"/>
       <c r="CL33" s="3"/>
       <c r="CM33" s="3"/>
-    </row>
-    <row r="34" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN33" s="3"/>
+      <c r="CO33" s="3"/>
+      <c r="CP33" s="3"/>
+      <c r="CQ33" s="3"/>
+    </row>
+    <row r="34" spans="2:95" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="3"/>
-      <c r="O34" s="3"/>
+      <c r="C34" s="9">
+        <f t="shared" ref="C34:M34" si="20">+C16/C14</f>
+        <v>0.46432137528332185</v>
+      </c>
+      <c r="D34" s="9">
+        <f t="shared" si="20"/>
+        <v>0.47777840188833159</v>
+      </c>
+      <c r="E34" s="9">
+        <f t="shared" si="20"/>
+        <v>0.45129178630766403</v>
+      </c>
+      <c r="F34" s="9">
+        <f t="shared" si="20"/>
+        <v>0.45008058117530664</v>
+      </c>
+      <c r="G34" s="9">
+        <f t="shared" si="20"/>
+        <v>0.47536676340011741</v>
+      </c>
+      <c r="H34" s="9">
+        <f t="shared" si="20"/>
+        <v>0.49758438567486024</v>
+      </c>
+      <c r="I34" s="9">
+        <f t="shared" si="20"/>
+        <v>0.47475837574828395</v>
+      </c>
+      <c r="J34" s="9">
+        <f t="shared" si="20"/>
+        <v>0.46653390739998796</v>
+      </c>
+      <c r="K34" s="9">
+        <f t="shared" si="20"/>
+        <v>0.48188997485159618</v>
+      </c>
+      <c r="L34" s="9">
+        <f t="shared" si="20"/>
+        <v>0.47292144774932876</v>
+      </c>
+      <c r="M34" s="9">
+        <f>+M16/M14</f>
+        <v>0.44416126094982455</v>
+      </c>
+      <c r="N34" s="9">
+        <f t="shared" ref="N34:O34" si="21">+N16/N14</f>
+        <v>0.42012840249974126</v>
+      </c>
+      <c r="O34" s="9">
+        <f t="shared" si="21"/>
+        <v>0.54086656034508662</v>
+      </c>
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
-      <c r="T34" s="3"/>
-      <c r="U34" s="3"/>
-      <c r="V34" s="3"/>
-      <c r="W34" s="3"/>
-      <c r="X34" s="3"/>
-      <c r="Y34" s="3"/>
-      <c r="Z34" s="3"/>
+      <c r="T34" s="9" t="e">
+        <f t="shared" ref="T34:Z34" si="22">+T16/T14</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U34" s="9" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V34" s="9" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W34" s="9" t="e">
+        <f t="shared" si="22"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X34" s="9">
+        <f t="shared" si="22"/>
+        <v>0.46129582897146709</v>
+      </c>
+      <c r="Y34" s="9">
+        <f t="shared" si="22"/>
+        <v>0.47920128729685085</v>
+      </c>
+      <c r="Z34" s="9">
+        <f t="shared" si="22"/>
+        <v>0.45483079190636216</v>
+      </c>
       <c r="AA34" s="3"/>
       <c r="AB34" s="3"/>
       <c r="AC34" s="3"/>
@@ -4484,35 +4863,99 @@
       <c r="CK34" s="3"/>
       <c r="CL34" s="3"/>
       <c r="CM34" s="3"/>
-    </row>
-    <row r="35" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN34" s="3"/>
+      <c r="CO34" s="3"/>
+      <c r="CP34" s="3"/>
+      <c r="CQ34" s="3"/>
+    </row>
+    <row r="35" spans="2:95" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3"/>
-      <c r="N35" s="3"/>
-      <c r="O35" s="3"/>
+      <c r="C35" s="9">
+        <f t="shared" ref="C35:M35" si="23">+C19/C14</f>
+        <v>1.7026268731515179E-2</v>
+      </c>
+      <c r="D35" s="9">
+        <f t="shared" si="23"/>
+        <v>8.9024902436626932E-2</v>
+      </c>
+      <c r="E35" s="9">
+        <f t="shared" si="23"/>
+        <v>4.8053118247587644E-2</v>
+      </c>
+      <c r="F35" s="9">
+        <f t="shared" si="23"/>
+        <v>-2.6677736100592388E-3</v>
+      </c>
+      <c r="G35" s="9">
+        <f t="shared" si="23"/>
+        <v>-0.25322029459348722</v>
+      </c>
+      <c r="H35" s="9">
+        <f t="shared" si="23"/>
+        <v>0.12371490675993171</v>
+      </c>
+      <c r="I35" s="9">
+        <f t="shared" si="23"/>
+        <v>9.6421298764702134E-3</v>
+      </c>
+      <c r="J35" s="9">
+        <f t="shared" si="23"/>
+        <v>-6.1052039543174848E-2</v>
+      </c>
+      <c r="K35" s="9">
+        <f t="shared" si="23"/>
+        <v>2.9301593907948677E-3</v>
+      </c>
+      <c r="L35" s="9">
+        <f t="shared" si="23"/>
+        <v>1.2784052558160548E-2</v>
+      </c>
+      <c r="M35" s="9">
+        <f>+M19/M14</f>
+        <v>-0.11280644634087006</v>
+      </c>
+      <c r="N35" s="9">
+        <f t="shared" ref="N35:O35" si="24">+N19/N14</f>
+        <v>-2.8775719136823252E-2</v>
+      </c>
+      <c r="O35" s="9">
+        <f t="shared" si="24"/>
+        <v>4.2570225525011995E-2</v>
+      </c>
       <c r="P35" s="3"/>
       <c r="Q35" s="3"/>
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
-      <c r="T35" s="3"/>
-      <c r="U35" s="3"/>
-      <c r="V35" s="3"/>
-      <c r="W35" s="3"/>
-      <c r="X35" s="3"/>
-      <c r="Y35" s="3"/>
-      <c r="Z35" s="3"/>
+      <c r="T35" s="9" t="e">
+        <f t="shared" ref="T35:Z35" si="25">+T19/T14</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U35" s="9" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V35" s="9" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W35" s="9" t="e">
+        <f t="shared" si="25"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X35" s="9">
+        <f t="shared" si="25"/>
+        <v>4.0293910130327168E-2</v>
+      </c>
+      <c r="Y35" s="9">
+        <f t="shared" si="25"/>
+        <v>-3.586461695754134E-2</v>
+      </c>
+      <c r="Z35" s="9">
+        <f t="shared" si="25"/>
+        <v>-3.28433040631287E-2</v>
+      </c>
       <c r="AA35" s="3"/>
       <c r="AB35" s="3"/>
       <c r="AC35" s="3"/>
@@ -4578,35 +5021,99 @@
       <c r="CK35" s="3"/>
       <c r="CL35" s="3"/>
       <c r="CM35" s="3"/>
-    </row>
-    <row r="36" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN35" s="3"/>
+      <c r="CO35" s="3"/>
+      <c r="CP35" s="3"/>
+      <c r="CQ35" s="3"/>
+    </row>
+    <row r="36" spans="2:95" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="3"/>
-      <c r="O36" s="3"/>
+      <c r="C36" s="9">
+        <f t="shared" ref="C36:M36" si="26">+C23/C22</f>
+        <v>0.29368256768677703</v>
+      </c>
+      <c r="D36" s="9">
+        <f t="shared" si="26"/>
+        <v>0.2138688327316485</v>
+      </c>
+      <c r="E36" s="9">
+        <f t="shared" si="26"/>
+        <v>7.1932843651626513E-2</v>
+      </c>
+      <c r="F36" s="9">
+        <f t="shared" si="26"/>
+        <v>2.3676839464882509</v>
+      </c>
+      <c r="G36" s="9">
+        <f t="shared" si="26"/>
+        <v>-1.7156813744110565E-2</v>
+      </c>
+      <c r="H36" s="9">
+        <f t="shared" si="26"/>
+        <v>-1.272087330939237E-2</v>
+      </c>
+      <c r="I36" s="9">
+        <f t="shared" si="26"/>
+        <v>0.83322303110523388</v>
+      </c>
+      <c r="J36" s="9">
+        <f t="shared" si="26"/>
+        <v>0.15225423136452146</v>
+      </c>
+      <c r="K36" s="9">
+        <f t="shared" si="26"/>
+        <v>0.49013461183846158</v>
+      </c>
+      <c r="L36" s="9">
+        <f t="shared" si="26"/>
+        <v>3.4591278837177772</v>
+      </c>
+      <c r="M36" s="9">
+        <f>+M23/M22</f>
+        <v>-1.6885732827476041</v>
+      </c>
+      <c r="N36" s="9">
+        <f t="shared" ref="N36:O36" si="27">+N23/N22</f>
+        <v>-2.037838855421736E-2</v>
+      </c>
+      <c r="O36" s="9">
+        <f t="shared" si="27"/>
+        <v>0.97362539114886548</v>
+      </c>
       <c r="P36" s="3"/>
       <c r="Q36" s="3"/>
       <c r="R36" s="3"/>
       <c r="S36" s="3"/>
-      <c r="T36" s="3"/>
-      <c r="U36" s="3"/>
-      <c r="V36" s="3"/>
-      <c r="W36" s="3"/>
-      <c r="X36" s="3"/>
-      <c r="Y36" s="3"/>
-      <c r="Z36" s="3"/>
+      <c r="T36" s="9" t="e">
+        <f t="shared" ref="T36:Z36" si="28">+T23/T22</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U36" s="9" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V36" s="9" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W36" s="9" t="e">
+        <f t="shared" si="28"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X36" s="9">
+        <f t="shared" si="28"/>
+        <v>0.11451010922080015</v>
+      </c>
+      <c r="Y36" s="9">
+        <f t="shared" si="28"/>
+        <v>1.41139469237456E-2</v>
+      </c>
+      <c r="Z36" s="9">
+        <f t="shared" si="28"/>
+        <v>-1.4687954713069791</v>
+      </c>
       <c r="AA36" s="3"/>
       <c r="AB36" s="3"/>
       <c r="AC36" s="3"/>
@@ -4672,8 +5179,12 @@
       <c r="CK36" s="3"/>
       <c r="CL36" s="3"/>
       <c r="CM36" s="3"/>
-    </row>
-    <row r="37" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN36" s="3"/>
+      <c r="CO36" s="3"/>
+      <c r="CP36" s="3"/>
+      <c r="CQ36" s="3"/>
+    </row>
+    <row r="37" spans="2:95" x14ac:dyDescent="0.2">
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
@@ -4763,8 +5274,12 @@
       <c r="CK37" s="3"/>
       <c r="CL37" s="3"/>
       <c r="CM37" s="3"/>
-    </row>
-    <row r="38" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN37" s="3"/>
+      <c r="CO37" s="3"/>
+      <c r="CP37" s="3"/>
+      <c r="CQ37" s="3"/>
+    </row>
+    <row r="38" spans="2:95" x14ac:dyDescent="0.2">
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
@@ -4854,8 +5369,12 @@
       <c r="CK38" s="3"/>
       <c r="CL38" s="3"/>
       <c r="CM38" s="3"/>
-    </row>
-    <row r="39" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN38" s="3"/>
+      <c r="CO38" s="3"/>
+      <c r="CP38" s="3"/>
+      <c r="CQ38" s="3"/>
+    </row>
+    <row r="39" spans="2:95" x14ac:dyDescent="0.2">
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -4945,8 +5464,12 @@
       <c r="CK39" s="3"/>
       <c r="CL39" s="3"/>
       <c r="CM39" s="3"/>
-    </row>
-    <row r="40" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN39" s="3"/>
+      <c r="CO39" s="3"/>
+      <c r="CP39" s="3"/>
+      <c r="CQ39" s="3"/>
+    </row>
+    <row r="40" spans="2:95" x14ac:dyDescent="0.2">
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -5036,8 +5559,12 @@
       <c r="CK40" s="3"/>
       <c r="CL40" s="3"/>
       <c r="CM40" s="3"/>
-    </row>
-    <row r="41" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN40" s="3"/>
+      <c r="CO40" s="3"/>
+      <c r="CP40" s="3"/>
+      <c r="CQ40" s="3"/>
+    </row>
+    <row r="41" spans="2:95" x14ac:dyDescent="0.2">
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -5127,8 +5654,12 @@
       <c r="CK41" s="3"/>
       <c r="CL41" s="3"/>
       <c r="CM41" s="3"/>
-    </row>
-    <row r="42" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN41" s="3"/>
+      <c r="CO41" s="3"/>
+      <c r="CP41" s="3"/>
+      <c r="CQ41" s="3"/>
+    </row>
+    <row r="42" spans="2:95" x14ac:dyDescent="0.2">
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
@@ -5218,8 +5749,12 @@
       <c r="CK42" s="3"/>
       <c r="CL42" s="3"/>
       <c r="CM42" s="3"/>
-    </row>
-    <row r="43" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN42" s="3"/>
+      <c r="CO42" s="3"/>
+      <c r="CP42" s="3"/>
+      <c r="CQ42" s="3"/>
+    </row>
+    <row r="43" spans="2:95" x14ac:dyDescent="0.2">
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
@@ -5309,8 +5844,12 @@
       <c r="CK43" s="3"/>
       <c r="CL43" s="3"/>
       <c r="CM43" s="3"/>
-    </row>
-    <row r="44" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN43" s="3"/>
+      <c r="CO43" s="3"/>
+      <c r="CP43" s="3"/>
+      <c r="CQ43" s="3"/>
+    </row>
+    <row r="44" spans="2:95" x14ac:dyDescent="0.2">
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
@@ -5400,8 +5939,12 @@
       <c r="CK44" s="3"/>
       <c r="CL44" s="3"/>
       <c r="CM44" s="3"/>
-    </row>
-    <row r="45" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN44" s="3"/>
+      <c r="CO44" s="3"/>
+      <c r="CP44" s="3"/>
+      <c r="CQ44" s="3"/>
+    </row>
+    <row r="45" spans="2:95" x14ac:dyDescent="0.2">
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -5491,8 +6034,12 @@
       <c r="CK45" s="3"/>
       <c r="CL45" s="3"/>
       <c r="CM45" s="3"/>
-    </row>
-    <row r="46" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN45" s="3"/>
+      <c r="CO45" s="3"/>
+      <c r="CP45" s="3"/>
+      <c r="CQ45" s="3"/>
+    </row>
+    <row r="46" spans="2:95" x14ac:dyDescent="0.2">
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -5582,8 +6129,12 @@
       <c r="CK46" s="3"/>
       <c r="CL46" s="3"/>
       <c r="CM46" s="3"/>
-    </row>
-    <row r="47" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN46" s="3"/>
+      <c r="CO46" s="3"/>
+      <c r="CP46" s="3"/>
+      <c r="CQ46" s="3"/>
+    </row>
+    <row r="47" spans="2:95" x14ac:dyDescent="0.2">
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -5673,8 +6224,12 @@
       <c r="CK47" s="3"/>
       <c r="CL47" s="3"/>
       <c r="CM47" s="3"/>
-    </row>
-    <row r="48" spans="2:91" x14ac:dyDescent="0.2">
+      <c r="CN47" s="3"/>
+      <c r="CO47" s="3"/>
+      <c r="CP47" s="3"/>
+      <c r="CQ47" s="3"/>
+    </row>
+    <row r="48" spans="2:95" x14ac:dyDescent="0.2">
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -5764,8 +6319,12 @@
       <c r="CK48" s="3"/>
       <c r="CL48" s="3"/>
       <c r="CM48" s="3"/>
-    </row>
-    <row r="49" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN48" s="3"/>
+      <c r="CO48" s="3"/>
+      <c r="CP48" s="3"/>
+      <c r="CQ48" s="3"/>
+    </row>
+    <row r="49" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -5855,8 +6414,12 @@
       <c r="CK49" s="3"/>
       <c r="CL49" s="3"/>
       <c r="CM49" s="3"/>
-    </row>
-    <row r="50" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN49" s="3"/>
+      <c r="CO49" s="3"/>
+      <c r="CP49" s="3"/>
+      <c r="CQ49" s="3"/>
+    </row>
+    <row r="50" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
@@ -5946,8 +6509,12 @@
       <c r="CK50" s="3"/>
       <c r="CL50" s="3"/>
       <c r="CM50" s="3"/>
-    </row>
-    <row r="51" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN50" s="3"/>
+      <c r="CO50" s="3"/>
+      <c r="CP50" s="3"/>
+      <c r="CQ50" s="3"/>
+    </row>
+    <row r="51" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
@@ -6037,8 +6604,12 @@
       <c r="CK51" s="3"/>
       <c r="CL51" s="3"/>
       <c r="CM51" s="3"/>
-    </row>
-    <row r="52" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN51" s="3"/>
+      <c r="CO51" s="3"/>
+      <c r="CP51" s="3"/>
+      <c r="CQ51" s="3"/>
+    </row>
+    <row r="52" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -6128,8 +6699,12 @@
       <c r="CK52" s="3"/>
       <c r="CL52" s="3"/>
       <c r="CM52" s="3"/>
-    </row>
-    <row r="53" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN52" s="3"/>
+      <c r="CO52" s="3"/>
+      <c r="CP52" s="3"/>
+      <c r="CQ52" s="3"/>
+    </row>
+    <row r="53" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -6219,8 +6794,12 @@
       <c r="CK53" s="3"/>
       <c r="CL53" s="3"/>
       <c r="CM53" s="3"/>
-    </row>
-    <row r="54" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN53" s="3"/>
+      <c r="CO53" s="3"/>
+      <c r="CP53" s="3"/>
+      <c r="CQ53" s="3"/>
+    </row>
+    <row r="54" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
@@ -6310,8 +6889,12 @@
       <c r="CK54" s="3"/>
       <c r="CL54" s="3"/>
       <c r="CM54" s="3"/>
-    </row>
-    <row r="55" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN54" s="3"/>
+      <c r="CO54" s="3"/>
+      <c r="CP54" s="3"/>
+      <c r="CQ54" s="3"/>
+    </row>
+    <row r="55" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
@@ -6401,8 +6984,12 @@
       <c r="CK55" s="3"/>
       <c r="CL55" s="3"/>
       <c r="CM55" s="3"/>
-    </row>
-    <row r="56" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN55" s="3"/>
+      <c r="CO55" s="3"/>
+      <c r="CP55" s="3"/>
+      <c r="CQ55" s="3"/>
+    </row>
+    <row r="56" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
@@ -6492,8 +7079,12 @@
       <c r="CK56" s="3"/>
       <c r="CL56" s="3"/>
       <c r="CM56" s="3"/>
-    </row>
-    <row r="57" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN56" s="3"/>
+      <c r="CO56" s="3"/>
+      <c r="CP56" s="3"/>
+      <c r="CQ56" s="3"/>
+    </row>
+    <row r="57" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -6583,8 +7174,12 @@
       <c r="CK57" s="3"/>
       <c r="CL57" s="3"/>
       <c r="CM57" s="3"/>
-    </row>
-    <row r="58" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN57" s="3"/>
+      <c r="CO57" s="3"/>
+      <c r="CP57" s="3"/>
+      <c r="CQ57" s="3"/>
+    </row>
+    <row r="58" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
@@ -6674,8 +7269,12 @@
       <c r="CK58" s="3"/>
       <c r="CL58" s="3"/>
       <c r="CM58" s="3"/>
-    </row>
-    <row r="59" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN58" s="3"/>
+      <c r="CO58" s="3"/>
+      <c r="CP58" s="3"/>
+      <c r="CQ58" s="3"/>
+    </row>
+    <row r="59" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
@@ -6765,8 +7364,12 @@
       <c r="CK59" s="3"/>
       <c r="CL59" s="3"/>
       <c r="CM59" s="3"/>
-    </row>
-    <row r="60" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN59" s="3"/>
+      <c r="CO59" s="3"/>
+      <c r="CP59" s="3"/>
+      <c r="CQ59" s="3"/>
+    </row>
+    <row r="60" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -6856,8 +7459,12 @@
       <c r="CK60" s="3"/>
       <c r="CL60" s="3"/>
       <c r="CM60" s="3"/>
-    </row>
-    <row r="61" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN60" s="3"/>
+      <c r="CO60" s="3"/>
+      <c r="CP60" s="3"/>
+      <c r="CQ60" s="3"/>
+    </row>
+    <row r="61" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -6947,8 +7554,12 @@
       <c r="CK61" s="3"/>
       <c r="CL61" s="3"/>
       <c r="CM61" s="3"/>
-    </row>
-    <row r="62" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN61" s="3"/>
+      <c r="CO61" s="3"/>
+      <c r="CP61" s="3"/>
+      <c r="CQ61" s="3"/>
+    </row>
+    <row r="62" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -7038,8 +7649,12 @@
       <c r="CK62" s="3"/>
       <c r="CL62" s="3"/>
       <c r="CM62" s="3"/>
-    </row>
-    <row r="63" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN62" s="3"/>
+      <c r="CO62" s="3"/>
+      <c r="CP62" s="3"/>
+      <c r="CQ62" s="3"/>
+    </row>
+    <row r="63" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -7129,8 +7744,12 @@
       <c r="CK63" s="3"/>
       <c r="CL63" s="3"/>
       <c r="CM63" s="3"/>
-    </row>
-    <row r="64" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN63" s="3"/>
+      <c r="CO63" s="3"/>
+      <c r="CP63" s="3"/>
+      <c r="CQ63" s="3"/>
+    </row>
+    <row r="64" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -7220,8 +7839,12 @@
       <c r="CK64" s="3"/>
       <c r="CL64" s="3"/>
       <c r="CM64" s="3"/>
-    </row>
-    <row r="65" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN64" s="3"/>
+      <c r="CO64" s="3"/>
+      <c r="CP64" s="3"/>
+      <c r="CQ64" s="3"/>
+    </row>
+    <row r="65" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -7311,8 +7934,12 @@
       <c r="CK65" s="3"/>
       <c r="CL65" s="3"/>
       <c r="CM65" s="3"/>
-    </row>
-    <row r="66" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN65" s="3"/>
+      <c r="CO65" s="3"/>
+      <c r="CP65" s="3"/>
+      <c r="CQ65" s="3"/>
+    </row>
+    <row r="66" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
@@ -7402,8 +8029,12 @@
       <c r="CK66" s="3"/>
       <c r="CL66" s="3"/>
       <c r="CM66" s="3"/>
-    </row>
-    <row r="67" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN66" s="3"/>
+      <c r="CO66" s="3"/>
+      <c r="CP66" s="3"/>
+      <c r="CQ66" s="3"/>
+    </row>
+    <row r="67" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -7493,8 +8124,12 @@
       <c r="CK67" s="3"/>
       <c r="CL67" s="3"/>
       <c r="CM67" s="3"/>
-    </row>
-    <row r="68" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN67" s="3"/>
+      <c r="CO67" s="3"/>
+      <c r="CP67" s="3"/>
+      <c r="CQ67" s="3"/>
+    </row>
+    <row r="68" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -7584,8 +8219,12 @@
       <c r="CK68" s="3"/>
       <c r="CL68" s="3"/>
       <c r="CM68" s="3"/>
-    </row>
-    <row r="69" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN68" s="3"/>
+      <c r="CO68" s="3"/>
+      <c r="CP68" s="3"/>
+      <c r="CQ68" s="3"/>
+    </row>
+    <row r="69" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
@@ -7675,8 +8314,12 @@
       <c r="CK69" s="3"/>
       <c r="CL69" s="3"/>
       <c r="CM69" s="3"/>
-    </row>
-    <row r="70" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN69" s="3"/>
+      <c r="CO69" s="3"/>
+      <c r="CP69" s="3"/>
+      <c r="CQ69" s="3"/>
+    </row>
+    <row r="70" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
@@ -7766,8 +8409,12 @@
       <c r="CK70" s="3"/>
       <c r="CL70" s="3"/>
       <c r="CM70" s="3"/>
-    </row>
-    <row r="71" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN70" s="3"/>
+      <c r="CO70" s="3"/>
+      <c r="CP70" s="3"/>
+      <c r="CQ70" s="3"/>
+    </row>
+    <row r="71" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
@@ -7857,8 +8504,12 @@
       <c r="CK71" s="3"/>
       <c r="CL71" s="3"/>
       <c r="CM71" s="3"/>
-    </row>
-    <row r="72" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN71" s="3"/>
+      <c r="CO71" s="3"/>
+      <c r="CP71" s="3"/>
+      <c r="CQ71" s="3"/>
+    </row>
+    <row r="72" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
@@ -7948,8 +8599,12 @@
       <c r="CK72" s="3"/>
       <c r="CL72" s="3"/>
       <c r="CM72" s="3"/>
-    </row>
-    <row r="73" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN72" s="3"/>
+      <c r="CO72" s="3"/>
+      <c r="CP72" s="3"/>
+      <c r="CQ72" s="3"/>
+    </row>
+    <row r="73" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
@@ -8039,8 +8694,12 @@
       <c r="CK73" s="3"/>
       <c r="CL73" s="3"/>
       <c r="CM73" s="3"/>
-    </row>
-    <row r="74" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN73" s="3"/>
+      <c r="CO73" s="3"/>
+      <c r="CP73" s="3"/>
+      <c r="CQ73" s="3"/>
+    </row>
+    <row r="74" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
@@ -8130,8 +8789,12 @@
       <c r="CK74" s="3"/>
       <c r="CL74" s="3"/>
       <c r="CM74" s="3"/>
-    </row>
-    <row r="75" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN74" s="3"/>
+      <c r="CO74" s="3"/>
+      <c r="CP74" s="3"/>
+      <c r="CQ74" s="3"/>
+    </row>
+    <row r="75" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -8221,8 +8884,12 @@
       <c r="CK75" s="3"/>
       <c r="CL75" s="3"/>
       <c r="CM75" s="3"/>
-    </row>
-    <row r="76" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN75" s="3"/>
+      <c r="CO75" s="3"/>
+      <c r="CP75" s="3"/>
+      <c r="CQ75" s="3"/>
+    </row>
+    <row r="76" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -8312,8 +8979,12 @@
       <c r="CK76" s="3"/>
       <c r="CL76" s="3"/>
       <c r="CM76" s="3"/>
-    </row>
-    <row r="77" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN76" s="3"/>
+      <c r="CO76" s="3"/>
+      <c r="CP76" s="3"/>
+      <c r="CQ76" s="3"/>
+    </row>
+    <row r="77" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -8403,8 +9074,12 @@
       <c r="CK77" s="3"/>
       <c r="CL77" s="3"/>
       <c r="CM77" s="3"/>
-    </row>
-    <row r="78" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN77" s="3"/>
+      <c r="CO77" s="3"/>
+      <c r="CP77" s="3"/>
+      <c r="CQ77" s="3"/>
+    </row>
+    <row r="78" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
@@ -8494,8 +9169,12 @@
       <c r="CK78" s="3"/>
       <c r="CL78" s="3"/>
       <c r="CM78" s="3"/>
-    </row>
-    <row r="79" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN78" s="3"/>
+      <c r="CO78" s="3"/>
+      <c r="CP78" s="3"/>
+      <c r="CQ78" s="3"/>
+    </row>
+    <row r="79" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -8585,8 +9264,12 @@
       <c r="CK79" s="3"/>
       <c r="CL79" s="3"/>
       <c r="CM79" s="3"/>
-    </row>
-    <row r="80" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN79" s="3"/>
+      <c r="CO79" s="3"/>
+      <c r="CP79" s="3"/>
+      <c r="CQ79" s="3"/>
+    </row>
+    <row r="80" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -8676,8 +9359,12 @@
       <c r="CK80" s="3"/>
       <c r="CL80" s="3"/>
       <c r="CM80" s="3"/>
-    </row>
-    <row r="81" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN80" s="3"/>
+      <c r="CO80" s="3"/>
+      <c r="CP80" s="3"/>
+      <c r="CQ80" s="3"/>
+    </row>
+    <row r="81" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
@@ -8767,8 +9454,12 @@
       <c r="CK81" s="3"/>
       <c r="CL81" s="3"/>
       <c r="CM81" s="3"/>
-    </row>
-    <row r="82" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN81" s="3"/>
+      <c r="CO81" s="3"/>
+      <c r="CP81" s="3"/>
+      <c r="CQ81" s="3"/>
+    </row>
+    <row r="82" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
@@ -8858,8 +9549,12 @@
       <c r="CK82" s="3"/>
       <c r="CL82" s="3"/>
       <c r="CM82" s="3"/>
-    </row>
-    <row r="83" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN82" s="3"/>
+      <c r="CO82" s="3"/>
+      <c r="CP82" s="3"/>
+      <c r="CQ82" s="3"/>
+    </row>
+    <row r="83" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
@@ -8949,8 +9644,12 @@
       <c r="CK83" s="3"/>
       <c r="CL83" s="3"/>
       <c r="CM83" s="3"/>
-    </row>
-    <row r="84" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN83" s="3"/>
+      <c r="CO83" s="3"/>
+      <c r="CP83" s="3"/>
+      <c r="CQ83" s="3"/>
+    </row>
+    <row r="84" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
@@ -9040,8 +9739,12 @@
       <c r="CK84" s="3"/>
       <c r="CL84" s="3"/>
       <c r="CM84" s="3"/>
-    </row>
-    <row r="85" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN84" s="3"/>
+      <c r="CO84" s="3"/>
+      <c r="CP84" s="3"/>
+      <c r="CQ84" s="3"/>
+    </row>
+    <row r="85" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
@@ -9131,8 +9834,12 @@
       <c r="CK85" s="3"/>
       <c r="CL85" s="3"/>
       <c r="CM85" s="3"/>
-    </row>
-    <row r="86" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN85" s="3"/>
+      <c r="CO85" s="3"/>
+      <c r="CP85" s="3"/>
+      <c r="CQ85" s="3"/>
+    </row>
+    <row r="86" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
@@ -9222,8 +9929,12 @@
       <c r="CK86" s="3"/>
       <c r="CL86" s="3"/>
       <c r="CM86" s="3"/>
-    </row>
-    <row r="87" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN86" s="3"/>
+      <c r="CO86" s="3"/>
+      <c r="CP86" s="3"/>
+      <c r="CQ86" s="3"/>
+    </row>
+    <row r="87" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
@@ -9313,8 +10024,12 @@
       <c r="CK87" s="3"/>
       <c r="CL87" s="3"/>
       <c r="CM87" s="3"/>
-    </row>
-    <row r="88" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN87" s="3"/>
+      <c r="CO87" s="3"/>
+      <c r="CP87" s="3"/>
+      <c r="CQ87" s="3"/>
+    </row>
+    <row r="88" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
@@ -9404,8 +10119,12 @@
       <c r="CK88" s="3"/>
       <c r="CL88" s="3"/>
       <c r="CM88" s="3"/>
-    </row>
-    <row r="89" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN88" s="3"/>
+      <c r="CO88" s="3"/>
+      <c r="CP88" s="3"/>
+      <c r="CQ88" s="3"/>
+    </row>
+    <row r="89" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
@@ -9495,8 +10214,12 @@
       <c r="CK89" s="3"/>
       <c r="CL89" s="3"/>
       <c r="CM89" s="3"/>
-    </row>
-    <row r="90" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN89" s="3"/>
+      <c r="CO89" s="3"/>
+      <c r="CP89" s="3"/>
+      <c r="CQ89" s="3"/>
+    </row>
+    <row r="90" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
@@ -9586,8 +10309,12 @@
       <c r="CK90" s="3"/>
       <c r="CL90" s="3"/>
       <c r="CM90" s="3"/>
-    </row>
-    <row r="91" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN90" s="3"/>
+      <c r="CO90" s="3"/>
+      <c r="CP90" s="3"/>
+      <c r="CQ90" s="3"/>
+    </row>
+    <row r="91" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
@@ -9677,8 +10404,12 @@
       <c r="CK91" s="3"/>
       <c r="CL91" s="3"/>
       <c r="CM91" s="3"/>
-    </row>
-    <row r="92" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN91" s="3"/>
+      <c r="CO91" s="3"/>
+      <c r="CP91" s="3"/>
+      <c r="CQ91" s="3"/>
+    </row>
+    <row r="92" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
@@ -9768,8 +10499,12 @@
       <c r="CK92" s="3"/>
       <c r="CL92" s="3"/>
       <c r="CM92" s="3"/>
-    </row>
-    <row r="93" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN92" s="3"/>
+      <c r="CO92" s="3"/>
+      <c r="CP92" s="3"/>
+      <c r="CQ92" s="3"/>
+    </row>
+    <row r="93" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
@@ -9859,8 +10594,12 @@
       <c r="CK93" s="3"/>
       <c r="CL93" s="3"/>
       <c r="CM93" s="3"/>
-    </row>
-    <row r="94" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN93" s="3"/>
+      <c r="CO93" s="3"/>
+      <c r="CP93" s="3"/>
+      <c r="CQ93" s="3"/>
+    </row>
+    <row r="94" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
@@ -9950,8 +10689,12 @@
       <c r="CK94" s="3"/>
       <c r="CL94" s="3"/>
       <c r="CM94" s="3"/>
-    </row>
-    <row r="95" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN94" s="3"/>
+      <c r="CO94" s="3"/>
+      <c r="CP94" s="3"/>
+      <c r="CQ94" s="3"/>
+    </row>
+    <row r="95" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
@@ -10041,8 +10784,12 @@
       <c r="CK95" s="3"/>
       <c r="CL95" s="3"/>
       <c r="CM95" s="3"/>
-    </row>
-    <row r="96" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN95" s="3"/>
+      <c r="CO95" s="3"/>
+      <c r="CP95" s="3"/>
+      <c r="CQ95" s="3"/>
+    </row>
+    <row r="96" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
@@ -10132,8 +10879,12 @@
       <c r="CK96" s="3"/>
       <c r="CL96" s="3"/>
       <c r="CM96" s="3"/>
-    </row>
-    <row r="97" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN96" s="3"/>
+      <c r="CO96" s="3"/>
+      <c r="CP96" s="3"/>
+      <c r="CQ96" s="3"/>
+    </row>
+    <row r="97" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
@@ -10223,8 +10974,12 @@
       <c r="CK97" s="3"/>
       <c r="CL97" s="3"/>
       <c r="CM97" s="3"/>
-    </row>
-    <row r="98" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN97" s="3"/>
+      <c r="CO97" s="3"/>
+      <c r="CP97" s="3"/>
+      <c r="CQ97" s="3"/>
+    </row>
+    <row r="98" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
@@ -10314,8 +11069,12 @@
       <c r="CK98" s="3"/>
       <c r="CL98" s="3"/>
       <c r="CM98" s="3"/>
-    </row>
-    <row r="99" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN98" s="3"/>
+      <c r="CO98" s="3"/>
+      <c r="CP98" s="3"/>
+      <c r="CQ98" s="3"/>
+    </row>
+    <row r="99" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
@@ -10405,8 +11164,12 @@
       <c r="CK99" s="3"/>
       <c r="CL99" s="3"/>
       <c r="CM99" s="3"/>
-    </row>
-    <row r="100" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN99" s="3"/>
+      <c r="CO99" s="3"/>
+      <c r="CP99" s="3"/>
+      <c r="CQ99" s="3"/>
+    </row>
+    <row r="100" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
@@ -10496,8 +11259,12 @@
       <c r="CK100" s="3"/>
       <c r="CL100" s="3"/>
       <c r="CM100" s="3"/>
-    </row>
-    <row r="101" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN100" s="3"/>
+      <c r="CO100" s="3"/>
+      <c r="CP100" s="3"/>
+      <c r="CQ100" s="3"/>
+    </row>
+    <row r="101" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
@@ -10587,8 +11354,12 @@
       <c r="CK101" s="3"/>
       <c r="CL101" s="3"/>
       <c r="CM101" s="3"/>
-    </row>
-    <row r="102" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN101" s="3"/>
+      <c r="CO101" s="3"/>
+      <c r="CP101" s="3"/>
+      <c r="CQ101" s="3"/>
+    </row>
+    <row r="102" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
@@ -10678,8 +11449,12 @@
       <c r="CK102" s="3"/>
       <c r="CL102" s="3"/>
       <c r="CM102" s="3"/>
-    </row>
-    <row r="103" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN102" s="3"/>
+      <c r="CO102" s="3"/>
+      <c r="CP102" s="3"/>
+      <c r="CQ102" s="3"/>
+    </row>
+    <row r="103" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
@@ -10769,8 +11544,12 @@
       <c r="CK103" s="3"/>
       <c r="CL103" s="3"/>
       <c r="CM103" s="3"/>
-    </row>
-    <row r="104" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN103" s="3"/>
+      <c r="CO103" s="3"/>
+      <c r="CP103" s="3"/>
+      <c r="CQ103" s="3"/>
+    </row>
+    <row r="104" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
@@ -10860,8 +11639,12 @@
       <c r="CK104" s="3"/>
       <c r="CL104" s="3"/>
       <c r="CM104" s="3"/>
-    </row>
-    <row r="105" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN104" s="3"/>
+      <c r="CO104" s="3"/>
+      <c r="CP104" s="3"/>
+      <c r="CQ104" s="3"/>
+    </row>
+    <row r="105" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
@@ -10951,8 +11734,12 @@
       <c r="CK105" s="3"/>
       <c r="CL105" s="3"/>
       <c r="CM105" s="3"/>
-    </row>
-    <row r="106" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN105" s="3"/>
+      <c r="CO105" s="3"/>
+      <c r="CP105" s="3"/>
+      <c r="CQ105" s="3"/>
+    </row>
+    <row r="106" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
@@ -11042,8 +11829,12 @@
       <c r="CK106" s="3"/>
       <c r="CL106" s="3"/>
       <c r="CM106" s="3"/>
-    </row>
-    <row r="107" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN106" s="3"/>
+      <c r="CO106" s="3"/>
+      <c r="CP106" s="3"/>
+      <c r="CQ106" s="3"/>
+    </row>
+    <row r="107" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
@@ -11133,8 +11924,12 @@
       <c r="CK107" s="3"/>
       <c r="CL107" s="3"/>
       <c r="CM107" s="3"/>
-    </row>
-    <row r="108" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN107" s="3"/>
+      <c r="CO107" s="3"/>
+      <c r="CP107" s="3"/>
+      <c r="CQ107" s="3"/>
+    </row>
+    <row r="108" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
@@ -11224,8 +12019,12 @@
       <c r="CK108" s="3"/>
       <c r="CL108" s="3"/>
       <c r="CM108" s="3"/>
-    </row>
-    <row r="109" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN108" s="3"/>
+      <c r="CO108" s="3"/>
+      <c r="CP108" s="3"/>
+      <c r="CQ108" s="3"/>
+    </row>
+    <row r="109" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
@@ -11315,8 +12114,12 @@
       <c r="CK109" s="3"/>
       <c r="CL109" s="3"/>
       <c r="CM109" s="3"/>
-    </row>
-    <row r="110" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN109" s="3"/>
+      <c r="CO109" s="3"/>
+      <c r="CP109" s="3"/>
+      <c r="CQ109" s="3"/>
+    </row>
+    <row r="110" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
@@ -11406,8 +12209,12 @@
       <c r="CK110" s="3"/>
       <c r="CL110" s="3"/>
       <c r="CM110" s="3"/>
-    </row>
-    <row r="111" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN110" s="3"/>
+      <c r="CO110" s="3"/>
+      <c r="CP110" s="3"/>
+      <c r="CQ110" s="3"/>
+    </row>
+    <row r="111" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
@@ -11497,8 +12304,12 @@
       <c r="CK111" s="3"/>
       <c r="CL111" s="3"/>
       <c r="CM111" s="3"/>
-    </row>
-    <row r="112" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN111" s="3"/>
+      <c r="CO111" s="3"/>
+      <c r="CP111" s="3"/>
+      <c r="CQ111" s="3"/>
+    </row>
+    <row r="112" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
@@ -11588,8 +12399,12 @@
       <c r="CK112" s="3"/>
       <c r="CL112" s="3"/>
       <c r="CM112" s="3"/>
-    </row>
-    <row r="113" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN112" s="3"/>
+      <c r="CO112" s="3"/>
+      <c r="CP112" s="3"/>
+      <c r="CQ112" s="3"/>
+    </row>
+    <row r="113" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
@@ -11679,8 +12494,12 @@
       <c r="CK113" s="3"/>
       <c r="CL113" s="3"/>
       <c r="CM113" s="3"/>
-    </row>
-    <row r="114" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN113" s="3"/>
+      <c r="CO113" s="3"/>
+      <c r="CP113" s="3"/>
+      <c r="CQ113" s="3"/>
+    </row>
+    <row r="114" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
@@ -11770,8 +12589,12 @@
       <c r="CK114" s="3"/>
       <c r="CL114" s="3"/>
       <c r="CM114" s="3"/>
-    </row>
-    <row r="115" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN114" s="3"/>
+      <c r="CO114" s="3"/>
+      <c r="CP114" s="3"/>
+      <c r="CQ114" s="3"/>
+    </row>
+    <row r="115" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
@@ -11861,8 +12684,12 @@
       <c r="CK115" s="3"/>
       <c r="CL115" s="3"/>
       <c r="CM115" s="3"/>
-    </row>
-    <row r="116" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN115" s="3"/>
+      <c r="CO115" s="3"/>
+      <c r="CP115" s="3"/>
+      <c r="CQ115" s="3"/>
+    </row>
+    <row r="116" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
@@ -11952,8 +12779,12 @@
       <c r="CK116" s="3"/>
       <c r="CL116" s="3"/>
       <c r="CM116" s="3"/>
-    </row>
-    <row r="117" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN116" s="3"/>
+      <c r="CO116" s="3"/>
+      <c r="CP116" s="3"/>
+      <c r="CQ116" s="3"/>
+    </row>
+    <row r="117" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
@@ -12043,8 +12874,12 @@
       <c r="CK117" s="3"/>
       <c r="CL117" s="3"/>
       <c r="CM117" s="3"/>
-    </row>
-    <row r="118" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN117" s="3"/>
+      <c r="CO117" s="3"/>
+      <c r="CP117" s="3"/>
+      <c r="CQ117" s="3"/>
+    </row>
+    <row r="118" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
@@ -12134,8 +12969,12 @@
       <c r="CK118" s="3"/>
       <c r="CL118" s="3"/>
       <c r="CM118" s="3"/>
-    </row>
-    <row r="119" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN118" s="3"/>
+      <c r="CO118" s="3"/>
+      <c r="CP118" s="3"/>
+      <c r="CQ118" s="3"/>
+    </row>
+    <row r="119" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
@@ -12225,8 +13064,12 @@
       <c r="CK119" s="3"/>
       <c r="CL119" s="3"/>
       <c r="CM119" s="3"/>
-    </row>
-    <row r="120" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN119" s="3"/>
+      <c r="CO119" s="3"/>
+      <c r="CP119" s="3"/>
+      <c r="CQ119" s="3"/>
+    </row>
+    <row r="120" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
@@ -12316,8 +13159,12 @@
       <c r="CK120" s="3"/>
       <c r="CL120" s="3"/>
       <c r="CM120" s="3"/>
-    </row>
-    <row r="121" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN120" s="3"/>
+      <c r="CO120" s="3"/>
+      <c r="CP120" s="3"/>
+      <c r="CQ120" s="3"/>
+    </row>
+    <row r="121" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
@@ -12407,8 +13254,12 @@
       <c r="CK121" s="3"/>
       <c r="CL121" s="3"/>
       <c r="CM121" s="3"/>
-    </row>
-    <row r="122" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN121" s="3"/>
+      <c r="CO121" s="3"/>
+      <c r="CP121" s="3"/>
+      <c r="CQ121" s="3"/>
+    </row>
+    <row r="122" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
@@ -12498,8 +13349,12 @@
       <c r="CK122" s="3"/>
       <c r="CL122" s="3"/>
       <c r="CM122" s="3"/>
-    </row>
-    <row r="123" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN122" s="3"/>
+      <c r="CO122" s="3"/>
+      <c r="CP122" s="3"/>
+      <c r="CQ122" s="3"/>
+    </row>
+    <row r="123" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
@@ -12589,8 +13444,12 @@
       <c r="CK123" s="3"/>
       <c r="CL123" s="3"/>
       <c r="CM123" s="3"/>
-    </row>
-    <row r="124" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN123" s="3"/>
+      <c r="CO123" s="3"/>
+      <c r="CP123" s="3"/>
+      <c r="CQ123" s="3"/>
+    </row>
+    <row r="124" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
@@ -12680,8 +13539,12 @@
       <c r="CK124" s="3"/>
       <c r="CL124" s="3"/>
       <c r="CM124" s="3"/>
-    </row>
-    <row r="125" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN124" s="3"/>
+      <c r="CO124" s="3"/>
+      <c r="CP124" s="3"/>
+      <c r="CQ124" s="3"/>
+    </row>
+    <row r="125" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
@@ -12771,8 +13634,12 @@
       <c r="CK125" s="3"/>
       <c r="CL125" s="3"/>
       <c r="CM125" s="3"/>
-    </row>
-    <row r="126" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN125" s="3"/>
+      <c r="CO125" s="3"/>
+      <c r="CP125" s="3"/>
+      <c r="CQ125" s="3"/>
+    </row>
+    <row r="126" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
@@ -12862,8 +13729,12 @@
       <c r="CK126" s="3"/>
       <c r="CL126" s="3"/>
       <c r="CM126" s="3"/>
-    </row>
-    <row r="127" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN126" s="3"/>
+      <c r="CO126" s="3"/>
+      <c r="CP126" s="3"/>
+      <c r="CQ126" s="3"/>
+    </row>
+    <row r="127" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
@@ -12953,8 +13824,12 @@
       <c r="CK127" s="3"/>
       <c r="CL127" s="3"/>
       <c r="CM127" s="3"/>
-    </row>
-    <row r="128" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN127" s="3"/>
+      <c r="CO127" s="3"/>
+      <c r="CP127" s="3"/>
+      <c r="CQ127" s="3"/>
+    </row>
+    <row r="128" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
@@ -13044,8 +13919,12 @@
       <c r="CK128" s="3"/>
       <c r="CL128" s="3"/>
       <c r="CM128" s="3"/>
-    </row>
-    <row r="129" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN128" s="3"/>
+      <c r="CO128" s="3"/>
+      <c r="CP128" s="3"/>
+      <c r="CQ128" s="3"/>
+    </row>
+    <row r="129" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
@@ -13135,8 +14014,12 @@
       <c r="CK129" s="3"/>
       <c r="CL129" s="3"/>
       <c r="CM129" s="3"/>
-    </row>
-    <row r="130" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN129" s="3"/>
+      <c r="CO129" s="3"/>
+      <c r="CP129" s="3"/>
+      <c r="CQ129" s="3"/>
+    </row>
+    <row r="130" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
@@ -13226,8 +14109,12 @@
       <c r="CK130" s="3"/>
       <c r="CL130" s="3"/>
       <c r="CM130" s="3"/>
-    </row>
-    <row r="131" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN130" s="3"/>
+      <c r="CO130" s="3"/>
+      <c r="CP130" s="3"/>
+      <c r="CQ130" s="3"/>
+    </row>
+    <row r="131" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
@@ -13317,8 +14204,12 @@
       <c r="CK131" s="3"/>
       <c r="CL131" s="3"/>
       <c r="CM131" s="3"/>
-    </row>
-    <row r="132" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN131" s="3"/>
+      <c r="CO131" s="3"/>
+      <c r="CP131" s="3"/>
+      <c r="CQ131" s="3"/>
+    </row>
+    <row r="132" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
@@ -13408,8 +14299,12 @@
       <c r="CK132" s="3"/>
       <c r="CL132" s="3"/>
       <c r="CM132" s="3"/>
-    </row>
-    <row r="133" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN132" s="3"/>
+      <c r="CO132" s="3"/>
+      <c r="CP132" s="3"/>
+      <c r="CQ132" s="3"/>
+    </row>
+    <row r="133" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
@@ -13499,8 +14394,12 @@
       <c r="CK133" s="3"/>
       <c r="CL133" s="3"/>
       <c r="CM133" s="3"/>
-    </row>
-    <row r="134" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN133" s="3"/>
+      <c r="CO133" s="3"/>
+      <c r="CP133" s="3"/>
+      <c r="CQ133" s="3"/>
+    </row>
+    <row r="134" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
@@ -13590,8 +14489,12 @@
       <c r="CK134" s="3"/>
       <c r="CL134" s="3"/>
       <c r="CM134" s="3"/>
-    </row>
-    <row r="135" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN134" s="3"/>
+      <c r="CO134" s="3"/>
+      <c r="CP134" s="3"/>
+      <c r="CQ134" s="3"/>
+    </row>
+    <row r="135" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
@@ -13681,8 +14584,12 @@
       <c r="CK135" s="3"/>
       <c r="CL135" s="3"/>
       <c r="CM135" s="3"/>
-    </row>
-    <row r="136" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN135" s="3"/>
+      <c r="CO135" s="3"/>
+      <c r="CP135" s="3"/>
+      <c r="CQ135" s="3"/>
+    </row>
+    <row r="136" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
@@ -13772,8 +14679,12 @@
       <c r="CK136" s="3"/>
       <c r="CL136" s="3"/>
       <c r="CM136" s="3"/>
-    </row>
-    <row r="137" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN136" s="3"/>
+      <c r="CO136" s="3"/>
+      <c r="CP136" s="3"/>
+      <c r="CQ136" s="3"/>
+    </row>
+    <row r="137" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
@@ -13863,8 +14774,12 @@
       <c r="CK137" s="3"/>
       <c r="CL137" s="3"/>
       <c r="CM137" s="3"/>
-    </row>
-    <row r="138" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN137" s="3"/>
+      <c r="CO137" s="3"/>
+      <c r="CP137" s="3"/>
+      <c r="CQ137" s="3"/>
+    </row>
+    <row r="138" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
@@ -13954,8 +14869,12 @@
       <c r="CK138" s="3"/>
       <c r="CL138" s="3"/>
       <c r="CM138" s="3"/>
-    </row>
-    <row r="139" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN138" s="3"/>
+      <c r="CO138" s="3"/>
+      <c r="CP138" s="3"/>
+      <c r="CQ138" s="3"/>
+    </row>
+    <row r="139" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
@@ -14045,8 +14964,12 @@
       <c r="CK139" s="3"/>
       <c r="CL139" s="3"/>
       <c r="CM139" s="3"/>
-    </row>
-    <row r="140" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN139" s="3"/>
+      <c r="CO139" s="3"/>
+      <c r="CP139" s="3"/>
+      <c r="CQ139" s="3"/>
+    </row>
+    <row r="140" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
@@ -14136,8 +15059,12 @@
       <c r="CK140" s="3"/>
       <c r="CL140" s="3"/>
       <c r="CM140" s="3"/>
-    </row>
-    <row r="141" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN140" s="3"/>
+      <c r="CO140" s="3"/>
+      <c r="CP140" s="3"/>
+      <c r="CQ140" s="3"/>
+    </row>
+    <row r="141" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
@@ -14227,8 +15154,12 @@
       <c r="CK141" s="3"/>
       <c r="CL141" s="3"/>
       <c r="CM141" s="3"/>
-    </row>
-    <row r="142" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN141" s="3"/>
+      <c r="CO141" s="3"/>
+      <c r="CP141" s="3"/>
+      <c r="CQ141" s="3"/>
+    </row>
+    <row r="142" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
@@ -14318,8 +15249,12 @@
       <c r="CK142" s="3"/>
       <c r="CL142" s="3"/>
       <c r="CM142" s="3"/>
-    </row>
-    <row r="143" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN142" s="3"/>
+      <c r="CO142" s="3"/>
+      <c r="CP142" s="3"/>
+      <c r="CQ142" s="3"/>
+    </row>
+    <row r="143" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
@@ -14409,8 +15344,12 @@
       <c r="CK143" s="3"/>
       <c r="CL143" s="3"/>
       <c r="CM143" s="3"/>
-    </row>
-    <row r="144" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN143" s="3"/>
+      <c r="CO143" s="3"/>
+      <c r="CP143" s="3"/>
+      <c r="CQ143" s="3"/>
+    </row>
+    <row r="144" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
@@ -14500,8 +15439,12 @@
       <c r="CK144" s="3"/>
       <c r="CL144" s="3"/>
       <c r="CM144" s="3"/>
-    </row>
-    <row r="145" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN144" s="3"/>
+      <c r="CO144" s="3"/>
+      <c r="CP144" s="3"/>
+      <c r="CQ144" s="3"/>
+    </row>
+    <row r="145" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
@@ -14591,8 +15534,12 @@
       <c r="CK145" s="3"/>
       <c r="CL145" s="3"/>
       <c r="CM145" s="3"/>
-    </row>
-    <row r="146" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN145" s="3"/>
+      <c r="CO145" s="3"/>
+      <c r="CP145" s="3"/>
+      <c r="CQ145" s="3"/>
+    </row>
+    <row r="146" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
@@ -14682,8 +15629,12 @@
       <c r="CK146" s="3"/>
       <c r="CL146" s="3"/>
       <c r="CM146" s="3"/>
-    </row>
-    <row r="147" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN146" s="3"/>
+      <c r="CO146" s="3"/>
+      <c r="CP146" s="3"/>
+      <c r="CQ146" s="3"/>
+    </row>
+    <row r="147" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
@@ -14773,8 +15724,12 @@
       <c r="CK147" s="3"/>
       <c r="CL147" s="3"/>
       <c r="CM147" s="3"/>
-    </row>
-    <row r="148" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN147" s="3"/>
+      <c r="CO147" s="3"/>
+      <c r="CP147" s="3"/>
+      <c r="CQ147" s="3"/>
+    </row>
+    <row r="148" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
@@ -14864,8 +15819,12 @@
       <c r="CK148" s="3"/>
       <c r="CL148" s="3"/>
       <c r="CM148" s="3"/>
-    </row>
-    <row r="149" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN148" s="3"/>
+      <c r="CO148" s="3"/>
+      <c r="CP148" s="3"/>
+      <c r="CQ148" s="3"/>
+    </row>
+    <row r="149" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
@@ -14955,8 +15914,12 @@
       <c r="CK149" s="3"/>
       <c r="CL149" s="3"/>
       <c r="CM149" s="3"/>
-    </row>
-    <row r="150" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN149" s="3"/>
+      <c r="CO149" s="3"/>
+      <c r="CP149" s="3"/>
+      <c r="CQ149" s="3"/>
+    </row>
+    <row r="150" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
@@ -15046,8 +16009,12 @@
       <c r="CK150" s="3"/>
       <c r="CL150" s="3"/>
       <c r="CM150" s="3"/>
-    </row>
-    <row r="151" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN150" s="3"/>
+      <c r="CO150" s="3"/>
+      <c r="CP150" s="3"/>
+      <c r="CQ150" s="3"/>
+    </row>
+    <row r="151" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
@@ -15137,8 +16104,12 @@
       <c r="CK151" s="3"/>
       <c r="CL151" s="3"/>
       <c r="CM151" s="3"/>
-    </row>
-    <row r="152" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN151" s="3"/>
+      <c r="CO151" s="3"/>
+      <c r="CP151" s="3"/>
+      <c r="CQ151" s="3"/>
+    </row>
+    <row r="152" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
@@ -15228,8 +16199,12 @@
       <c r="CK152" s="3"/>
       <c r="CL152" s="3"/>
       <c r="CM152" s="3"/>
-    </row>
-    <row r="153" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN152" s="3"/>
+      <c r="CO152" s="3"/>
+      <c r="CP152" s="3"/>
+      <c r="CQ152" s="3"/>
+    </row>
+    <row r="153" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
@@ -15319,8 +16294,12 @@
       <c r="CK153" s="3"/>
       <c r="CL153" s="3"/>
       <c r="CM153" s="3"/>
-    </row>
-    <row r="154" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN153" s="3"/>
+      <c r="CO153" s="3"/>
+      <c r="CP153" s="3"/>
+      <c r="CQ153" s="3"/>
+    </row>
+    <row r="154" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
@@ -15410,8 +16389,12 @@
       <c r="CK154" s="3"/>
       <c r="CL154" s="3"/>
       <c r="CM154" s="3"/>
-    </row>
-    <row r="155" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN154" s="3"/>
+      <c r="CO154" s="3"/>
+      <c r="CP154" s="3"/>
+      <c r="CQ154" s="3"/>
+    </row>
+    <row r="155" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
@@ -15501,8 +16484,12 @@
       <c r="CK155" s="3"/>
       <c r="CL155" s="3"/>
       <c r="CM155" s="3"/>
-    </row>
-    <row r="156" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN155" s="3"/>
+      <c r="CO155" s="3"/>
+      <c r="CP155" s="3"/>
+      <c r="CQ155" s="3"/>
+    </row>
+    <row r="156" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
@@ -15592,8 +16579,12 @@
       <c r="CK156" s="3"/>
       <c r="CL156" s="3"/>
       <c r="CM156" s="3"/>
-    </row>
-    <row r="157" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN156" s="3"/>
+      <c r="CO156" s="3"/>
+      <c r="CP156" s="3"/>
+      <c r="CQ156" s="3"/>
+    </row>
+    <row r="157" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
@@ -15683,8 +16674,12 @@
       <c r="CK157" s="3"/>
       <c r="CL157" s="3"/>
       <c r="CM157" s="3"/>
-    </row>
-    <row r="158" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN157" s="3"/>
+      <c r="CO157" s="3"/>
+      <c r="CP157" s="3"/>
+      <c r="CQ157" s="3"/>
+    </row>
+    <row r="158" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
@@ -15774,8 +16769,12 @@
       <c r="CK158" s="3"/>
       <c r="CL158" s="3"/>
       <c r="CM158" s="3"/>
-    </row>
-    <row r="159" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN158" s="3"/>
+      <c r="CO158" s="3"/>
+      <c r="CP158" s="3"/>
+      <c r="CQ158" s="3"/>
+    </row>
+    <row r="159" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
@@ -15865,8 +16864,12 @@
       <c r="CK159" s="3"/>
       <c r="CL159" s="3"/>
       <c r="CM159" s="3"/>
-    </row>
-    <row r="160" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN159" s="3"/>
+      <c r="CO159" s="3"/>
+      <c r="CP159" s="3"/>
+      <c r="CQ159" s="3"/>
+    </row>
+    <row r="160" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
@@ -15956,8 +16959,12 @@
       <c r="CK160" s="3"/>
       <c r="CL160" s="3"/>
       <c r="CM160" s="3"/>
-    </row>
-    <row r="161" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN160" s="3"/>
+      <c r="CO160" s="3"/>
+      <c r="CP160" s="3"/>
+      <c r="CQ160" s="3"/>
+    </row>
+    <row r="161" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
@@ -16047,8 +17054,12 @@
       <c r="CK161" s="3"/>
       <c r="CL161" s="3"/>
       <c r="CM161" s="3"/>
-    </row>
-    <row r="162" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN161" s="3"/>
+      <c r="CO161" s="3"/>
+      <c r="CP161" s="3"/>
+      <c r="CQ161" s="3"/>
+    </row>
+    <row r="162" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
@@ -16138,8 +17149,12 @@
       <c r="CK162" s="3"/>
       <c r="CL162" s="3"/>
       <c r="CM162" s="3"/>
-    </row>
-    <row r="163" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN162" s="3"/>
+      <c r="CO162" s="3"/>
+      <c r="CP162" s="3"/>
+      <c r="CQ162" s="3"/>
+    </row>
+    <row r="163" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
@@ -16229,8 +17244,12 @@
       <c r="CK163" s="3"/>
       <c r="CL163" s="3"/>
       <c r="CM163" s="3"/>
-    </row>
-    <row r="164" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN163" s="3"/>
+      <c r="CO163" s="3"/>
+      <c r="CP163" s="3"/>
+      <c r="CQ163" s="3"/>
+    </row>
+    <row r="164" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
@@ -16320,8 +17339,12 @@
       <c r="CK164" s="3"/>
       <c r="CL164" s="3"/>
       <c r="CM164" s="3"/>
-    </row>
-    <row r="165" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN164" s="3"/>
+      <c r="CO164" s="3"/>
+      <c r="CP164" s="3"/>
+      <c r="CQ164" s="3"/>
+    </row>
+    <row r="165" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
@@ -16411,8 +17434,12 @@
       <c r="CK165" s="3"/>
       <c r="CL165" s="3"/>
       <c r="CM165" s="3"/>
-    </row>
-    <row r="166" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN165" s="3"/>
+      <c r="CO165" s="3"/>
+      <c r="CP165" s="3"/>
+      <c r="CQ165" s="3"/>
+    </row>
+    <row r="166" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
@@ -16502,8 +17529,12 @@
       <c r="CK166" s="3"/>
       <c r="CL166" s="3"/>
       <c r="CM166" s="3"/>
-    </row>
-    <row r="167" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN166" s="3"/>
+      <c r="CO166" s="3"/>
+      <c r="CP166" s="3"/>
+      <c r="CQ166" s="3"/>
+    </row>
+    <row r="167" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
@@ -16593,8 +17624,12 @@
       <c r="CK167" s="3"/>
       <c r="CL167" s="3"/>
       <c r="CM167" s="3"/>
-    </row>
-    <row r="168" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN167" s="3"/>
+      <c r="CO167" s="3"/>
+      <c r="CP167" s="3"/>
+      <c r="CQ167" s="3"/>
+    </row>
+    <row r="168" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
@@ -16684,8 +17719,12 @@
       <c r="CK168" s="3"/>
       <c r="CL168" s="3"/>
       <c r="CM168" s="3"/>
-    </row>
-    <row r="169" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN168" s="3"/>
+      <c r="CO168" s="3"/>
+      <c r="CP168" s="3"/>
+      <c r="CQ168" s="3"/>
+    </row>
+    <row r="169" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
@@ -16775,8 +17814,12 @@
       <c r="CK169" s="3"/>
       <c r="CL169" s="3"/>
       <c r="CM169" s="3"/>
-    </row>
-    <row r="170" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN169" s="3"/>
+      <c r="CO169" s="3"/>
+      <c r="CP169" s="3"/>
+      <c r="CQ169" s="3"/>
+    </row>
+    <row r="170" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
@@ -16866,8 +17909,12 @@
       <c r="CK170" s="3"/>
       <c r="CL170" s="3"/>
       <c r="CM170" s="3"/>
-    </row>
-    <row r="171" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN170" s="3"/>
+      <c r="CO170" s="3"/>
+      <c r="CP170" s="3"/>
+      <c r="CQ170" s="3"/>
+    </row>
+    <row r="171" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
@@ -16957,8 +18004,12 @@
       <c r="CK171" s="3"/>
       <c r="CL171" s="3"/>
       <c r="CM171" s="3"/>
-    </row>
-    <row r="172" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN171" s="3"/>
+      <c r="CO171" s="3"/>
+      <c r="CP171" s="3"/>
+      <c r="CQ171" s="3"/>
+    </row>
+    <row r="172" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
@@ -17048,8 +18099,12 @@
       <c r="CK172" s="3"/>
       <c r="CL172" s="3"/>
       <c r="CM172" s="3"/>
-    </row>
-    <row r="173" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN172" s="3"/>
+      <c r="CO172" s="3"/>
+      <c r="CP172" s="3"/>
+      <c r="CQ172" s="3"/>
+    </row>
+    <row r="173" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
@@ -17139,8 +18194,12 @@
       <c r="CK173" s="3"/>
       <c r="CL173" s="3"/>
       <c r="CM173" s="3"/>
-    </row>
-    <row r="174" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN173" s="3"/>
+      <c r="CO173" s="3"/>
+      <c r="CP173" s="3"/>
+      <c r="CQ173" s="3"/>
+    </row>
+    <row r="174" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
@@ -17230,8 +18289,12 @@
       <c r="CK174" s="3"/>
       <c r="CL174" s="3"/>
       <c r="CM174" s="3"/>
-    </row>
-    <row r="175" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN174" s="3"/>
+      <c r="CO174" s="3"/>
+      <c r="CP174" s="3"/>
+      <c r="CQ174" s="3"/>
+    </row>
+    <row r="175" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
@@ -17321,8 +18384,12 @@
       <c r="CK175" s="3"/>
       <c r="CL175" s="3"/>
       <c r="CM175" s="3"/>
-    </row>
-    <row r="176" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN175" s="3"/>
+      <c r="CO175" s="3"/>
+      <c r="CP175" s="3"/>
+      <c r="CQ175" s="3"/>
+    </row>
+    <row r="176" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
@@ -17412,8 +18479,12 @@
       <c r="CK176" s="3"/>
       <c r="CL176" s="3"/>
       <c r="CM176" s="3"/>
-    </row>
-    <row r="177" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN176" s="3"/>
+      <c r="CO176" s="3"/>
+      <c r="CP176" s="3"/>
+      <c r="CQ176" s="3"/>
+    </row>
+    <row r="177" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
       <c r="E177" s="3"/>
@@ -17503,8 +18574,12 @@
       <c r="CK177" s="3"/>
       <c r="CL177" s="3"/>
       <c r="CM177" s="3"/>
-    </row>
-    <row r="178" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN177" s="3"/>
+      <c r="CO177" s="3"/>
+      <c r="CP177" s="3"/>
+      <c r="CQ177" s="3"/>
+    </row>
+    <row r="178" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
@@ -17594,8 +18669,12 @@
       <c r="CK178" s="3"/>
       <c r="CL178" s="3"/>
       <c r="CM178" s="3"/>
-    </row>
-    <row r="179" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN178" s="3"/>
+      <c r="CO178" s="3"/>
+      <c r="CP178" s="3"/>
+      <c r="CQ178" s="3"/>
+    </row>
+    <row r="179" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
@@ -17685,8 +18764,12 @@
       <c r="CK179" s="3"/>
       <c r="CL179" s="3"/>
       <c r="CM179" s="3"/>
-    </row>
-    <row r="180" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN179" s="3"/>
+      <c r="CO179" s="3"/>
+      <c r="CP179" s="3"/>
+      <c r="CQ179" s="3"/>
+    </row>
+    <row r="180" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
@@ -17776,8 +18859,12 @@
       <c r="CK180" s="3"/>
       <c r="CL180" s="3"/>
       <c r="CM180" s="3"/>
-    </row>
-    <row r="181" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN180" s="3"/>
+      <c r="CO180" s="3"/>
+      <c r="CP180" s="3"/>
+      <c r="CQ180" s="3"/>
+    </row>
+    <row r="181" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
@@ -17867,8 +18954,12 @@
       <c r="CK181" s="3"/>
       <c r="CL181" s="3"/>
       <c r="CM181" s="3"/>
-    </row>
-    <row r="182" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN181" s="3"/>
+      <c r="CO181" s="3"/>
+      <c r="CP181" s="3"/>
+      <c r="CQ181" s="3"/>
+    </row>
+    <row r="182" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
@@ -17958,8 +19049,12 @@
       <c r="CK182" s="3"/>
       <c r="CL182" s="3"/>
       <c r="CM182" s="3"/>
-    </row>
-    <row r="183" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN182" s="3"/>
+      <c r="CO182" s="3"/>
+      <c r="CP182" s="3"/>
+      <c r="CQ182" s="3"/>
+    </row>
+    <row r="183" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
@@ -18049,8 +19144,12 @@
       <c r="CK183" s="3"/>
       <c r="CL183" s="3"/>
       <c r="CM183" s="3"/>
-    </row>
-    <row r="184" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN183" s="3"/>
+      <c r="CO183" s="3"/>
+      <c r="CP183" s="3"/>
+      <c r="CQ183" s="3"/>
+    </row>
+    <row r="184" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
@@ -18140,8 +19239,12 @@
       <c r="CK184" s="3"/>
       <c r="CL184" s="3"/>
       <c r="CM184" s="3"/>
-    </row>
-    <row r="185" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN184" s="3"/>
+      <c r="CO184" s="3"/>
+      <c r="CP184" s="3"/>
+      <c r="CQ184" s="3"/>
+    </row>
+    <row r="185" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="3"/>
@@ -18231,8 +19334,12 @@
       <c r="CK185" s="3"/>
       <c r="CL185" s="3"/>
       <c r="CM185" s="3"/>
-    </row>
-    <row r="186" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN185" s="3"/>
+      <c r="CO185" s="3"/>
+      <c r="CP185" s="3"/>
+      <c r="CQ185" s="3"/>
+    </row>
+    <row r="186" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
@@ -18322,8 +19429,12 @@
       <c r="CK186" s="3"/>
       <c r="CL186" s="3"/>
       <c r="CM186" s="3"/>
-    </row>
-    <row r="187" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN186" s="3"/>
+      <c r="CO186" s="3"/>
+      <c r="CP186" s="3"/>
+      <c r="CQ186" s="3"/>
+    </row>
+    <row r="187" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
@@ -18413,8 +19524,12 @@
       <c r="CK187" s="3"/>
       <c r="CL187" s="3"/>
       <c r="CM187" s="3"/>
-    </row>
-    <row r="188" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN187" s="3"/>
+      <c r="CO187" s="3"/>
+      <c r="CP187" s="3"/>
+      <c r="CQ187" s="3"/>
+    </row>
+    <row r="188" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
@@ -18504,8 +19619,12 @@
       <c r="CK188" s="3"/>
       <c r="CL188" s="3"/>
       <c r="CM188" s="3"/>
-    </row>
-    <row r="189" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN188" s="3"/>
+      <c r="CO188" s="3"/>
+      <c r="CP188" s="3"/>
+      <c r="CQ188" s="3"/>
+    </row>
+    <row r="189" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
       <c r="E189" s="3"/>
@@ -18595,8 +19714,12 @@
       <c r="CK189" s="3"/>
       <c r="CL189" s="3"/>
       <c r="CM189" s="3"/>
-    </row>
-    <row r="190" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN189" s="3"/>
+      <c r="CO189" s="3"/>
+      <c r="CP189" s="3"/>
+      <c r="CQ189" s="3"/>
+    </row>
+    <row r="190" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
@@ -18686,8 +19809,12 @@
       <c r="CK190" s="3"/>
       <c r="CL190" s="3"/>
       <c r="CM190" s="3"/>
-    </row>
-    <row r="191" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN190" s="3"/>
+      <c r="CO190" s="3"/>
+      <c r="CP190" s="3"/>
+      <c r="CQ190" s="3"/>
+    </row>
+    <row r="191" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
@@ -18777,8 +19904,12 @@
       <c r="CK191" s="3"/>
       <c r="CL191" s="3"/>
       <c r="CM191" s="3"/>
-    </row>
-    <row r="192" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN191" s="3"/>
+      <c r="CO191" s="3"/>
+      <c r="CP191" s="3"/>
+      <c r="CQ191" s="3"/>
+    </row>
+    <row r="192" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
@@ -18868,8 +19999,12 @@
       <c r="CK192" s="3"/>
       <c r="CL192" s="3"/>
       <c r="CM192" s="3"/>
-    </row>
-    <row r="193" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN192" s="3"/>
+      <c r="CO192" s="3"/>
+      <c r="CP192" s="3"/>
+      <c r="CQ192" s="3"/>
+    </row>
+    <row r="193" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
@@ -18959,8 +20094,12 @@
       <c r="CK193" s="3"/>
       <c r="CL193" s="3"/>
       <c r="CM193" s="3"/>
-    </row>
-    <row r="194" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN193" s="3"/>
+      <c r="CO193" s="3"/>
+      <c r="CP193" s="3"/>
+      <c r="CQ193" s="3"/>
+    </row>
+    <row r="194" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
@@ -19050,8 +20189,12 @@
       <c r="CK194" s="3"/>
       <c r="CL194" s="3"/>
       <c r="CM194" s="3"/>
-    </row>
-    <row r="195" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN194" s="3"/>
+      <c r="CO194" s="3"/>
+      <c r="CP194" s="3"/>
+      <c r="CQ194" s="3"/>
+    </row>
+    <row r="195" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
@@ -19141,8 +20284,12 @@
       <c r="CK195" s="3"/>
       <c r="CL195" s="3"/>
       <c r="CM195" s="3"/>
-    </row>
-    <row r="196" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN195" s="3"/>
+      <c r="CO195" s="3"/>
+      <c r="CP195" s="3"/>
+      <c r="CQ195" s="3"/>
+    </row>
+    <row r="196" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
@@ -19232,8 +20379,12 @@
       <c r="CK196" s="3"/>
       <c r="CL196" s="3"/>
       <c r="CM196" s="3"/>
-    </row>
-    <row r="197" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN196" s="3"/>
+      <c r="CO196" s="3"/>
+      <c r="CP196" s="3"/>
+      <c r="CQ196" s="3"/>
+    </row>
+    <row r="197" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
       <c r="E197" s="3"/>
@@ -19323,8 +20474,12 @@
       <c r="CK197" s="3"/>
       <c r="CL197" s="3"/>
       <c r="CM197" s="3"/>
-    </row>
-    <row r="198" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN197" s="3"/>
+      <c r="CO197" s="3"/>
+      <c r="CP197" s="3"/>
+      <c r="CQ197" s="3"/>
+    </row>
+    <row r="198" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
       <c r="E198" s="3"/>
@@ -19414,8 +20569,12 @@
       <c r="CK198" s="3"/>
       <c r="CL198" s="3"/>
       <c r="CM198" s="3"/>
-    </row>
-    <row r="199" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN198" s="3"/>
+      <c r="CO198" s="3"/>
+      <c r="CP198" s="3"/>
+      <c r="CQ198" s="3"/>
+    </row>
+    <row r="199" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
@@ -19505,8 +20664,12 @@
       <c r="CK199" s="3"/>
       <c r="CL199" s="3"/>
       <c r="CM199" s="3"/>
-    </row>
-    <row r="200" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN199" s="3"/>
+      <c r="CO199" s="3"/>
+      <c r="CP199" s="3"/>
+      <c r="CQ199" s="3"/>
+    </row>
+    <row r="200" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
@@ -19596,8 +20759,12 @@
       <c r="CK200" s="3"/>
       <c r="CL200" s="3"/>
       <c r="CM200" s="3"/>
-    </row>
-    <row r="201" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN200" s="3"/>
+      <c r="CO200" s="3"/>
+      <c r="CP200" s="3"/>
+      <c r="CQ200" s="3"/>
+    </row>
+    <row r="201" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C201" s="3"/>
       <c r="D201" s="3"/>
       <c r="E201" s="3"/>
@@ -19687,8 +20854,12 @@
       <c r="CK201" s="3"/>
       <c r="CL201" s="3"/>
       <c r="CM201" s="3"/>
-    </row>
-    <row r="202" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN201" s="3"/>
+      <c r="CO201" s="3"/>
+      <c r="CP201" s="3"/>
+      <c r="CQ201" s="3"/>
+    </row>
+    <row r="202" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
@@ -19778,8 +20949,12 @@
       <c r="CK202" s="3"/>
       <c r="CL202" s="3"/>
       <c r="CM202" s="3"/>
-    </row>
-    <row r="203" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN202" s="3"/>
+      <c r="CO202" s="3"/>
+      <c r="CP202" s="3"/>
+      <c r="CQ202" s="3"/>
+    </row>
+    <row r="203" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
       <c r="E203" s="3"/>
@@ -19869,8 +21044,12 @@
       <c r="CK203" s="3"/>
       <c r="CL203" s="3"/>
       <c r="CM203" s="3"/>
-    </row>
-    <row r="204" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN203" s="3"/>
+      <c r="CO203" s="3"/>
+      <c r="CP203" s="3"/>
+      <c r="CQ203" s="3"/>
+    </row>
+    <row r="204" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
       <c r="E204" s="3"/>
@@ -19960,8 +21139,12 @@
       <c r="CK204" s="3"/>
       <c r="CL204" s="3"/>
       <c r="CM204" s="3"/>
-    </row>
-    <row r="205" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN204" s="3"/>
+      <c r="CO204" s="3"/>
+      <c r="CP204" s="3"/>
+      <c r="CQ204" s="3"/>
+    </row>
+    <row r="205" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
       <c r="E205" s="3"/>
@@ -20051,8 +21234,12 @@
       <c r="CK205" s="3"/>
       <c r="CL205" s="3"/>
       <c r="CM205" s="3"/>
-    </row>
-    <row r="206" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN205" s="3"/>
+      <c r="CO205" s="3"/>
+      <c r="CP205" s="3"/>
+      <c r="CQ205" s="3"/>
+    </row>
+    <row r="206" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
@@ -20142,8 +21329,12 @@
       <c r="CK206" s="3"/>
       <c r="CL206" s="3"/>
       <c r="CM206" s="3"/>
-    </row>
-    <row r="207" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN206" s="3"/>
+      <c r="CO206" s="3"/>
+      <c r="CP206" s="3"/>
+      <c r="CQ206" s="3"/>
+    </row>
+    <row r="207" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
       <c r="E207" s="3"/>
@@ -20233,8 +21424,12 @@
       <c r="CK207" s="3"/>
       <c r="CL207" s="3"/>
       <c r="CM207" s="3"/>
-    </row>
-    <row r="208" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN207" s="3"/>
+      <c r="CO207" s="3"/>
+      <c r="CP207" s="3"/>
+      <c r="CQ207" s="3"/>
+    </row>
+    <row r="208" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
@@ -20324,8 +21519,12 @@
       <c r="CK208" s="3"/>
       <c r="CL208" s="3"/>
       <c r="CM208" s="3"/>
-    </row>
-    <row r="209" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN208" s="3"/>
+      <c r="CO208" s="3"/>
+      <c r="CP208" s="3"/>
+      <c r="CQ208" s="3"/>
+    </row>
+    <row r="209" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
       <c r="E209" s="3"/>
@@ -20415,8 +21614,12 @@
       <c r="CK209" s="3"/>
       <c r="CL209" s="3"/>
       <c r="CM209" s="3"/>
-    </row>
-    <row r="210" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN209" s="3"/>
+      <c r="CO209" s="3"/>
+      <c r="CP209" s="3"/>
+      <c r="CQ209" s="3"/>
+    </row>
+    <row r="210" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
       <c r="E210" s="3"/>
@@ -20506,8 +21709,12 @@
       <c r="CK210" s="3"/>
       <c r="CL210" s="3"/>
       <c r="CM210" s="3"/>
-    </row>
-    <row r="211" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN210" s="3"/>
+      <c r="CO210" s="3"/>
+      <c r="CP210" s="3"/>
+      <c r="CQ210" s="3"/>
+    </row>
+    <row r="211" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
       <c r="E211" s="3"/>
@@ -20597,8 +21804,12 @@
       <c r="CK211" s="3"/>
       <c r="CL211" s="3"/>
       <c r="CM211" s="3"/>
-    </row>
-    <row r="212" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN211" s="3"/>
+      <c r="CO211" s="3"/>
+      <c r="CP211" s="3"/>
+      <c r="CQ211" s="3"/>
+    </row>
+    <row r="212" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
       <c r="E212" s="3"/>
@@ -20688,8 +21899,12 @@
       <c r="CK212" s="3"/>
       <c r="CL212" s="3"/>
       <c r="CM212" s="3"/>
-    </row>
-    <row r="213" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN212" s="3"/>
+      <c r="CO212" s="3"/>
+      <c r="CP212" s="3"/>
+      <c r="CQ212" s="3"/>
+    </row>
+    <row r="213" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
       <c r="E213" s="3"/>
@@ -20779,8 +21994,12 @@
       <c r="CK213" s="3"/>
       <c r="CL213" s="3"/>
       <c r="CM213" s="3"/>
-    </row>
-    <row r="214" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN213" s="3"/>
+      <c r="CO213" s="3"/>
+      <c r="CP213" s="3"/>
+      <c r="CQ213" s="3"/>
+    </row>
+    <row r="214" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
       <c r="E214" s="3"/>
@@ -20870,8 +22089,12 @@
       <c r="CK214" s="3"/>
       <c r="CL214" s="3"/>
       <c r="CM214" s="3"/>
-    </row>
-    <row r="215" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN214" s="3"/>
+      <c r="CO214" s="3"/>
+      <c r="CP214" s="3"/>
+      <c r="CQ214" s="3"/>
+    </row>
+    <row r="215" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
       <c r="E215" s="3"/>
@@ -20961,8 +22184,12 @@
       <c r="CK215" s="3"/>
       <c r="CL215" s="3"/>
       <c r="CM215" s="3"/>
-    </row>
-    <row r="216" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN215" s="3"/>
+      <c r="CO215" s="3"/>
+      <c r="CP215" s="3"/>
+      <c r="CQ215" s="3"/>
+    </row>
+    <row r="216" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
       <c r="E216" s="3"/>
@@ -21052,8 +22279,12 @@
       <c r="CK216" s="3"/>
       <c r="CL216" s="3"/>
       <c r="CM216" s="3"/>
-    </row>
-    <row r="217" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN216" s="3"/>
+      <c r="CO216" s="3"/>
+      <c r="CP216" s="3"/>
+      <c r="CQ216" s="3"/>
+    </row>
+    <row r="217" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
       <c r="E217" s="3"/>
@@ -21143,8 +22374,12 @@
       <c r="CK217" s="3"/>
       <c r="CL217" s="3"/>
       <c r="CM217" s="3"/>
-    </row>
-    <row r="218" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN217" s="3"/>
+      <c r="CO217" s="3"/>
+      <c r="CP217" s="3"/>
+      <c r="CQ217" s="3"/>
+    </row>
+    <row r="218" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
       <c r="E218" s="3"/>
@@ -21234,8 +22469,12 @@
       <c r="CK218" s="3"/>
       <c r="CL218" s="3"/>
       <c r="CM218" s="3"/>
-    </row>
-    <row r="219" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN218" s="3"/>
+      <c r="CO218" s="3"/>
+      <c r="CP218" s="3"/>
+      <c r="CQ218" s="3"/>
+    </row>
+    <row r="219" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C219" s="3"/>
       <c r="D219" s="3"/>
       <c r="E219" s="3"/>
@@ -21325,8 +22564,12 @@
       <c r="CK219" s="3"/>
       <c r="CL219" s="3"/>
       <c r="CM219" s="3"/>
-    </row>
-    <row r="220" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN219" s="3"/>
+      <c r="CO219" s="3"/>
+      <c r="CP219" s="3"/>
+      <c r="CQ219" s="3"/>
+    </row>
+    <row r="220" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
       <c r="E220" s="3"/>
@@ -21416,8 +22659,12 @@
       <c r="CK220" s="3"/>
       <c r="CL220" s="3"/>
       <c r="CM220" s="3"/>
-    </row>
-    <row r="221" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN220" s="3"/>
+      <c r="CO220" s="3"/>
+      <c r="CP220" s="3"/>
+      <c r="CQ220" s="3"/>
+    </row>
+    <row r="221" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C221" s="3"/>
       <c r="D221" s="3"/>
       <c r="E221" s="3"/>
@@ -21507,8 +22754,12 @@
       <c r="CK221" s="3"/>
       <c r="CL221" s="3"/>
       <c r="CM221" s="3"/>
-    </row>
-    <row r="222" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN221" s="3"/>
+      <c r="CO221" s="3"/>
+      <c r="CP221" s="3"/>
+      <c r="CQ221" s="3"/>
+    </row>
+    <row r="222" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C222" s="3"/>
       <c r="D222" s="3"/>
       <c r="E222" s="3"/>
@@ -21598,8 +22849,12 @@
       <c r="CK222" s="3"/>
       <c r="CL222" s="3"/>
       <c r="CM222" s="3"/>
-    </row>
-    <row r="223" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN222" s="3"/>
+      <c r="CO222" s="3"/>
+      <c r="CP222" s="3"/>
+      <c r="CQ222" s="3"/>
+    </row>
+    <row r="223" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C223" s="3"/>
       <c r="D223" s="3"/>
       <c r="E223" s="3"/>
@@ -21689,8 +22944,12 @@
       <c r="CK223" s="3"/>
       <c r="CL223" s="3"/>
       <c r="CM223" s="3"/>
-    </row>
-    <row r="224" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN223" s="3"/>
+      <c r="CO223" s="3"/>
+      <c r="CP223" s="3"/>
+      <c r="CQ223" s="3"/>
+    </row>
+    <row r="224" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
       <c r="E224" s="3"/>
@@ -21780,8 +23039,12 @@
       <c r="CK224" s="3"/>
       <c r="CL224" s="3"/>
       <c r="CM224" s="3"/>
-    </row>
-    <row r="225" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN224" s="3"/>
+      <c r="CO224" s="3"/>
+      <c r="CP224" s="3"/>
+      <c r="CQ224" s="3"/>
+    </row>
+    <row r="225" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C225" s="3"/>
       <c r="D225" s="3"/>
       <c r="E225" s="3"/>
@@ -21871,8 +23134,12 @@
       <c r="CK225" s="3"/>
       <c r="CL225" s="3"/>
       <c r="CM225" s="3"/>
-    </row>
-    <row r="226" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN225" s="3"/>
+      <c r="CO225" s="3"/>
+      <c r="CP225" s="3"/>
+      <c r="CQ225" s="3"/>
+    </row>
+    <row r="226" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C226" s="3"/>
       <c r="D226" s="3"/>
       <c r="E226" s="3"/>
@@ -21962,8 +23229,12 @@
       <c r="CK226" s="3"/>
       <c r="CL226" s="3"/>
       <c r="CM226" s="3"/>
-    </row>
-    <row r="227" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN226" s="3"/>
+      <c r="CO226" s="3"/>
+      <c r="CP226" s="3"/>
+      <c r="CQ226" s="3"/>
+    </row>
+    <row r="227" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C227" s="3"/>
       <c r="D227" s="3"/>
       <c r="E227" s="3"/>
@@ -22053,8 +23324,12 @@
       <c r="CK227" s="3"/>
       <c r="CL227" s="3"/>
       <c r="CM227" s="3"/>
-    </row>
-    <row r="228" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN227" s="3"/>
+      <c r="CO227" s="3"/>
+      <c r="CP227" s="3"/>
+      <c r="CQ227" s="3"/>
+    </row>
+    <row r="228" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C228" s="3"/>
       <c r="D228" s="3"/>
       <c r="E228" s="3"/>
@@ -22144,8 +23419,12 @@
       <c r="CK228" s="3"/>
       <c r="CL228" s="3"/>
       <c r="CM228" s="3"/>
-    </row>
-    <row r="229" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN228" s="3"/>
+      <c r="CO228" s="3"/>
+      <c r="CP228" s="3"/>
+      <c r="CQ228" s="3"/>
+    </row>
+    <row r="229" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
       <c r="E229" s="3"/>
@@ -22235,8 +23514,12 @@
       <c r="CK229" s="3"/>
       <c r="CL229" s="3"/>
       <c r="CM229" s="3"/>
-    </row>
-    <row r="230" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN229" s="3"/>
+      <c r="CO229" s="3"/>
+      <c r="CP229" s="3"/>
+      <c r="CQ229" s="3"/>
+    </row>
+    <row r="230" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C230" s="3"/>
       <c r="D230" s="3"/>
       <c r="E230" s="3"/>
@@ -22326,8 +23609,12 @@
       <c r="CK230" s="3"/>
       <c r="CL230" s="3"/>
       <c r="CM230" s="3"/>
-    </row>
-    <row r="231" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN230" s="3"/>
+      <c r="CO230" s="3"/>
+      <c r="CP230" s="3"/>
+      <c r="CQ230" s="3"/>
+    </row>
+    <row r="231" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C231" s="3"/>
       <c r="D231" s="3"/>
       <c r="E231" s="3"/>
@@ -22417,8 +23704,12 @@
       <c r="CK231" s="3"/>
       <c r="CL231" s="3"/>
       <c r="CM231" s="3"/>
-    </row>
-    <row r="232" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN231" s="3"/>
+      <c r="CO231" s="3"/>
+      <c r="CP231" s="3"/>
+      <c r="CQ231" s="3"/>
+    </row>
+    <row r="232" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
       <c r="E232" s="3"/>
@@ -22508,8 +23799,12 @@
       <c r="CK232" s="3"/>
       <c r="CL232" s="3"/>
       <c r="CM232" s="3"/>
-    </row>
-    <row r="233" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN232" s="3"/>
+      <c r="CO232" s="3"/>
+      <c r="CP232" s="3"/>
+      <c r="CQ232" s="3"/>
+    </row>
+    <row r="233" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C233" s="3"/>
       <c r="D233" s="3"/>
       <c r="E233" s="3"/>
@@ -22599,8 +23894,12 @@
       <c r="CK233" s="3"/>
       <c r="CL233" s="3"/>
       <c r="CM233" s="3"/>
-    </row>
-    <row r="234" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN233" s="3"/>
+      <c r="CO233" s="3"/>
+      <c r="CP233" s="3"/>
+      <c r="CQ233" s="3"/>
+    </row>
+    <row r="234" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C234" s="3"/>
       <c r="D234" s="3"/>
       <c r="E234" s="3"/>
@@ -22690,8 +23989,12 @@
       <c r="CK234" s="3"/>
       <c r="CL234" s="3"/>
       <c r="CM234" s="3"/>
-    </row>
-    <row r="235" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN234" s="3"/>
+      <c r="CO234" s="3"/>
+      <c r="CP234" s="3"/>
+      <c r="CQ234" s="3"/>
+    </row>
+    <row r="235" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C235" s="3"/>
       <c r="D235" s="3"/>
       <c r="E235" s="3"/>
@@ -22781,8 +24084,12 @@
       <c r="CK235" s="3"/>
       <c r="CL235" s="3"/>
       <c r="CM235" s="3"/>
-    </row>
-    <row r="236" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN235" s="3"/>
+      <c r="CO235" s="3"/>
+      <c r="CP235" s="3"/>
+      <c r="CQ235" s="3"/>
+    </row>
+    <row r="236" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C236" s="3"/>
       <c r="D236" s="3"/>
       <c r="E236" s="3"/>
@@ -22872,8 +24179,12 @@
       <c r="CK236" s="3"/>
       <c r="CL236" s="3"/>
       <c r="CM236" s="3"/>
-    </row>
-    <row r="237" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN236" s="3"/>
+      <c r="CO236" s="3"/>
+      <c r="CP236" s="3"/>
+      <c r="CQ236" s="3"/>
+    </row>
+    <row r="237" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
       <c r="E237" s="3"/>
@@ -22963,8 +24274,12 @@
       <c r="CK237" s="3"/>
       <c r="CL237" s="3"/>
       <c r="CM237" s="3"/>
-    </row>
-    <row r="238" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN237" s="3"/>
+      <c r="CO237" s="3"/>
+      <c r="CP237" s="3"/>
+      <c r="CQ237" s="3"/>
+    </row>
+    <row r="238" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C238" s="3"/>
       <c r="D238" s="3"/>
       <c r="E238" s="3"/>
@@ -23054,8 +24369,12 @@
       <c r="CK238" s="3"/>
       <c r="CL238" s="3"/>
       <c r="CM238" s="3"/>
-    </row>
-    <row r="239" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN238" s="3"/>
+      <c r="CO238" s="3"/>
+      <c r="CP238" s="3"/>
+      <c r="CQ238" s="3"/>
+    </row>
+    <row r="239" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C239" s="3"/>
       <c r="D239" s="3"/>
       <c r="E239" s="3"/>
@@ -23145,8 +24464,12 @@
       <c r="CK239" s="3"/>
       <c r="CL239" s="3"/>
       <c r="CM239" s="3"/>
-    </row>
-    <row r="240" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN239" s="3"/>
+      <c r="CO239" s="3"/>
+      <c r="CP239" s="3"/>
+      <c r="CQ239" s="3"/>
+    </row>
+    <row r="240" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C240" s="3"/>
       <c r="D240" s="3"/>
       <c r="E240" s="3"/>
@@ -23236,8 +24559,12 @@
       <c r="CK240" s="3"/>
       <c r="CL240" s="3"/>
       <c r="CM240" s="3"/>
-    </row>
-    <row r="241" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN240" s="3"/>
+      <c r="CO240" s="3"/>
+      <c r="CP240" s="3"/>
+      <c r="CQ240" s="3"/>
+    </row>
+    <row r="241" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C241" s="3"/>
       <c r="D241" s="3"/>
       <c r="E241" s="3"/>
@@ -23327,8 +24654,12 @@
       <c r="CK241" s="3"/>
       <c r="CL241" s="3"/>
       <c r="CM241" s="3"/>
-    </row>
-    <row r="242" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN241" s="3"/>
+      <c r="CO241" s="3"/>
+      <c r="CP241" s="3"/>
+      <c r="CQ241" s="3"/>
+    </row>
+    <row r="242" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
       <c r="E242" s="3"/>
@@ -23418,8 +24749,12 @@
       <c r="CK242" s="3"/>
       <c r="CL242" s="3"/>
       <c r="CM242" s="3"/>
-    </row>
-    <row r="243" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN242" s="3"/>
+      <c r="CO242" s="3"/>
+      <c r="CP242" s="3"/>
+      <c r="CQ242" s="3"/>
+    </row>
+    <row r="243" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C243" s="3"/>
       <c r="D243" s="3"/>
       <c r="E243" s="3"/>
@@ -23509,8 +24844,12 @@
       <c r="CK243" s="3"/>
       <c r="CL243" s="3"/>
       <c r="CM243" s="3"/>
-    </row>
-    <row r="244" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN243" s="3"/>
+      <c r="CO243" s="3"/>
+      <c r="CP243" s="3"/>
+      <c r="CQ243" s="3"/>
+    </row>
+    <row r="244" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C244" s="3"/>
       <c r="D244" s="3"/>
       <c r="E244" s="3"/>
@@ -23600,8 +24939,12 @@
       <c r="CK244" s="3"/>
       <c r="CL244" s="3"/>
       <c r="CM244" s="3"/>
-    </row>
-    <row r="245" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN244" s="3"/>
+      <c r="CO244" s="3"/>
+      <c r="CP244" s="3"/>
+      <c r="CQ244" s="3"/>
+    </row>
+    <row r="245" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C245" s="3"/>
       <c r="D245" s="3"/>
       <c r="E245" s="3"/>
@@ -23691,8 +25034,12 @@
       <c r="CK245" s="3"/>
       <c r="CL245" s="3"/>
       <c r="CM245" s="3"/>
-    </row>
-    <row r="246" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN245" s="3"/>
+      <c r="CO245" s="3"/>
+      <c r="CP245" s="3"/>
+      <c r="CQ245" s="3"/>
+    </row>
+    <row r="246" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C246" s="3"/>
       <c r="D246" s="3"/>
       <c r="E246" s="3"/>
@@ -23782,8 +25129,12 @@
       <c r="CK246" s="3"/>
       <c r="CL246" s="3"/>
       <c r="CM246" s="3"/>
-    </row>
-    <row r="247" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN246" s="3"/>
+      <c r="CO246" s="3"/>
+      <c r="CP246" s="3"/>
+      <c r="CQ246" s="3"/>
+    </row>
+    <row r="247" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C247" s="3"/>
       <c r="D247" s="3"/>
       <c r="E247" s="3"/>
@@ -23873,8 +25224,12 @@
       <c r="CK247" s="3"/>
       <c r="CL247" s="3"/>
       <c r="CM247" s="3"/>
-    </row>
-    <row r="248" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN247" s="3"/>
+      <c r="CO247" s="3"/>
+      <c r="CP247" s="3"/>
+      <c r="CQ247" s="3"/>
+    </row>
+    <row r="248" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C248" s="3"/>
       <c r="D248" s="3"/>
       <c r="E248" s="3"/>
@@ -23964,8 +25319,12 @@
       <c r="CK248" s="3"/>
       <c r="CL248" s="3"/>
       <c r="CM248" s="3"/>
-    </row>
-    <row r="249" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN248" s="3"/>
+      <c r="CO248" s="3"/>
+      <c r="CP248" s="3"/>
+      <c r="CQ248" s="3"/>
+    </row>
+    <row r="249" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C249" s="3"/>
       <c r="D249" s="3"/>
       <c r="E249" s="3"/>
@@ -24055,8 +25414,12 @@
       <c r="CK249" s="3"/>
       <c r="CL249" s="3"/>
       <c r="CM249" s="3"/>
-    </row>
-    <row r="250" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN249" s="3"/>
+      <c r="CO249" s="3"/>
+      <c r="CP249" s="3"/>
+      <c r="CQ249" s="3"/>
+    </row>
+    <row r="250" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C250" s="3"/>
       <c r="D250" s="3"/>
       <c r="E250" s="3"/>
@@ -24146,8 +25509,12 @@
       <c r="CK250" s="3"/>
       <c r="CL250" s="3"/>
       <c r="CM250" s="3"/>
-    </row>
-    <row r="251" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN250" s="3"/>
+      <c r="CO250" s="3"/>
+      <c r="CP250" s="3"/>
+      <c r="CQ250" s="3"/>
+    </row>
+    <row r="251" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C251" s="3"/>
       <c r="D251" s="3"/>
       <c r="E251" s="3"/>
@@ -24237,8 +25604,12 @@
       <c r="CK251" s="3"/>
       <c r="CL251" s="3"/>
       <c r="CM251" s="3"/>
-    </row>
-    <row r="252" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN251" s="3"/>
+      <c r="CO251" s="3"/>
+      <c r="CP251" s="3"/>
+      <c r="CQ251" s="3"/>
+    </row>
+    <row r="252" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C252" s="3"/>
       <c r="D252" s="3"/>
       <c r="E252" s="3"/>
@@ -24328,8 +25699,12 @@
       <c r="CK252" s="3"/>
       <c r="CL252" s="3"/>
       <c r="CM252" s="3"/>
-    </row>
-    <row r="253" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN252" s="3"/>
+      <c r="CO252" s="3"/>
+      <c r="CP252" s="3"/>
+      <c r="CQ252" s="3"/>
+    </row>
+    <row r="253" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C253" s="3"/>
       <c r="D253" s="3"/>
       <c r="E253" s="3"/>
@@ -24419,8 +25794,12 @@
       <c r="CK253" s="3"/>
       <c r="CL253" s="3"/>
       <c r="CM253" s="3"/>
-    </row>
-    <row r="254" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN253" s="3"/>
+      <c r="CO253" s="3"/>
+      <c r="CP253" s="3"/>
+      <c r="CQ253" s="3"/>
+    </row>
+    <row r="254" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C254" s="3"/>
       <c r="D254" s="3"/>
       <c r="E254" s="3"/>
@@ -24510,8 +25889,12 @@
       <c r="CK254" s="3"/>
       <c r="CL254" s="3"/>
       <c r="CM254" s="3"/>
-    </row>
-    <row r="255" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN254" s="3"/>
+      <c r="CO254" s="3"/>
+      <c r="CP254" s="3"/>
+      <c r="CQ254" s="3"/>
+    </row>
+    <row r="255" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C255" s="3"/>
       <c r="D255" s="3"/>
       <c r="E255" s="3"/>
@@ -24601,8 +25984,12 @@
       <c r="CK255" s="3"/>
       <c r="CL255" s="3"/>
       <c r="CM255" s="3"/>
-    </row>
-    <row r="256" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN255" s="3"/>
+      <c r="CO255" s="3"/>
+      <c r="CP255" s="3"/>
+      <c r="CQ255" s="3"/>
+    </row>
+    <row r="256" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C256" s="3"/>
       <c r="D256" s="3"/>
       <c r="E256" s="3"/>
@@ -24692,8 +26079,12 @@
       <c r="CK256" s="3"/>
       <c r="CL256" s="3"/>
       <c r="CM256" s="3"/>
-    </row>
-    <row r="257" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN256" s="3"/>
+      <c r="CO256" s="3"/>
+      <c r="CP256" s="3"/>
+      <c r="CQ256" s="3"/>
+    </row>
+    <row r="257" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C257" s="3"/>
       <c r="D257" s="3"/>
       <c r="E257" s="3"/>
@@ -24783,8 +26174,12 @@
       <c r="CK257" s="3"/>
       <c r="CL257" s="3"/>
       <c r="CM257" s="3"/>
-    </row>
-    <row r="258" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN257" s="3"/>
+      <c r="CO257" s="3"/>
+      <c r="CP257" s="3"/>
+      <c r="CQ257" s="3"/>
+    </row>
+    <row r="258" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C258" s="3"/>
       <c r="D258" s="3"/>
       <c r="E258" s="3"/>
@@ -24874,8 +26269,12 @@
       <c r="CK258" s="3"/>
       <c r="CL258" s="3"/>
       <c r="CM258" s="3"/>
-    </row>
-    <row r="259" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN258" s="3"/>
+      <c r="CO258" s="3"/>
+      <c r="CP258" s="3"/>
+      <c r="CQ258" s="3"/>
+    </row>
+    <row r="259" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C259" s="3"/>
       <c r="D259" s="3"/>
       <c r="E259" s="3"/>
@@ -24965,8 +26364,12 @@
       <c r="CK259" s="3"/>
       <c r="CL259" s="3"/>
       <c r="CM259" s="3"/>
-    </row>
-    <row r="260" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN259" s="3"/>
+      <c r="CO259" s="3"/>
+      <c r="CP259" s="3"/>
+      <c r="CQ259" s="3"/>
+    </row>
+    <row r="260" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C260" s="3"/>
       <c r="D260" s="3"/>
       <c r="E260" s="3"/>
@@ -25056,8 +26459,12 @@
       <c r="CK260" s="3"/>
       <c r="CL260" s="3"/>
       <c r="CM260" s="3"/>
-    </row>
-    <row r="261" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN260" s="3"/>
+      <c r="CO260" s="3"/>
+      <c r="CP260" s="3"/>
+      <c r="CQ260" s="3"/>
+    </row>
+    <row r="261" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C261" s="3"/>
       <c r="D261" s="3"/>
       <c r="E261" s="3"/>
@@ -25147,8 +26554,12 @@
       <c r="CK261" s="3"/>
       <c r="CL261" s="3"/>
       <c r="CM261" s="3"/>
-    </row>
-    <row r="262" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN261" s="3"/>
+      <c r="CO261" s="3"/>
+      <c r="CP261" s="3"/>
+      <c r="CQ261" s="3"/>
+    </row>
+    <row r="262" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C262" s="3"/>
       <c r="D262" s="3"/>
       <c r="E262" s="3"/>
@@ -25238,8 +26649,12 @@
       <c r="CK262" s="3"/>
       <c r="CL262" s="3"/>
       <c r="CM262" s="3"/>
-    </row>
-    <row r="263" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN262" s="3"/>
+      <c r="CO262" s="3"/>
+      <c r="CP262" s="3"/>
+      <c r="CQ262" s="3"/>
+    </row>
+    <row r="263" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C263" s="3"/>
       <c r="D263" s="3"/>
       <c r="E263" s="3"/>
@@ -25329,8 +26744,12 @@
       <c r="CK263" s="3"/>
       <c r="CL263" s="3"/>
       <c r="CM263" s="3"/>
-    </row>
-    <row r="264" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN263" s="3"/>
+      <c r="CO263" s="3"/>
+      <c r="CP263" s="3"/>
+      <c r="CQ263" s="3"/>
+    </row>
+    <row r="264" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C264" s="3"/>
       <c r="D264" s="3"/>
       <c r="E264" s="3"/>
@@ -25420,8 +26839,12 @@
       <c r="CK264" s="3"/>
       <c r="CL264" s="3"/>
       <c r="CM264" s="3"/>
-    </row>
-    <row r="265" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN264" s="3"/>
+      <c r="CO264" s="3"/>
+      <c r="CP264" s="3"/>
+      <c r="CQ264" s="3"/>
+    </row>
+    <row r="265" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C265" s="3"/>
       <c r="D265" s="3"/>
       <c r="E265" s="3"/>
@@ -25511,8 +26934,12 @@
       <c r="CK265" s="3"/>
       <c r="CL265" s="3"/>
       <c r="CM265" s="3"/>
-    </row>
-    <row r="266" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN265" s="3"/>
+      <c r="CO265" s="3"/>
+      <c r="CP265" s="3"/>
+      <c r="CQ265" s="3"/>
+    </row>
+    <row r="266" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C266" s="3"/>
       <c r="D266" s="3"/>
       <c r="E266" s="3"/>
@@ -25602,8 +27029,12 @@
       <c r="CK266" s="3"/>
       <c r="CL266" s="3"/>
       <c r="CM266" s="3"/>
-    </row>
-    <row r="267" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN266" s="3"/>
+      <c r="CO266" s="3"/>
+      <c r="CP266" s="3"/>
+      <c r="CQ266" s="3"/>
+    </row>
+    <row r="267" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C267" s="3"/>
       <c r="D267" s="3"/>
       <c r="E267" s="3"/>
@@ -25693,8 +27124,12 @@
       <c r="CK267" s="3"/>
       <c r="CL267" s="3"/>
       <c r="CM267" s="3"/>
-    </row>
-    <row r="268" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN267" s="3"/>
+      <c r="CO267" s="3"/>
+      <c r="CP267" s="3"/>
+      <c r="CQ267" s="3"/>
+    </row>
+    <row r="268" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C268" s="3"/>
       <c r="D268" s="3"/>
       <c r="E268" s="3"/>
@@ -25784,8 +27219,12 @@
       <c r="CK268" s="3"/>
       <c r="CL268" s="3"/>
       <c r="CM268" s="3"/>
-    </row>
-    <row r="269" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN268" s="3"/>
+      <c r="CO268" s="3"/>
+      <c r="CP268" s="3"/>
+      <c r="CQ268" s="3"/>
+    </row>
+    <row r="269" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C269" s="3"/>
       <c r="D269" s="3"/>
       <c r="E269" s="3"/>
@@ -25875,8 +27314,12 @@
       <c r="CK269" s="3"/>
       <c r="CL269" s="3"/>
       <c r="CM269" s="3"/>
-    </row>
-    <row r="270" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN269" s="3"/>
+      <c r="CO269" s="3"/>
+      <c r="CP269" s="3"/>
+      <c r="CQ269" s="3"/>
+    </row>
+    <row r="270" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C270" s="3"/>
       <c r="D270" s="3"/>
       <c r="E270" s="3"/>
@@ -25966,8 +27409,12 @@
       <c r="CK270" s="3"/>
       <c r="CL270" s="3"/>
       <c r="CM270" s="3"/>
-    </row>
-    <row r="271" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN270" s="3"/>
+      <c r="CO270" s="3"/>
+      <c r="CP270" s="3"/>
+      <c r="CQ270" s="3"/>
+    </row>
+    <row r="271" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C271" s="3"/>
       <c r="D271" s="3"/>
       <c r="E271" s="3"/>
@@ -26057,8 +27504,12 @@
       <c r="CK271" s="3"/>
       <c r="CL271" s="3"/>
       <c r="CM271" s="3"/>
-    </row>
-    <row r="272" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN271" s="3"/>
+      <c r="CO271" s="3"/>
+      <c r="CP271" s="3"/>
+      <c r="CQ271" s="3"/>
+    </row>
+    <row r="272" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C272" s="3"/>
       <c r="D272" s="3"/>
       <c r="E272" s="3"/>
@@ -26148,8 +27599,12 @@
       <c r="CK272" s="3"/>
       <c r="CL272" s="3"/>
       <c r="CM272" s="3"/>
-    </row>
-    <row r="273" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN272" s="3"/>
+      <c r="CO272" s="3"/>
+      <c r="CP272" s="3"/>
+      <c r="CQ272" s="3"/>
+    </row>
+    <row r="273" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C273" s="3"/>
       <c r="D273" s="3"/>
       <c r="E273" s="3"/>
@@ -26239,8 +27694,12 @@
       <c r="CK273" s="3"/>
       <c r="CL273" s="3"/>
       <c r="CM273" s="3"/>
-    </row>
-    <row r="274" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN273" s="3"/>
+      <c r="CO273" s="3"/>
+      <c r="CP273" s="3"/>
+      <c r="CQ273" s="3"/>
+    </row>
+    <row r="274" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C274" s="3"/>
       <c r="D274" s="3"/>
       <c r="E274" s="3"/>
@@ -26330,8 +27789,12 @@
       <c r="CK274" s="3"/>
       <c r="CL274" s="3"/>
       <c r="CM274" s="3"/>
-    </row>
-    <row r="275" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN274" s="3"/>
+      <c r="CO274" s="3"/>
+      <c r="CP274" s="3"/>
+      <c r="CQ274" s="3"/>
+    </row>
+    <row r="275" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C275" s="3"/>
       <c r="D275" s="3"/>
       <c r="E275" s="3"/>
@@ -26421,8 +27884,12 @@
       <c r="CK275" s="3"/>
       <c r="CL275" s="3"/>
       <c r="CM275" s="3"/>
-    </row>
-    <row r="276" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN275" s="3"/>
+      <c r="CO275" s="3"/>
+      <c r="CP275" s="3"/>
+      <c r="CQ275" s="3"/>
+    </row>
+    <row r="276" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C276" s="3"/>
       <c r="D276" s="3"/>
       <c r="E276" s="3"/>
@@ -26512,8 +27979,12 @@
       <c r="CK276" s="3"/>
       <c r="CL276" s="3"/>
       <c r="CM276" s="3"/>
-    </row>
-    <row r="277" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN276" s="3"/>
+      <c r="CO276" s="3"/>
+      <c r="CP276" s="3"/>
+      <c r="CQ276" s="3"/>
+    </row>
+    <row r="277" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C277" s="3"/>
       <c r="D277" s="3"/>
       <c r="E277" s="3"/>
@@ -26603,8 +28074,12 @@
       <c r="CK277" s="3"/>
       <c r="CL277" s="3"/>
       <c r="CM277" s="3"/>
-    </row>
-    <row r="278" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN277" s="3"/>
+      <c r="CO277" s="3"/>
+      <c r="CP277" s="3"/>
+      <c r="CQ277" s="3"/>
+    </row>
+    <row r="278" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C278" s="3"/>
       <c r="D278" s="3"/>
       <c r="E278" s="3"/>
@@ -26694,8 +28169,12 @@
       <c r="CK278" s="3"/>
       <c r="CL278" s="3"/>
       <c r="CM278" s="3"/>
-    </row>
-    <row r="279" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN278" s="3"/>
+      <c r="CO278" s="3"/>
+      <c r="CP278" s="3"/>
+      <c r="CQ278" s="3"/>
+    </row>
+    <row r="279" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C279" s="3"/>
       <c r="D279" s="3"/>
       <c r="E279" s="3"/>
@@ -26785,8 +28264,12 @@
       <c r="CK279" s="3"/>
       <c r="CL279" s="3"/>
       <c r="CM279" s="3"/>
-    </row>
-    <row r="280" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN279" s="3"/>
+      <c r="CO279" s="3"/>
+      <c r="CP279" s="3"/>
+      <c r="CQ279" s="3"/>
+    </row>
+    <row r="280" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C280" s="3"/>
       <c r="D280" s="3"/>
       <c r="E280" s="3"/>
@@ -26876,8 +28359,12 @@
       <c r="CK280" s="3"/>
       <c r="CL280" s="3"/>
       <c r="CM280" s="3"/>
-    </row>
-    <row r="281" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN280" s="3"/>
+      <c r="CO280" s="3"/>
+      <c r="CP280" s="3"/>
+      <c r="CQ280" s="3"/>
+    </row>
+    <row r="281" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C281" s="3"/>
       <c r="D281" s="3"/>
       <c r="E281" s="3"/>
@@ -26967,8 +28454,12 @@
       <c r="CK281" s="3"/>
       <c r="CL281" s="3"/>
       <c r="CM281" s="3"/>
-    </row>
-    <row r="282" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN281" s="3"/>
+      <c r="CO281" s="3"/>
+      <c r="CP281" s="3"/>
+      <c r="CQ281" s="3"/>
+    </row>
+    <row r="282" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C282" s="3"/>
       <c r="D282" s="3"/>
       <c r="E282" s="3"/>
@@ -27058,8 +28549,12 @@
       <c r="CK282" s="3"/>
       <c r="CL282" s="3"/>
       <c r="CM282" s="3"/>
-    </row>
-    <row r="283" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN282" s="3"/>
+      <c r="CO282" s="3"/>
+      <c r="CP282" s="3"/>
+      <c r="CQ282" s="3"/>
+    </row>
+    <row r="283" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C283" s="3"/>
       <c r="D283" s="3"/>
       <c r="E283" s="3"/>
@@ -27149,8 +28644,12 @@
       <c r="CK283" s="3"/>
       <c r="CL283" s="3"/>
       <c r="CM283" s="3"/>
-    </row>
-    <row r="284" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN283" s="3"/>
+      <c r="CO283" s="3"/>
+      <c r="CP283" s="3"/>
+      <c r="CQ283" s="3"/>
+    </row>
+    <row r="284" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C284" s="3"/>
       <c r="D284" s="3"/>
       <c r="E284" s="3"/>
@@ -27240,8 +28739,12 @@
       <c r="CK284" s="3"/>
       <c r="CL284" s="3"/>
       <c r="CM284" s="3"/>
-    </row>
-    <row r="285" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN284" s="3"/>
+      <c r="CO284" s="3"/>
+      <c r="CP284" s="3"/>
+      <c r="CQ284" s="3"/>
+    </row>
+    <row r="285" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C285" s="3"/>
       <c r="D285" s="3"/>
       <c r="E285" s="3"/>
@@ -27331,8 +28834,12 @@
       <c r="CK285" s="3"/>
       <c r="CL285" s="3"/>
       <c r="CM285" s="3"/>
-    </row>
-    <row r="286" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN285" s="3"/>
+      <c r="CO285" s="3"/>
+      <c r="CP285" s="3"/>
+      <c r="CQ285" s="3"/>
+    </row>
+    <row r="286" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C286" s="3"/>
       <c r="D286" s="3"/>
       <c r="E286" s="3"/>
@@ -27422,8 +28929,12 @@
       <c r="CK286" s="3"/>
       <c r="CL286" s="3"/>
       <c r="CM286" s="3"/>
-    </row>
-    <row r="287" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN286" s="3"/>
+      <c r="CO286" s="3"/>
+      <c r="CP286" s="3"/>
+      <c r="CQ286" s="3"/>
+    </row>
+    <row r="287" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C287" s="3"/>
       <c r="D287" s="3"/>
       <c r="E287" s="3"/>
@@ -27513,8 +29024,12 @@
       <c r="CK287" s="3"/>
       <c r="CL287" s="3"/>
       <c r="CM287" s="3"/>
-    </row>
-    <row r="288" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN287" s="3"/>
+      <c r="CO287" s="3"/>
+      <c r="CP287" s="3"/>
+      <c r="CQ287" s="3"/>
+    </row>
+    <row r="288" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C288" s="3"/>
       <c r="D288" s="3"/>
       <c r="E288" s="3"/>
@@ -27604,8 +29119,12 @@
       <c r="CK288" s="3"/>
       <c r="CL288" s="3"/>
       <c r="CM288" s="3"/>
-    </row>
-    <row r="289" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN288" s="3"/>
+      <c r="CO288" s="3"/>
+      <c r="CP288" s="3"/>
+      <c r="CQ288" s="3"/>
+    </row>
+    <row r="289" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C289" s="3"/>
       <c r="D289" s="3"/>
       <c r="E289" s="3"/>
@@ -27695,8 +29214,12 @@
       <c r="CK289" s="3"/>
       <c r="CL289" s="3"/>
       <c r="CM289" s="3"/>
-    </row>
-    <row r="290" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN289" s="3"/>
+      <c r="CO289" s="3"/>
+      <c r="CP289" s="3"/>
+      <c r="CQ289" s="3"/>
+    </row>
+    <row r="290" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C290" s="3"/>
       <c r="D290" s="3"/>
       <c r="E290" s="3"/>
@@ -27786,8 +29309,12 @@
       <c r="CK290" s="3"/>
       <c r="CL290" s="3"/>
       <c r="CM290" s="3"/>
-    </row>
-    <row r="291" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN290" s="3"/>
+      <c r="CO290" s="3"/>
+      <c r="CP290" s="3"/>
+      <c r="CQ290" s="3"/>
+    </row>
+    <row r="291" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C291" s="3"/>
       <c r="D291" s="3"/>
       <c r="E291" s="3"/>
@@ -27877,8 +29404,12 @@
       <c r="CK291" s="3"/>
       <c r="CL291" s="3"/>
       <c r="CM291" s="3"/>
-    </row>
-    <row r="292" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN291" s="3"/>
+      <c r="CO291" s="3"/>
+      <c r="CP291" s="3"/>
+      <c r="CQ291" s="3"/>
+    </row>
+    <row r="292" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C292" s="3"/>
       <c r="D292" s="3"/>
       <c r="E292" s="3"/>
@@ -27968,8 +29499,12 @@
       <c r="CK292" s="3"/>
       <c r="CL292" s="3"/>
       <c r="CM292" s="3"/>
-    </row>
-    <row r="293" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN292" s="3"/>
+      <c r="CO292" s="3"/>
+      <c r="CP292" s="3"/>
+      <c r="CQ292" s="3"/>
+    </row>
+    <row r="293" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C293" s="3"/>
       <c r="D293" s="3"/>
       <c r="E293" s="3"/>
@@ -28059,8 +29594,12 @@
       <c r="CK293" s="3"/>
       <c r="CL293" s="3"/>
       <c r="CM293" s="3"/>
-    </row>
-    <row r="294" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN293" s="3"/>
+      <c r="CO293" s="3"/>
+      <c r="CP293" s="3"/>
+      <c r="CQ293" s="3"/>
+    </row>
+    <row r="294" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C294" s="3"/>
       <c r="D294" s="3"/>
       <c r="E294" s="3"/>
@@ -28150,8 +29689,12 @@
       <c r="CK294" s="3"/>
       <c r="CL294" s="3"/>
       <c r="CM294" s="3"/>
-    </row>
-    <row r="295" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN294" s="3"/>
+      <c r="CO294" s="3"/>
+      <c r="CP294" s="3"/>
+      <c r="CQ294" s="3"/>
+    </row>
+    <row r="295" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C295" s="3"/>
       <c r="D295" s="3"/>
       <c r="E295" s="3"/>
@@ -28241,8 +29784,12 @@
       <c r="CK295" s="3"/>
       <c r="CL295" s="3"/>
       <c r="CM295" s="3"/>
-    </row>
-    <row r="296" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN295" s="3"/>
+      <c r="CO295" s="3"/>
+      <c r="CP295" s="3"/>
+      <c r="CQ295" s="3"/>
+    </row>
+    <row r="296" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C296" s="3"/>
       <c r="D296" s="3"/>
       <c r="E296" s="3"/>
@@ -28332,8 +29879,12 @@
       <c r="CK296" s="3"/>
       <c r="CL296" s="3"/>
       <c r="CM296" s="3"/>
-    </row>
-    <row r="297" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN296" s="3"/>
+      <c r="CO296" s="3"/>
+      <c r="CP296" s="3"/>
+      <c r="CQ296" s="3"/>
+    </row>
+    <row r="297" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C297" s="3"/>
       <c r="D297" s="3"/>
       <c r="E297" s="3"/>
@@ -28423,8 +29974,12 @@
       <c r="CK297" s="3"/>
       <c r="CL297" s="3"/>
       <c r="CM297" s="3"/>
-    </row>
-    <row r="298" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN297" s="3"/>
+      <c r="CO297" s="3"/>
+      <c r="CP297" s="3"/>
+      <c r="CQ297" s="3"/>
+    </row>
+    <row r="298" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C298" s="3"/>
       <c r="D298" s="3"/>
       <c r="E298" s="3"/>
@@ -28514,8 +30069,12 @@
       <c r="CK298" s="3"/>
       <c r="CL298" s="3"/>
       <c r="CM298" s="3"/>
-    </row>
-    <row r="299" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN298" s="3"/>
+      <c r="CO298" s="3"/>
+      <c r="CP298" s="3"/>
+      <c r="CQ298" s="3"/>
+    </row>
+    <row r="299" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C299" s="3"/>
       <c r="D299" s="3"/>
       <c r="E299" s="3"/>
@@ -28605,8 +30164,12 @@
       <c r="CK299" s="3"/>
       <c r="CL299" s="3"/>
       <c r="CM299" s="3"/>
-    </row>
-    <row r="300" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN299" s="3"/>
+      <c r="CO299" s="3"/>
+      <c r="CP299" s="3"/>
+      <c r="CQ299" s="3"/>
+    </row>
+    <row r="300" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C300" s="3"/>
       <c r="D300" s="3"/>
       <c r="E300" s="3"/>
@@ -28696,8 +30259,12 @@
       <c r="CK300" s="3"/>
       <c r="CL300" s="3"/>
       <c r="CM300" s="3"/>
-    </row>
-    <row r="301" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN300" s="3"/>
+      <c r="CO300" s="3"/>
+      <c r="CP300" s="3"/>
+      <c r="CQ300" s="3"/>
+    </row>
+    <row r="301" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C301" s="3"/>
       <c r="D301" s="3"/>
       <c r="E301" s="3"/>
@@ -28787,8 +30354,12 @@
       <c r="CK301" s="3"/>
       <c r="CL301" s="3"/>
       <c r="CM301" s="3"/>
-    </row>
-    <row r="302" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN301" s="3"/>
+      <c r="CO301" s="3"/>
+      <c r="CP301" s="3"/>
+      <c r="CQ301" s="3"/>
+    </row>
+    <row r="302" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C302" s="3"/>
       <c r="D302" s="3"/>
       <c r="E302" s="3"/>
@@ -28878,8 +30449,12 @@
       <c r="CK302" s="3"/>
       <c r="CL302" s="3"/>
       <c r="CM302" s="3"/>
-    </row>
-    <row r="303" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN302" s="3"/>
+      <c r="CO302" s="3"/>
+      <c r="CP302" s="3"/>
+      <c r="CQ302" s="3"/>
+    </row>
+    <row r="303" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C303" s="3"/>
       <c r="D303" s="3"/>
       <c r="E303" s="3"/>
@@ -28969,8 +30544,12 @@
       <c r="CK303" s="3"/>
       <c r="CL303" s="3"/>
       <c r="CM303" s="3"/>
-    </row>
-    <row r="304" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN303" s="3"/>
+      <c r="CO303" s="3"/>
+      <c r="CP303" s="3"/>
+      <c r="CQ303" s="3"/>
+    </row>
+    <row r="304" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C304" s="3"/>
       <c r="D304" s="3"/>
       <c r="E304" s="3"/>
@@ -29060,8 +30639,12 @@
       <c r="CK304" s="3"/>
       <c r="CL304" s="3"/>
       <c r="CM304" s="3"/>
-    </row>
-    <row r="305" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN304" s="3"/>
+      <c r="CO304" s="3"/>
+      <c r="CP304" s="3"/>
+      <c r="CQ304" s="3"/>
+    </row>
+    <row r="305" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C305" s="3"/>
       <c r="D305" s="3"/>
       <c r="E305" s="3"/>
@@ -29151,8 +30734,12 @@
       <c r="CK305" s="3"/>
       <c r="CL305" s="3"/>
       <c r="CM305" s="3"/>
-    </row>
-    <row r="306" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN305" s="3"/>
+      <c r="CO305" s="3"/>
+      <c r="CP305" s="3"/>
+      <c r="CQ305" s="3"/>
+    </row>
+    <row r="306" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C306" s="3"/>
       <c r="D306" s="3"/>
       <c r="E306" s="3"/>
@@ -29242,8 +30829,12 @@
       <c r="CK306" s="3"/>
       <c r="CL306" s="3"/>
       <c r="CM306" s="3"/>
-    </row>
-    <row r="307" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN306" s="3"/>
+      <c r="CO306" s="3"/>
+      <c r="CP306" s="3"/>
+      <c r="CQ306" s="3"/>
+    </row>
+    <row r="307" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C307" s="3"/>
       <c r="D307" s="3"/>
       <c r="E307" s="3"/>
@@ -29333,8 +30924,12 @@
       <c r="CK307" s="3"/>
       <c r="CL307" s="3"/>
       <c r="CM307" s="3"/>
-    </row>
-    <row r="308" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN307" s="3"/>
+      <c r="CO307" s="3"/>
+      <c r="CP307" s="3"/>
+      <c r="CQ307" s="3"/>
+    </row>
+    <row r="308" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C308" s="3"/>
       <c r="D308" s="3"/>
       <c r="E308" s="3"/>
@@ -29424,8 +31019,12 @@
       <c r="CK308" s="3"/>
       <c r="CL308" s="3"/>
       <c r="CM308" s="3"/>
-    </row>
-    <row r="309" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN308" s="3"/>
+      <c r="CO308" s="3"/>
+      <c r="CP308" s="3"/>
+      <c r="CQ308" s="3"/>
+    </row>
+    <row r="309" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C309" s="3"/>
       <c r="D309" s="3"/>
       <c r="E309" s="3"/>
@@ -29515,8 +31114,12 @@
       <c r="CK309" s="3"/>
       <c r="CL309" s="3"/>
       <c r="CM309" s="3"/>
-    </row>
-    <row r="310" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN309" s="3"/>
+      <c r="CO309" s="3"/>
+      <c r="CP309" s="3"/>
+      <c r="CQ309" s="3"/>
+    </row>
+    <row r="310" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C310" s="3"/>
       <c r="D310" s="3"/>
       <c r="E310" s="3"/>
@@ -29606,8 +31209,12 @@
       <c r="CK310" s="3"/>
       <c r="CL310" s="3"/>
       <c r="CM310" s="3"/>
-    </row>
-    <row r="311" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN310" s="3"/>
+      <c r="CO310" s="3"/>
+      <c r="CP310" s="3"/>
+      <c r="CQ310" s="3"/>
+    </row>
+    <row r="311" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C311" s="3"/>
       <c r="D311" s="3"/>
       <c r="E311" s="3"/>
@@ -29697,8 +31304,12 @@
       <c r="CK311" s="3"/>
       <c r="CL311" s="3"/>
       <c r="CM311" s="3"/>
-    </row>
-    <row r="312" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN311" s="3"/>
+      <c r="CO311" s="3"/>
+      <c r="CP311" s="3"/>
+      <c r="CQ311" s="3"/>
+    </row>
+    <row r="312" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C312" s="3"/>
       <c r="D312" s="3"/>
       <c r="E312" s="3"/>
@@ -29788,8 +31399,12 @@
       <c r="CK312" s="3"/>
       <c r="CL312" s="3"/>
       <c r="CM312" s="3"/>
-    </row>
-    <row r="313" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN312" s="3"/>
+      <c r="CO312" s="3"/>
+      <c r="CP312" s="3"/>
+      <c r="CQ312" s="3"/>
+    </row>
+    <row r="313" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C313" s="3"/>
       <c r="D313" s="3"/>
       <c r="E313" s="3"/>
@@ -29879,8 +31494,12 @@
       <c r="CK313" s="3"/>
       <c r="CL313" s="3"/>
       <c r="CM313" s="3"/>
-    </row>
-    <row r="314" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN313" s="3"/>
+      <c r="CO313" s="3"/>
+      <c r="CP313" s="3"/>
+      <c r="CQ313" s="3"/>
+    </row>
+    <row r="314" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C314" s="3"/>
       <c r="D314" s="3"/>
       <c r="E314" s="3"/>
@@ -29970,8 +31589,12 @@
       <c r="CK314" s="3"/>
       <c r="CL314" s="3"/>
       <c r="CM314" s="3"/>
-    </row>
-    <row r="315" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN314" s="3"/>
+      <c r="CO314" s="3"/>
+      <c r="CP314" s="3"/>
+      <c r="CQ314" s="3"/>
+    </row>
+    <row r="315" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C315" s="3"/>
       <c r="D315" s="3"/>
       <c r="E315" s="3"/>
@@ -30061,8 +31684,12 @@
       <c r="CK315" s="3"/>
       <c r="CL315" s="3"/>
       <c r="CM315" s="3"/>
-    </row>
-    <row r="316" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN315" s="3"/>
+      <c r="CO315" s="3"/>
+      <c r="CP315" s="3"/>
+      <c r="CQ315" s="3"/>
+    </row>
+    <row r="316" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C316" s="3"/>
       <c r="D316" s="3"/>
       <c r="E316" s="3"/>
@@ -30152,8 +31779,12 @@
       <c r="CK316" s="3"/>
       <c r="CL316" s="3"/>
       <c r="CM316" s="3"/>
-    </row>
-    <row r="317" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN316" s="3"/>
+      <c r="CO316" s="3"/>
+      <c r="CP316" s="3"/>
+      <c r="CQ316" s="3"/>
+    </row>
+    <row r="317" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C317" s="3"/>
       <c r="D317" s="3"/>
       <c r="E317" s="3"/>
@@ -30243,8 +31874,12 @@
       <c r="CK317" s="3"/>
       <c r="CL317" s="3"/>
       <c r="CM317" s="3"/>
-    </row>
-    <row r="318" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN317" s="3"/>
+      <c r="CO317" s="3"/>
+      <c r="CP317" s="3"/>
+      <c r="CQ317" s="3"/>
+    </row>
+    <row r="318" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C318" s="3"/>
       <c r="D318" s="3"/>
       <c r="E318" s="3"/>
@@ -30334,8 +31969,12 @@
       <c r="CK318" s="3"/>
       <c r="CL318" s="3"/>
       <c r="CM318" s="3"/>
-    </row>
-    <row r="319" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN318" s="3"/>
+      <c r="CO318" s="3"/>
+      <c r="CP318" s="3"/>
+      <c r="CQ318" s="3"/>
+    </row>
+    <row r="319" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C319" s="3"/>
       <c r="D319" s="3"/>
       <c r="E319" s="3"/>
@@ -30425,8 +32064,12 @@
       <c r="CK319" s="3"/>
       <c r="CL319" s="3"/>
       <c r="CM319" s="3"/>
-    </row>
-    <row r="320" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN319" s="3"/>
+      <c r="CO319" s="3"/>
+      <c r="CP319" s="3"/>
+      <c r="CQ319" s="3"/>
+    </row>
+    <row r="320" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C320" s="3"/>
       <c r="D320" s="3"/>
       <c r="E320" s="3"/>
@@ -30516,8 +32159,12 @@
       <c r="CK320" s="3"/>
       <c r="CL320" s="3"/>
       <c r="CM320" s="3"/>
-    </row>
-    <row r="321" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN320" s="3"/>
+      <c r="CO320" s="3"/>
+      <c r="CP320" s="3"/>
+      <c r="CQ320" s="3"/>
+    </row>
+    <row r="321" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C321" s="3"/>
       <c r="D321" s="3"/>
       <c r="E321" s="3"/>
@@ -30607,8 +32254,12 @@
       <c r="CK321" s="3"/>
       <c r="CL321" s="3"/>
       <c r="CM321" s="3"/>
-    </row>
-    <row r="322" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN321" s="3"/>
+      <c r="CO321" s="3"/>
+      <c r="CP321" s="3"/>
+      <c r="CQ321" s="3"/>
+    </row>
+    <row r="322" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C322" s="3"/>
       <c r="D322" s="3"/>
       <c r="E322" s="3"/>
@@ -30698,8 +32349,12 @@
       <c r="CK322" s="3"/>
       <c r="CL322" s="3"/>
       <c r="CM322" s="3"/>
-    </row>
-    <row r="323" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN322" s="3"/>
+      <c r="CO322" s="3"/>
+      <c r="CP322" s="3"/>
+      <c r="CQ322" s="3"/>
+    </row>
+    <row r="323" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C323" s="3"/>
       <c r="D323" s="3"/>
       <c r="E323" s="3"/>
@@ -30789,8 +32444,12 @@
       <c r="CK323" s="3"/>
       <c r="CL323" s="3"/>
       <c r="CM323" s="3"/>
-    </row>
-    <row r="324" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN323" s="3"/>
+      <c r="CO323" s="3"/>
+      <c r="CP323" s="3"/>
+      <c r="CQ323" s="3"/>
+    </row>
+    <row r="324" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C324" s="3"/>
       <c r="D324" s="3"/>
       <c r="E324" s="3"/>
@@ -30880,8 +32539,12 @@
       <c r="CK324" s="3"/>
       <c r="CL324" s="3"/>
       <c r="CM324" s="3"/>
-    </row>
-    <row r="325" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN324" s="3"/>
+      <c r="CO324" s="3"/>
+      <c r="CP324" s="3"/>
+      <c r="CQ324" s="3"/>
+    </row>
+    <row r="325" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C325" s="3"/>
       <c r="D325" s="3"/>
       <c r="E325" s="3"/>
@@ -30971,8 +32634,12 @@
       <c r="CK325" s="3"/>
       <c r="CL325" s="3"/>
       <c r="CM325" s="3"/>
-    </row>
-    <row r="326" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN325" s="3"/>
+      <c r="CO325" s="3"/>
+      <c r="CP325" s="3"/>
+      <c r="CQ325" s="3"/>
+    </row>
+    <row r="326" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C326" s="3"/>
       <c r="D326" s="3"/>
       <c r="E326" s="3"/>
@@ -31062,8 +32729,12 @@
       <c r="CK326" s="3"/>
       <c r="CL326" s="3"/>
       <c r="CM326" s="3"/>
-    </row>
-    <row r="327" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN326" s="3"/>
+      <c r="CO326" s="3"/>
+      <c r="CP326" s="3"/>
+      <c r="CQ326" s="3"/>
+    </row>
+    <row r="327" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C327" s="3"/>
       <c r="D327" s="3"/>
       <c r="E327" s="3"/>
@@ -31153,8 +32824,12 @@
       <c r="CK327" s="3"/>
       <c r="CL327" s="3"/>
       <c r="CM327" s="3"/>
-    </row>
-    <row r="328" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN327" s="3"/>
+      <c r="CO327" s="3"/>
+      <c r="CP327" s="3"/>
+      <c r="CQ327" s="3"/>
+    </row>
+    <row r="328" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C328" s="3"/>
       <c r="D328" s="3"/>
       <c r="E328" s="3"/>
@@ -31244,8 +32919,12 @@
       <c r="CK328" s="3"/>
       <c r="CL328" s="3"/>
       <c r="CM328" s="3"/>
-    </row>
-    <row r="329" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN328" s="3"/>
+      <c r="CO328" s="3"/>
+      <c r="CP328" s="3"/>
+      <c r="CQ328" s="3"/>
+    </row>
+    <row r="329" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C329" s="3"/>
       <c r="D329" s="3"/>
       <c r="E329" s="3"/>
@@ -31335,8 +33014,12 @@
       <c r="CK329" s="3"/>
       <c r="CL329" s="3"/>
       <c r="CM329" s="3"/>
-    </row>
-    <row r="330" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN329" s="3"/>
+      <c r="CO329" s="3"/>
+      <c r="CP329" s="3"/>
+      <c r="CQ329" s="3"/>
+    </row>
+    <row r="330" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C330" s="3"/>
       <c r="D330" s="3"/>
       <c r="E330" s="3"/>
@@ -31426,8 +33109,12 @@
       <c r="CK330" s="3"/>
       <c r="CL330" s="3"/>
       <c r="CM330" s="3"/>
-    </row>
-    <row r="331" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN330" s="3"/>
+      <c r="CO330" s="3"/>
+      <c r="CP330" s="3"/>
+      <c r="CQ330" s="3"/>
+    </row>
+    <row r="331" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C331" s="3"/>
       <c r="D331" s="3"/>
       <c r="E331" s="3"/>
@@ -31517,8 +33204,12 @@
       <c r="CK331" s="3"/>
       <c r="CL331" s="3"/>
       <c r="CM331" s="3"/>
-    </row>
-    <row r="332" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN331" s="3"/>
+      <c r="CO331" s="3"/>
+      <c r="CP331" s="3"/>
+      <c r="CQ331" s="3"/>
+    </row>
+    <row r="332" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C332" s="3"/>
       <c r="D332" s="3"/>
       <c r="E332" s="3"/>
@@ -31608,8 +33299,12 @@
       <c r="CK332" s="3"/>
       <c r="CL332" s="3"/>
       <c r="CM332" s="3"/>
-    </row>
-    <row r="333" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN332" s="3"/>
+      <c r="CO332" s="3"/>
+      <c r="CP332" s="3"/>
+      <c r="CQ332" s="3"/>
+    </row>
+    <row r="333" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C333" s="3"/>
       <c r="D333" s="3"/>
       <c r="E333" s="3"/>
@@ -31699,8 +33394,12 @@
       <c r="CK333" s="3"/>
       <c r="CL333" s="3"/>
       <c r="CM333" s="3"/>
-    </row>
-    <row r="334" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN333" s="3"/>
+      <c r="CO333" s="3"/>
+      <c r="CP333" s="3"/>
+      <c r="CQ333" s="3"/>
+    </row>
+    <row r="334" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C334" s="3"/>
       <c r="D334" s="3"/>
       <c r="E334" s="3"/>
@@ -31790,8 +33489,12 @@
       <c r="CK334" s="3"/>
       <c r="CL334" s="3"/>
       <c r="CM334" s="3"/>
-    </row>
-    <row r="335" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN334" s="3"/>
+      <c r="CO334" s="3"/>
+      <c r="CP334" s="3"/>
+      <c r="CQ334" s="3"/>
+    </row>
+    <row r="335" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C335" s="3"/>
       <c r="D335" s="3"/>
       <c r="E335" s="3"/>
@@ -31881,8 +33584,12 @@
       <c r="CK335" s="3"/>
       <c r="CL335" s="3"/>
       <c r="CM335" s="3"/>
-    </row>
-    <row r="336" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN335" s="3"/>
+      <c r="CO335" s="3"/>
+      <c r="CP335" s="3"/>
+      <c r="CQ335" s="3"/>
+    </row>
+    <row r="336" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C336" s="3"/>
       <c r="D336" s="3"/>
       <c r="E336" s="3"/>
@@ -31972,8 +33679,12 @@
       <c r="CK336" s="3"/>
       <c r="CL336" s="3"/>
       <c r="CM336" s="3"/>
-    </row>
-    <row r="337" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN336" s="3"/>
+      <c r="CO336" s="3"/>
+      <c r="CP336" s="3"/>
+      <c r="CQ336" s="3"/>
+    </row>
+    <row r="337" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C337" s="3"/>
       <c r="D337" s="3"/>
       <c r="E337" s="3"/>
@@ -32063,8 +33774,12 @@
       <c r="CK337" s="3"/>
       <c r="CL337" s="3"/>
       <c r="CM337" s="3"/>
-    </row>
-    <row r="338" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN337" s="3"/>
+      <c r="CO337" s="3"/>
+      <c r="CP337" s="3"/>
+      <c r="CQ337" s="3"/>
+    </row>
+    <row r="338" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C338" s="3"/>
       <c r="D338" s="3"/>
       <c r="E338" s="3"/>
@@ -32154,8 +33869,12 @@
       <c r="CK338" s="3"/>
       <c r="CL338" s="3"/>
       <c r="CM338" s="3"/>
-    </row>
-    <row r="339" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN338" s="3"/>
+      <c r="CO338" s="3"/>
+      <c r="CP338" s="3"/>
+      <c r="CQ338" s="3"/>
+    </row>
+    <row r="339" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C339" s="3"/>
       <c r="D339" s="3"/>
       <c r="E339" s="3"/>
@@ -32245,8 +33964,12 @@
       <c r="CK339" s="3"/>
       <c r="CL339" s="3"/>
       <c r="CM339" s="3"/>
-    </row>
-    <row r="340" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN339" s="3"/>
+      <c r="CO339" s="3"/>
+      <c r="CP339" s="3"/>
+      <c r="CQ339" s="3"/>
+    </row>
+    <row r="340" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C340" s="3"/>
       <c r="D340" s="3"/>
       <c r="E340" s="3"/>
@@ -32336,8 +34059,12 @@
       <c r="CK340" s="3"/>
       <c r="CL340" s="3"/>
       <c r="CM340" s="3"/>
-    </row>
-    <row r="341" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN340" s="3"/>
+      <c r="CO340" s="3"/>
+      <c r="CP340" s="3"/>
+      <c r="CQ340" s="3"/>
+    </row>
+    <row r="341" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C341" s="3"/>
       <c r="D341" s="3"/>
       <c r="E341" s="3"/>
@@ -32427,8 +34154,12 @@
       <c r="CK341" s="3"/>
       <c r="CL341" s="3"/>
       <c r="CM341" s="3"/>
-    </row>
-    <row r="342" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN341" s="3"/>
+      <c r="CO341" s="3"/>
+      <c r="CP341" s="3"/>
+      <c r="CQ341" s="3"/>
+    </row>
+    <row r="342" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C342" s="3"/>
       <c r="D342" s="3"/>
       <c r="E342" s="3"/>
@@ -32518,8 +34249,12 @@
       <c r="CK342" s="3"/>
       <c r="CL342" s="3"/>
       <c r="CM342" s="3"/>
-    </row>
-    <row r="343" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN342" s="3"/>
+      <c r="CO342" s="3"/>
+      <c r="CP342" s="3"/>
+      <c r="CQ342" s="3"/>
+    </row>
+    <row r="343" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C343" s="3"/>
       <c r="D343" s="3"/>
       <c r="E343" s="3"/>
@@ -32609,8 +34344,12 @@
       <c r="CK343" s="3"/>
       <c r="CL343" s="3"/>
       <c r="CM343" s="3"/>
-    </row>
-    <row r="344" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN343" s="3"/>
+      <c r="CO343" s="3"/>
+      <c r="CP343" s="3"/>
+      <c r="CQ343" s="3"/>
+    </row>
+    <row r="344" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C344" s="3"/>
       <c r="D344" s="3"/>
       <c r="E344" s="3"/>
@@ -32700,8 +34439,12 @@
       <c r="CK344" s="3"/>
       <c r="CL344" s="3"/>
       <c r="CM344" s="3"/>
-    </row>
-    <row r="345" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN344" s="3"/>
+      <c r="CO344" s="3"/>
+      <c r="CP344" s="3"/>
+      <c r="CQ344" s="3"/>
+    </row>
+    <row r="345" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C345" s="3"/>
       <c r="D345" s="3"/>
       <c r="E345" s="3"/>
@@ -32791,8 +34534,12 @@
       <c r="CK345" s="3"/>
       <c r="CL345" s="3"/>
       <c r="CM345" s="3"/>
-    </row>
-    <row r="346" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN345" s="3"/>
+      <c r="CO345" s="3"/>
+      <c r="CP345" s="3"/>
+      <c r="CQ345" s="3"/>
+    </row>
+    <row r="346" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C346" s="3"/>
       <c r="D346" s="3"/>
       <c r="E346" s="3"/>
@@ -32882,8 +34629,12 @@
       <c r="CK346" s="3"/>
       <c r="CL346" s="3"/>
       <c r="CM346" s="3"/>
-    </row>
-    <row r="347" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN346" s="3"/>
+      <c r="CO346" s="3"/>
+      <c r="CP346" s="3"/>
+      <c r="CQ346" s="3"/>
+    </row>
+    <row r="347" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C347" s="3"/>
       <c r="D347" s="3"/>
       <c r="E347" s="3"/>
@@ -32973,8 +34724,12 @@
       <c r="CK347" s="3"/>
       <c r="CL347" s="3"/>
       <c r="CM347" s="3"/>
-    </row>
-    <row r="348" spans="3:91" x14ac:dyDescent="0.2">
+      <c r="CN347" s="3"/>
+      <c r="CO347" s="3"/>
+      <c r="CP347" s="3"/>
+      <c r="CQ347" s="3"/>
+    </row>
+    <row r="348" spans="3:95" x14ac:dyDescent="0.2">
       <c r="C348" s="3"/>
       <c r="D348" s="3"/>
       <c r="E348" s="3"/>
@@ -33064,6 +34819,10 @@
       <c r="CK348" s="3"/>
       <c r="CL348" s="3"/>
       <c r="CM348" s="3"/>
+      <c r="CN348" s="3"/>
+      <c r="CO348" s="3"/>
+      <c r="CP348" s="3"/>
+      <c r="CQ348" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
